--- a/examples/TimeCourse_Niepel_CellSyst_2019/report/v1/raw_data/MN20160421_X03 total.xlsx
+++ b/examples/TimeCourse_Niepel_CellSyst_2019/report/v1/raw_data/MN20160421_X03 total.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8069" uniqueCount="5867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6209" uniqueCount="4528">
   <si>
     <t>Label: MN20160421_X03</t>
   </si>
@@ -13598,4023 +13598,6 @@
   </si>
   <si>
     <t>9847</t>
-  </si>
-  <si>
-    <t>4/24/2016 7:45:00 PM</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>878</t>
-  </si>
-  <si>
-    <t>9658</t>
-  </si>
-  <si>
-    <t>11332</t>
-  </si>
-  <si>
-    <t>12569</t>
-  </si>
-  <si>
-    <t>8432</t>
-  </si>
-  <si>
-    <t>11263</t>
-  </si>
-  <si>
-    <t>8941</t>
-  </si>
-  <si>
-    <t>14601</t>
-  </si>
-  <si>
-    <t>12568</t>
-  </si>
-  <si>
-    <t>3646</t>
-  </si>
-  <si>
-    <t>4948</t>
-  </si>
-  <si>
-    <t>4317</t>
-  </si>
-  <si>
-    <t>10157</t>
-  </si>
-  <si>
-    <t>3627</t>
-  </si>
-  <si>
-    <t>17186</t>
-  </si>
-  <si>
-    <t>6082</t>
-  </si>
-  <si>
-    <t>16647</t>
-  </si>
-  <si>
-    <t>3569</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>12282</t>
-  </si>
-  <si>
-    <t>5870</t>
-  </si>
-  <si>
-    <t>3349</t>
-  </si>
-  <si>
-    <t>13600</t>
-  </si>
-  <si>
-    <t>13885</t>
-  </si>
-  <si>
-    <t>17700</t>
-  </si>
-  <si>
-    <t>2376</t>
-  </si>
-  <si>
-    <t>16684</t>
-  </si>
-  <si>
-    <t>15699</t>
-  </si>
-  <si>
-    <t>11974</t>
-  </si>
-  <si>
-    <t>17053</t>
-  </si>
-  <si>
-    <t>4498</t>
-  </si>
-  <si>
-    <t>13995</t>
-  </si>
-  <si>
-    <t>17520</t>
-  </si>
-  <si>
-    <t>11550</t>
-  </si>
-  <si>
-    <t>7130</t>
-  </si>
-  <si>
-    <t>18147</t>
-  </si>
-  <si>
-    <t>16697</t>
-  </si>
-  <si>
-    <t>2609</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>12506</t>
-  </si>
-  <si>
-    <t>16207</t>
-  </si>
-  <si>
-    <t>16852</t>
-  </si>
-  <si>
-    <t>16777</t>
-  </si>
-  <si>
-    <t>18130</t>
-  </si>
-  <si>
-    <t>10639</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>16976</t>
-  </si>
-  <si>
-    <t>12648</t>
-  </si>
-  <si>
-    <t>5252</t>
-  </si>
-  <si>
-    <t>15527</t>
-  </si>
-  <si>
-    <t>16326</t>
-  </si>
-  <si>
-    <t>6250</t>
-  </si>
-  <si>
-    <t>2987</t>
-  </si>
-  <si>
-    <t>17155</t>
-  </si>
-  <si>
-    <t>13947</t>
-  </si>
-  <si>
-    <t>15108</t>
-  </si>
-  <si>
-    <t>11329</t>
-  </si>
-  <si>
-    <t>15786</t>
-  </si>
-  <si>
-    <t>6204</t>
-  </si>
-  <si>
-    <t>7867</t>
-  </si>
-  <si>
-    <t>17330</t>
-  </si>
-  <si>
-    <t>8020</t>
-  </si>
-  <si>
-    <t>17706</t>
-  </si>
-  <si>
-    <t>17224</t>
-  </si>
-  <si>
-    <t>17462</t>
-  </si>
-  <si>
-    <t>16259</t>
-  </si>
-  <si>
-    <t>13902</t>
-  </si>
-  <si>
-    <t>8567</t>
-  </si>
-  <si>
-    <t>17225</t>
-  </si>
-  <si>
-    <t>16903</t>
-  </si>
-  <si>
-    <t>17256</t>
-  </si>
-  <si>
-    <t>2060</t>
-  </si>
-  <si>
-    <t>3436</t>
-  </si>
-  <si>
-    <t>18027</t>
-  </si>
-  <si>
-    <t>17704</t>
-  </si>
-  <si>
-    <t>10866</t>
-  </si>
-  <si>
-    <t>1878</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>1693</t>
-  </si>
-  <si>
-    <t>14149</t>
-  </si>
-  <si>
-    <t>15807</t>
-  </si>
-  <si>
-    <t>2911</t>
-  </si>
-  <si>
-    <t>16838</t>
-  </si>
-  <si>
-    <t>6226</t>
-  </si>
-  <si>
-    <t>10371</t>
-  </si>
-  <si>
-    <t>17469</t>
-  </si>
-  <si>
-    <t>17658</t>
-  </si>
-  <si>
-    <t>17221</t>
-  </si>
-  <si>
-    <t>13653</t>
-  </si>
-  <si>
-    <t>13496</t>
-  </si>
-  <si>
-    <t>12116</t>
-  </si>
-  <si>
-    <t>16503</t>
-  </si>
-  <si>
-    <t>17719</t>
-  </si>
-  <si>
-    <t>17008</t>
-  </si>
-  <si>
-    <t>18324</t>
-  </si>
-  <si>
-    <t>16404</t>
-  </si>
-  <si>
-    <t>10724</t>
-  </si>
-  <si>
-    <t>8750</t>
-  </si>
-  <si>
-    <t>17668</t>
-  </si>
-  <si>
-    <t>17802</t>
-  </si>
-  <si>
-    <t>6524</t>
-  </si>
-  <si>
-    <t>7484</t>
-  </si>
-  <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>17641</t>
-  </si>
-  <si>
-    <t>16936</t>
-  </si>
-  <si>
-    <t>15382</t>
-  </si>
-  <si>
-    <t>17536</t>
-  </si>
-  <si>
-    <t>15116</t>
-  </si>
-  <si>
-    <t>17959</t>
-  </si>
-  <si>
-    <t>17766</t>
-  </si>
-  <si>
-    <t>16281</t>
-  </si>
-  <si>
-    <t>12351</t>
-  </si>
-  <si>
-    <t>2064</t>
-  </si>
-  <si>
-    <t>1995</t>
-  </si>
-  <si>
-    <t>6662</t>
-  </si>
-  <si>
-    <t>15162</t>
-  </si>
-  <si>
-    <t>9118</t>
-  </si>
-  <si>
-    <t>18808</t>
-  </si>
-  <si>
-    <t>17873</t>
-  </si>
-  <si>
-    <t>16671</t>
-  </si>
-  <si>
-    <t>15523</t>
-  </si>
-  <si>
-    <t>14818</t>
-  </si>
-  <si>
-    <t>3318</t>
-  </si>
-  <si>
-    <t>9962</t>
-  </si>
-  <si>
-    <t>15544</t>
-  </si>
-  <si>
-    <t>2473</t>
-  </si>
-  <si>
-    <t>16963</t>
-  </si>
-  <si>
-    <t>17003</t>
-  </si>
-  <si>
-    <t>17222</t>
-  </si>
-  <si>
-    <t>17455</t>
-  </si>
-  <si>
-    <t>5980</t>
-  </si>
-  <si>
-    <t>17264</t>
-  </si>
-  <si>
-    <t>16894</t>
-  </si>
-  <si>
-    <t>16859</t>
-  </si>
-  <si>
-    <t>9915</t>
-  </si>
-  <si>
-    <t>18150</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>17599</t>
-  </si>
-  <si>
-    <t>11088</t>
-  </si>
-  <si>
-    <t>13639</t>
-  </si>
-  <si>
-    <t>3556</t>
-  </si>
-  <si>
-    <t>15562</t>
-  </si>
-  <si>
-    <t>7923</t>
-  </si>
-  <si>
-    <t>3060</t>
-  </si>
-  <si>
-    <t>17114</t>
-  </si>
-  <si>
-    <t>3435</t>
-  </si>
-  <si>
-    <t>16354</t>
-  </si>
-  <si>
-    <t>9568</t>
-  </si>
-  <si>
-    <t>17402</t>
-  </si>
-  <si>
-    <t>17597</t>
-  </si>
-  <si>
-    <t>9044</t>
-  </si>
-  <si>
-    <t>17023</t>
-  </si>
-  <si>
-    <t>6505</t>
-  </si>
-  <si>
-    <t>16949</t>
-  </si>
-  <si>
-    <t>17623</t>
-  </si>
-  <si>
-    <t>16251</t>
-  </si>
-  <si>
-    <t>17045</t>
-  </si>
-  <si>
-    <t>17882</t>
-  </si>
-  <si>
-    <t>17521</t>
-  </si>
-  <si>
-    <t>17790</t>
-  </si>
-  <si>
-    <t>17601</t>
-  </si>
-  <si>
-    <t>10978</t>
-  </si>
-  <si>
-    <t>3786</t>
-  </si>
-  <si>
-    <t>12846</t>
-  </si>
-  <si>
-    <t>4964</t>
-  </si>
-  <si>
-    <t>16356</t>
-  </si>
-  <si>
-    <t>3104</t>
-  </si>
-  <si>
-    <t>5995</t>
-  </si>
-  <si>
-    <t>1566</t>
-  </si>
-  <si>
-    <t>17119</t>
-  </si>
-  <si>
-    <t>16505</t>
-  </si>
-  <si>
-    <t>17707</t>
-  </si>
-  <si>
-    <t>17710</t>
-  </si>
-  <si>
-    <t>6656</t>
-  </si>
-  <si>
-    <t>6215</t>
-  </si>
-  <si>
-    <t>15411</t>
-  </si>
-  <si>
-    <t>2575</t>
-  </si>
-  <si>
-    <t>16712</t>
-  </si>
-  <si>
-    <t>17733</t>
-  </si>
-  <si>
-    <t>17379</t>
-  </si>
-  <si>
-    <t>14184</t>
-  </si>
-  <si>
-    <t>17764</t>
-  </si>
-  <si>
-    <t>16665</t>
-  </si>
-  <si>
-    <t>17532</t>
-  </si>
-  <si>
-    <t>17399</t>
-  </si>
-  <si>
-    <t>13841</t>
-  </si>
-  <si>
-    <t>14095</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>11145</t>
-  </si>
-  <si>
-    <t>10163</t>
-  </si>
-  <si>
-    <t>17765</t>
-  </si>
-  <si>
-    <t>16882</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>17420</t>
-  </si>
-  <si>
-    <t>15830</t>
-  </si>
-  <si>
-    <t>12036</t>
-  </si>
-  <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>16948</t>
-  </si>
-  <si>
-    <t>9591</t>
-  </si>
-  <si>
-    <t>7726</t>
-  </si>
-  <si>
-    <t>18017</t>
-  </si>
-  <si>
-    <t>8899</t>
-  </si>
-  <si>
-    <t>17502</t>
-  </si>
-  <si>
-    <t>13862</t>
-  </si>
-  <si>
-    <t>17314</t>
-  </si>
-  <si>
-    <t>900</t>
-  </si>
-  <si>
-    <t>12528</t>
-  </si>
-  <si>
-    <t>16550</t>
-  </si>
-  <si>
-    <t>7414</t>
-  </si>
-  <si>
-    <t>6823</t>
-  </si>
-  <si>
-    <t>14708</t>
-  </si>
-  <si>
-    <t>1078</t>
-  </si>
-  <si>
-    <t>6778</t>
-  </si>
-  <si>
-    <t>12532</t>
-  </si>
-  <si>
-    <t>5869</t>
-  </si>
-  <si>
-    <t>17271</t>
-  </si>
-  <si>
-    <t>9881</t>
-  </si>
-  <si>
-    <t>3478</t>
-  </si>
-  <si>
-    <t>6026</t>
-  </si>
-  <si>
-    <t>12966</t>
-  </si>
-  <si>
-    <t>8474</t>
-  </si>
-  <si>
-    <t>9470</t>
-  </si>
-  <si>
-    <t>2177</t>
-  </si>
-  <si>
-    <t>12102</t>
-  </si>
-  <si>
-    <t>8057</t>
-  </si>
-  <si>
-    <t>9891</t>
-  </si>
-  <si>
-    <t>4/24/2016 11:45:00 PM</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>871</t>
-  </si>
-  <si>
-    <t>10033</t>
-  </si>
-  <si>
-    <t>11731</t>
-  </si>
-  <si>
-    <t>12981</t>
-  </si>
-  <si>
-    <t>8589</t>
-  </si>
-  <si>
-    <t>11456</t>
-  </si>
-  <si>
-    <t>11607</t>
-  </si>
-  <si>
-    <t>6583</t>
-  </si>
-  <si>
-    <t>9250</t>
-  </si>
-  <si>
-    <t>13503</t>
-  </si>
-  <si>
-    <t>15187</t>
-  </si>
-  <si>
-    <t>4519</t>
-  </si>
-  <si>
-    <t>10682</t>
-  </si>
-  <si>
-    <t>17869</t>
-  </si>
-  <si>
-    <t>6255</t>
-  </si>
-  <si>
-    <t>17361</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>2371</t>
-  </si>
-  <si>
-    <t>6116</t>
-  </si>
-  <si>
-    <t>14271</t>
-  </si>
-  <si>
-    <t>14538</t>
-  </si>
-  <si>
-    <t>18356</t>
-  </si>
-  <si>
-    <t>17387</t>
-  </si>
-  <si>
-    <t>16329</t>
-  </si>
-  <si>
-    <t>12434</t>
-  </si>
-  <si>
-    <t>17666</t>
-  </si>
-  <si>
-    <t>14661</t>
-  </si>
-  <si>
-    <t>17986</t>
-  </si>
-  <si>
-    <t>12204</t>
-  </si>
-  <si>
-    <t>18743</t>
-  </si>
-  <si>
-    <t>17371</t>
-  </si>
-  <si>
-    <t>14722</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>13302</t>
-  </si>
-  <si>
-    <t>16845</t>
-  </si>
-  <si>
-    <t>17612</t>
-  </si>
-  <si>
-    <t>17348</t>
-  </si>
-  <si>
-    <t>18395</t>
-  </si>
-  <si>
-    <t>11176</t>
-  </si>
-  <si>
-    <t>1042</t>
-  </si>
-  <si>
-    <t>13223</t>
-  </si>
-  <si>
-    <t>16913</t>
-  </si>
-  <si>
-    <t>6553</t>
-  </si>
-  <si>
-    <t>15900</t>
-  </si>
-  <si>
-    <t>11861</t>
-  </si>
-  <si>
-    <t>16534</t>
-  </si>
-  <si>
-    <t>10096</t>
-  </si>
-  <si>
-    <t>8446</t>
-  </si>
-  <si>
-    <t>18098</t>
-  </si>
-  <si>
-    <t>14899</t>
-  </si>
-  <si>
-    <t>18073</t>
-  </si>
-  <si>
-    <t>2693</t>
-  </si>
-  <si>
-    <t>17854</t>
-  </si>
-  <si>
-    <t>18303</t>
-  </si>
-  <si>
-    <t>16834</t>
-  </si>
-  <si>
-    <t>14599</t>
-  </si>
-  <si>
-    <t>8966</t>
-  </si>
-  <si>
-    <t>17481</t>
-  </si>
-  <si>
-    <t>17763</t>
-  </si>
-  <si>
-    <t>17834</t>
-  </si>
-  <si>
-    <t>2486</t>
-  </si>
-  <si>
-    <t>3438</t>
-  </si>
-  <si>
-    <t>18408</t>
-  </si>
-  <si>
-    <t>18038</t>
-  </si>
-  <si>
-    <t>11333</t>
-  </si>
-  <si>
-    <t>1033</t>
-  </si>
-  <si>
-    <t>14885</t>
-  </si>
-  <si>
-    <t>16499</t>
-  </si>
-  <si>
-    <t>17391</t>
-  </si>
-  <si>
-    <t>6517</t>
-  </si>
-  <si>
-    <t>10882</t>
-  </si>
-  <si>
-    <t>17956</t>
-  </si>
-  <si>
-    <t>3726</t>
-  </si>
-  <si>
-    <t>14520</t>
-  </si>
-  <si>
-    <t>18258</t>
-  </si>
-  <si>
-    <t>18110</t>
-  </si>
-  <si>
-    <t>14361</t>
-  </si>
-  <si>
-    <t>1487</t>
-  </si>
-  <si>
-    <t>14014</t>
-  </si>
-  <si>
-    <t>12841</t>
-  </si>
-  <si>
-    <t>15444</t>
-  </si>
-  <si>
-    <t>17123</t>
-  </si>
-  <si>
-    <t>18099</t>
-  </si>
-  <si>
-    <t>19092</t>
-  </si>
-  <si>
-    <t>18333</t>
-  </si>
-  <si>
-    <t>17027</t>
-  </si>
-  <si>
-    <t>11123</t>
-  </si>
-  <si>
-    <t>9287</t>
-  </si>
-  <si>
-    <t>18255</t>
-  </si>
-  <si>
-    <t>18485</t>
-  </si>
-  <si>
-    <t>6672</t>
-  </si>
-  <si>
-    <t>7896</t>
-  </si>
-  <si>
-    <t>18052</t>
-  </si>
-  <si>
-    <t>17376</t>
-  </si>
-  <si>
-    <t>16108</t>
-  </si>
-  <si>
-    <t>18043</t>
-  </si>
-  <si>
-    <t>15856</t>
-  </si>
-  <si>
-    <t>18368</t>
-  </si>
-  <si>
-    <t>18332</t>
-  </si>
-  <si>
-    <t>17142</t>
-  </si>
-  <si>
-    <t>12726</t>
-  </si>
-  <si>
-    <t>17517</t>
-  </si>
-  <si>
-    <t>4547</t>
-  </si>
-  <si>
-    <t>6964</t>
-  </si>
-  <si>
-    <t>9533</t>
-  </si>
-  <si>
-    <t>19538</t>
-  </si>
-  <si>
-    <t>18517</t>
-  </si>
-  <si>
-    <t>17609</t>
-  </si>
-  <si>
-    <t>7889</t>
-  </si>
-  <si>
-    <t>16016</t>
-  </si>
-  <si>
-    <t>10453</t>
-  </si>
-  <si>
-    <t>16050</t>
-  </si>
-  <si>
-    <t>17622</t>
-  </si>
-  <si>
-    <t>17579</t>
-  </si>
-  <si>
-    <t>3292</t>
-  </si>
-  <si>
-    <t>17887</t>
-  </si>
-  <si>
-    <t>6163</t>
-  </si>
-  <si>
-    <t>18070</t>
-  </si>
-  <si>
-    <t>6234</t>
-  </si>
-  <si>
-    <t>17775</t>
-  </si>
-  <si>
-    <t>17381</t>
-  </si>
-  <si>
-    <t>16267</t>
-  </si>
-  <si>
-    <t>2926</t>
-  </si>
-  <si>
-    <t>5183</t>
-  </si>
-  <si>
-    <t>10399</t>
-  </si>
-  <si>
-    <t>18566</t>
-  </si>
-  <si>
-    <t>1080</t>
-  </si>
-  <si>
-    <t>18143</t>
-  </si>
-  <si>
-    <t>11441</t>
-  </si>
-  <si>
-    <t>14329</t>
-  </si>
-  <si>
-    <t>3616</t>
-  </si>
-  <si>
-    <t>16280</t>
-  </si>
-  <si>
-    <t>8406</t>
-  </si>
-  <si>
-    <t>3134</t>
-  </si>
-  <si>
-    <t>17588</t>
-  </si>
-  <si>
-    <t>3573</t>
-  </si>
-  <si>
-    <t>16929</t>
-  </si>
-  <si>
-    <t>9980</t>
-  </si>
-  <si>
-    <t>17985</t>
-  </si>
-  <si>
-    <t>18084</t>
-  </si>
-  <si>
-    <t>9573</t>
-  </si>
-  <si>
-    <t>17543</t>
-  </si>
-  <si>
-    <t>6734</t>
-  </si>
-  <si>
-    <t>17501</t>
-  </si>
-  <si>
-    <t>18271</t>
-  </si>
-  <si>
-    <t>16941</t>
-  </si>
-  <si>
-    <t>17945</t>
-  </si>
-  <si>
-    <t>4778</t>
-  </si>
-  <si>
-    <t>18391</t>
-  </si>
-  <si>
-    <t>18157</t>
-  </si>
-  <si>
-    <t>18411</t>
-  </si>
-  <si>
-    <t>18080</t>
-  </si>
-  <si>
-    <t>11364</t>
-  </si>
-  <si>
-    <t>3827</t>
-  </si>
-  <si>
-    <t>13530</t>
-  </si>
-  <si>
-    <t>5060</t>
-  </si>
-  <si>
-    <t>17137</t>
-  </si>
-  <si>
-    <t>3140</t>
-  </si>
-  <si>
-    <t>2702</t>
-  </si>
-  <si>
-    <t>17813</t>
-  </si>
-  <si>
-    <t>17223</t>
-  </si>
-  <si>
-    <t>18227</t>
-  </si>
-  <si>
-    <t>18223</t>
-  </si>
-  <si>
-    <t>6930</t>
-  </si>
-  <si>
-    <t>6371</t>
-  </si>
-  <si>
-    <t>16072</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>2634</t>
-  </si>
-  <si>
-    <t>13935</t>
-  </si>
-  <si>
-    <t>17369</t>
-  </si>
-  <si>
-    <t>18344</t>
-  </si>
-  <si>
-    <t>17993</t>
-  </si>
-  <si>
-    <t>14813</t>
-  </si>
-  <si>
-    <t>18187</t>
-  </si>
-  <si>
-    <t>17298</t>
-  </si>
-  <si>
-    <t>18015</t>
-  </si>
-  <si>
-    <t>17964</t>
-  </si>
-  <si>
-    <t>14602</t>
-  </si>
-  <si>
-    <t>14620</t>
-  </si>
-  <si>
-    <t>11608</t>
-  </si>
-  <si>
-    <t>10810</t>
-  </si>
-  <si>
-    <t>18438</t>
-  </si>
-  <si>
-    <t>17613</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>959</t>
-  </si>
-  <si>
-    <t>17981</t>
-  </si>
-  <si>
-    <t>16527</t>
-  </si>
-  <si>
-    <t>6108</t>
-  </si>
-  <si>
-    <t>12476</t>
-  </si>
-  <si>
-    <t>957</t>
-  </si>
-  <si>
-    <t>3136</t>
-  </si>
-  <si>
-    <t>17701</t>
-  </si>
-  <si>
-    <t>10052</t>
-  </si>
-  <si>
-    <t>18704</t>
-  </si>
-  <si>
-    <t>9318</t>
-  </si>
-  <si>
-    <t>18186</t>
-  </si>
-  <si>
-    <t>14491</t>
-  </si>
-  <si>
-    <t>18067</t>
-  </si>
-  <si>
-    <t>12438</t>
-  </si>
-  <si>
-    <t>872</t>
-  </si>
-  <si>
-    <t>13092</t>
-  </si>
-  <si>
-    <t>17409</t>
-  </si>
-  <si>
-    <t>16612</t>
-  </si>
-  <si>
-    <t>7906</t>
-  </si>
-  <si>
-    <t>7025</t>
-  </si>
-  <si>
-    <t>15535</t>
-  </si>
-  <si>
-    <t>1031</t>
-  </si>
-  <si>
-    <t>7129</t>
-  </si>
-  <si>
-    <t>13082</t>
-  </si>
-  <si>
-    <t>17933</t>
-  </si>
-  <si>
-    <t>10396</t>
-  </si>
-  <si>
-    <t>15016</t>
-  </si>
-  <si>
-    <t>3512</t>
-  </si>
-  <si>
-    <t>12023</t>
-  </si>
-  <si>
-    <t>13347</t>
-  </si>
-  <si>
-    <t>8326</t>
-  </si>
-  <si>
-    <t>12449</t>
-  </si>
-  <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>8397</t>
-  </si>
-  <si>
-    <t>10042</t>
-  </si>
-  <si>
-    <t>4/25/2016 3:45:00 AM</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>817</t>
-  </si>
-  <si>
-    <t>2474</t>
-  </si>
-  <si>
-    <t>12166</t>
-  </si>
-  <si>
-    <t>13492</t>
-  </si>
-  <si>
-    <t>8730</t>
-  </si>
-  <si>
-    <t>9425</t>
-  </si>
-  <si>
-    <t>14063</t>
-  </si>
-  <si>
-    <t>15783</t>
-  </si>
-  <si>
-    <t>13775</t>
-  </si>
-  <si>
-    <t>3537</t>
-  </si>
-  <si>
-    <t>17113</t>
-  </si>
-  <si>
-    <t>4679</t>
-  </si>
-  <si>
-    <t>11346</t>
-  </si>
-  <si>
-    <t>18512</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>3687</t>
-  </si>
-  <si>
-    <t>882</t>
-  </si>
-  <si>
-    <t>2366</t>
-  </si>
-  <si>
-    <t>14980</t>
-  </si>
-  <si>
-    <t>6295</t>
-  </si>
-  <si>
-    <t>3480</t>
-  </si>
-  <si>
-    <t>14944</t>
-  </si>
-  <si>
-    <t>15209</t>
-  </si>
-  <si>
-    <t>18975</t>
-  </si>
-  <si>
-    <t>18177</t>
-  </si>
-  <si>
-    <t>17034</t>
-  </si>
-  <si>
-    <t>5369</t>
-  </si>
-  <si>
-    <t>18253</t>
-  </si>
-  <si>
-    <t>4911</t>
-  </si>
-  <si>
-    <t>15387</t>
-  </si>
-  <si>
-    <t>18591</t>
-  </si>
-  <si>
-    <t>12896</t>
-  </si>
-  <si>
-    <t>10523</t>
-  </si>
-  <si>
-    <t>7601</t>
-  </si>
-  <si>
-    <t>19380</t>
-  </si>
-  <si>
-    <t>1943</t>
-  </si>
-  <si>
-    <t>15299</t>
-  </si>
-  <si>
-    <t>14100</t>
-  </si>
-  <si>
-    <t>17607</t>
-  </si>
-  <si>
-    <t>17917</t>
-  </si>
-  <si>
-    <t>18759</t>
-  </si>
-  <si>
-    <t>11716</t>
-  </si>
-  <si>
-    <t>986</t>
-  </si>
-  <si>
-    <t>3323</t>
-  </si>
-  <si>
-    <t>18379</t>
-  </si>
-  <si>
-    <t>13760</t>
-  </si>
-  <si>
-    <t>5700</t>
-  </si>
-  <si>
-    <t>16975</t>
-  </si>
-  <si>
-    <t>17578</t>
-  </si>
-  <si>
-    <t>3031</t>
-  </si>
-  <si>
-    <t>17998</t>
-  </si>
-  <si>
-    <t>15150</t>
-  </si>
-  <si>
-    <t>16795</t>
-  </si>
-  <si>
-    <t>12459</t>
-  </si>
-  <si>
-    <t>17116</t>
-  </si>
-  <si>
-    <t>10505</t>
-  </si>
-  <si>
-    <t>1591</t>
-  </si>
-  <si>
-    <t>8711</t>
-  </si>
-  <si>
-    <t>18932</t>
-  </si>
-  <si>
-    <t>15674</t>
-  </si>
-  <si>
-    <t>2274</t>
-  </si>
-  <si>
-    <t>8619</t>
-  </si>
-  <si>
-    <t>18210</t>
-  </si>
-  <si>
-    <t>19085</t>
-  </si>
-  <si>
-    <t>15243</t>
-  </si>
-  <si>
-    <t>9447</t>
-  </si>
-  <si>
-    <t>18206</t>
-  </si>
-  <si>
-    <t>18129</t>
-  </si>
-  <si>
-    <t>18282</t>
-  </si>
-  <si>
-    <t>2520</t>
-  </si>
-  <si>
-    <t>18721</t>
-  </si>
-  <si>
-    <t>18370</t>
-  </si>
-  <si>
-    <t>11887</t>
-  </si>
-  <si>
-    <t>979</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>15487</t>
-  </si>
-  <si>
-    <t>17358</t>
-  </si>
-  <si>
-    <t>17918</t>
-  </si>
-  <si>
-    <t>6836</t>
-  </si>
-  <si>
-    <t>11468</t>
-  </si>
-  <si>
-    <t>18428</t>
-  </si>
-  <si>
-    <t>15161</t>
-  </si>
-  <si>
-    <t>18650</t>
-  </si>
-  <si>
-    <t>18944</t>
-  </si>
-  <si>
-    <t>14617</t>
-  </si>
-  <si>
-    <t>13635</t>
-  </si>
-  <si>
-    <t>16319</t>
-  </si>
-  <si>
-    <t>17727</t>
-  </si>
-  <si>
-    <t>18578</t>
-  </si>
-  <si>
-    <t>18023</t>
-  </si>
-  <si>
-    <t>19678</t>
-  </si>
-  <si>
-    <t>18739</t>
-  </si>
-  <si>
-    <t>17736</t>
-  </si>
-  <si>
-    <t>11566</t>
-  </si>
-  <si>
-    <t>18740</t>
-  </si>
-  <si>
-    <t>3557</t>
-  </si>
-  <si>
-    <t>19157</t>
-  </si>
-  <si>
-    <t>8327</t>
-  </si>
-  <si>
-    <t>981</t>
-  </si>
-  <si>
-    <t>18531</t>
-  </si>
-  <si>
-    <t>17770</t>
-  </si>
-  <si>
-    <t>16939</t>
-  </si>
-  <si>
-    <t>18446</t>
-  </si>
-  <si>
-    <t>16179</t>
-  </si>
-  <si>
-    <t>18731</t>
-  </si>
-  <si>
-    <t>2472</t>
-  </si>
-  <si>
-    <t>18850</t>
-  </si>
-  <si>
-    <t>18011</t>
-  </si>
-  <si>
-    <t>13234</t>
-  </si>
-  <si>
-    <t>18044</t>
-  </si>
-  <si>
-    <t>4754</t>
-  </si>
-  <si>
-    <t>2089</t>
-  </si>
-  <si>
-    <t>16526</t>
-  </si>
-  <si>
-    <t>9970</t>
-  </si>
-  <si>
-    <t>19904</t>
-  </si>
-  <si>
-    <t>12001</t>
-  </si>
-  <si>
-    <t>18831</t>
-  </si>
-  <si>
-    <t>18178</t>
-  </si>
-  <si>
-    <t>2999</t>
-  </si>
-  <si>
-    <t>8237</t>
-  </si>
-  <si>
-    <t>16878</t>
-  </si>
-  <si>
-    <t>10979</t>
-  </si>
-  <si>
-    <t>16651</t>
-  </si>
-  <si>
-    <t>18302</t>
-  </si>
-  <si>
-    <t>18588</t>
-  </si>
-  <si>
-    <t>6267</t>
-  </si>
-  <si>
-    <t>18875</t>
-  </si>
-  <si>
-    <t>6573</t>
-  </si>
-  <si>
-    <t>18196</t>
-  </si>
-  <si>
-    <t>18061</t>
-  </si>
-  <si>
-    <t>18033</t>
-  </si>
-  <si>
-    <t>5322</t>
-  </si>
-  <si>
-    <t>19094</t>
-  </si>
-  <si>
-    <t>1048</t>
-  </si>
-  <si>
-    <t>18661</t>
-  </si>
-  <si>
-    <t>12026</t>
-  </si>
-  <si>
-    <t>15119</t>
-  </si>
-  <si>
-    <t>16938</t>
-  </si>
-  <si>
-    <t>9065</t>
-  </si>
-  <si>
-    <t>3257</t>
-  </si>
-  <si>
-    <t>18189</t>
-  </si>
-  <si>
-    <t>17406</t>
-  </si>
-  <si>
-    <t>18555</t>
-  </si>
-  <si>
-    <t>18655</t>
-  </si>
-  <si>
-    <t>10107</t>
-  </si>
-  <si>
-    <t>18118</t>
-  </si>
-  <si>
-    <t>1564</t>
-  </si>
-  <si>
-    <t>6960</t>
-  </si>
-  <si>
-    <t>18108</t>
-  </si>
-  <si>
-    <t>18765</t>
-  </si>
-  <si>
-    <t>17586</t>
-  </si>
-  <si>
-    <t>18764</t>
-  </si>
-  <si>
-    <t>4889</t>
-  </si>
-  <si>
-    <t>18931</t>
-  </si>
-  <si>
-    <t>18797</t>
-  </si>
-  <si>
-    <t>18599</t>
-  </si>
-  <si>
-    <t>12053</t>
-  </si>
-  <si>
-    <t>14239</t>
-  </si>
-  <si>
-    <t>5176</t>
-  </si>
-  <si>
-    <t>17938</t>
-  </si>
-  <si>
-    <t>6580</t>
-  </si>
-  <si>
-    <t>18374</t>
-  </si>
-  <si>
-    <t>18030</t>
-  </si>
-  <si>
-    <t>2534</t>
-  </si>
-  <si>
-    <t>18866</t>
-  </si>
-  <si>
-    <t>18674</t>
-  </si>
-  <si>
-    <t>7127</t>
-  </si>
-  <si>
-    <t>6482</t>
-  </si>
-  <si>
-    <t>16911</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>2655</t>
-  </si>
-  <si>
-    <t>18194</t>
-  </si>
-  <si>
-    <t>18992</t>
-  </si>
-  <si>
-    <t>18507</t>
-  </si>
-  <si>
-    <t>18461</t>
-  </si>
-  <si>
-    <t>17909</t>
-  </si>
-  <si>
-    <t>18538</t>
-  </si>
-  <si>
-    <t>18609</t>
-  </si>
-  <si>
-    <t>15427</t>
-  </si>
-  <si>
-    <t>989</t>
-  </si>
-  <si>
-    <t>11328</t>
-  </si>
-  <si>
-    <t>18911</t>
-  </si>
-  <si>
-    <t>18136</t>
-  </si>
-  <si>
-    <t>965</t>
-  </si>
-  <si>
-    <t>931</t>
-  </si>
-  <si>
-    <t>1434</t>
-  </si>
-  <si>
-    <t>17201</t>
-  </si>
-  <si>
-    <t>6355</t>
-  </si>
-  <si>
-    <t>12939</t>
-  </si>
-  <si>
-    <t>917</t>
-  </si>
-  <si>
-    <t>3172</t>
-  </si>
-  <si>
-    <t>18266</t>
-  </si>
-  <si>
-    <t>8174</t>
-  </si>
-  <si>
-    <t>19300</t>
-  </si>
-  <si>
-    <t>9627</t>
-  </si>
-  <si>
-    <t>10253</t>
-  </si>
-  <si>
-    <t>18694</t>
-  </si>
-  <si>
-    <t>18918</t>
-  </si>
-  <si>
-    <t>13128</t>
-  </si>
-  <si>
-    <t>810</t>
-  </si>
-  <si>
-    <t>13728</t>
-  </si>
-  <si>
-    <t>17979</t>
-  </si>
-  <si>
-    <t>17372</t>
-  </si>
-  <si>
-    <t>8257</t>
-  </si>
-  <si>
-    <t>7215</t>
-  </si>
-  <si>
-    <t>16293</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>7295</t>
-  </si>
-  <si>
-    <t>13656</t>
-  </si>
-  <si>
-    <t>6114</t>
-  </si>
-  <si>
-    <t>18547</t>
-  </si>
-  <si>
-    <t>10987</t>
-  </si>
-  <si>
-    <t>15627</t>
-  </si>
-  <si>
-    <t>3501</t>
-  </si>
-  <si>
-    <t>12430</t>
-  </si>
-  <si>
-    <t>6354</t>
-  </si>
-  <si>
-    <t>13836</t>
-  </si>
-  <si>
-    <t>8171</t>
-  </si>
-  <si>
-    <t>9278</t>
-  </si>
-  <si>
-    <t>12776</t>
-  </si>
-  <si>
-    <t>8647</t>
-  </si>
-  <si>
-    <t>10043</t>
-  </si>
-  <si>
-    <t>4/25/2016 7:45:00 AM</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>779</t>
-  </si>
-  <si>
-    <t>2469</t>
-  </si>
-  <si>
-    <t>10864</t>
-  </si>
-  <si>
-    <t>12499</t>
-  </si>
-  <si>
-    <t>13985</t>
-  </si>
-  <si>
-    <t>8860</t>
-  </si>
-  <si>
-    <t>12151</t>
-  </si>
-  <si>
-    <t>6664</t>
-  </si>
-  <si>
-    <t>9727</t>
-  </si>
-  <si>
-    <t>14558</t>
-  </si>
-  <si>
-    <t>16348</t>
-  </si>
-  <si>
-    <t>14227</t>
-  </si>
-  <si>
-    <t>3418</t>
-  </si>
-  <si>
-    <t>5334</t>
-  </si>
-  <si>
-    <t>18047</t>
-  </si>
-  <si>
-    <t>4785</t>
-  </si>
-  <si>
-    <t>11917</t>
-  </si>
-  <si>
-    <t>19239</t>
-  </si>
-  <si>
-    <t>6544</t>
-  </si>
-  <si>
-    <t>18651</t>
-  </si>
-  <si>
-    <t>875</t>
-  </si>
-  <si>
-    <t>15813</t>
-  </si>
-  <si>
-    <t>3505</t>
-  </si>
-  <si>
-    <t>15634</t>
-  </si>
-  <si>
-    <t>15853</t>
-  </si>
-  <si>
-    <t>19487</t>
-  </si>
-  <si>
-    <t>18909</t>
-  </si>
-  <si>
-    <t>2755</t>
-  </si>
-  <si>
-    <t>5566</t>
-  </si>
-  <si>
-    <t>18923</t>
-  </si>
-  <si>
-    <t>5066</t>
-  </si>
-  <si>
-    <t>15946</t>
-  </si>
-  <si>
-    <t>18903</t>
-  </si>
-  <si>
-    <t>7830</t>
-  </si>
-  <si>
-    <t>19595</t>
-  </si>
-  <si>
-    <t>2057</t>
-  </si>
-  <si>
-    <t>18705</t>
-  </si>
-  <si>
-    <t>16035</t>
-  </si>
-  <si>
-    <t>944</t>
-  </si>
-  <si>
-    <t>14775</t>
-  </si>
-  <si>
-    <t>18167</t>
-  </si>
-  <si>
-    <t>18519</t>
-  </si>
-  <si>
-    <t>18337</t>
-  </si>
-  <si>
-    <t>19015</t>
-  </si>
-  <si>
-    <t>12365</t>
-  </si>
-  <si>
-    <t>948</t>
-  </si>
-  <si>
-    <t>3285</t>
-  </si>
-  <si>
-    <t>18908</t>
-  </si>
-  <si>
-    <t>5897</t>
-  </si>
-  <si>
-    <t>17497</t>
-  </si>
-  <si>
-    <t>18153</t>
-  </si>
-  <si>
-    <t>2925</t>
-  </si>
-  <si>
-    <t>7104</t>
-  </si>
-  <si>
-    <t>3027</t>
-  </si>
-  <si>
-    <t>18160</t>
-  </si>
-  <si>
-    <t>15609</t>
-  </si>
-  <si>
-    <t>17534</t>
-  </si>
-  <si>
-    <t>13057</t>
-  </si>
-  <si>
-    <t>10968</t>
-  </si>
-  <si>
-    <t>7050</t>
-  </si>
-  <si>
-    <t>9348</t>
-  </si>
-  <si>
-    <t>19515</t>
-  </si>
-  <si>
-    <t>16278</t>
-  </si>
-  <si>
-    <t>18585</t>
-  </si>
-  <si>
-    <t>18629</t>
-  </si>
-  <si>
-    <t>19690</t>
-  </si>
-  <si>
-    <t>18247</t>
-  </si>
-  <si>
-    <t>9920</t>
-  </si>
-  <si>
-    <t>18607</t>
-  </si>
-  <si>
-    <t>18744</t>
-  </si>
-  <si>
-    <t>18563</t>
-  </si>
-  <si>
-    <t>18554</t>
-  </si>
-  <si>
-    <t>3471</t>
-  </si>
-  <si>
-    <t>19065</t>
-  </si>
-  <si>
-    <t>18702</t>
-  </si>
-  <si>
-    <t>12516</t>
-  </si>
-  <si>
-    <t>16117</t>
-  </si>
-  <si>
-    <t>18471</t>
-  </si>
-  <si>
-    <t>7073</t>
-  </si>
-  <si>
-    <t>11995</t>
-  </si>
-  <si>
-    <t>18747</t>
-  </si>
-  <si>
-    <t>15803</t>
-  </si>
-  <si>
-    <t>19717</t>
-  </si>
-  <si>
-    <t>17121</t>
-  </si>
-  <si>
-    <t>18315</t>
-  </si>
-  <si>
-    <t>18877</t>
-  </si>
-  <si>
-    <t>20205</t>
-  </si>
-  <si>
-    <t>19230</t>
-  </si>
-  <si>
-    <t>18298</t>
-  </si>
-  <si>
-    <t>10343</t>
-  </si>
-  <si>
-    <t>19150</t>
-  </si>
-  <si>
-    <t>3614</t>
-  </si>
-  <si>
-    <t>19776</t>
-  </si>
-  <si>
-    <t>6749</t>
-  </si>
-  <si>
-    <t>8773</t>
-  </si>
-  <si>
-    <t>928</t>
-  </si>
-  <si>
-    <t>18816</t>
-  </si>
-  <si>
-    <t>17975</t>
-  </si>
-  <si>
-    <t>17807</t>
-  </si>
-  <si>
-    <t>18742</t>
-  </si>
-  <si>
-    <t>16821</t>
-  </si>
-  <si>
-    <t>19000</t>
-  </si>
-  <si>
-    <t>3376</t>
-  </si>
-  <si>
-    <t>19377</t>
-  </si>
-  <si>
-    <t>19021</t>
-  </si>
-  <si>
-    <t>13663</t>
-  </si>
-  <si>
-    <t>4913</t>
-  </si>
-  <si>
-    <t>2126</t>
-  </si>
-  <si>
-    <t>17360</t>
-  </si>
-  <si>
-    <t>10427</t>
-  </si>
-  <si>
-    <t>20093</t>
-  </si>
-  <si>
-    <t>12475</t>
-  </si>
-  <si>
-    <t>19267</t>
-  </si>
-  <si>
-    <t>18827</t>
-  </si>
-  <si>
-    <t>8585</t>
-  </si>
-  <si>
-    <t>17449</t>
-  </si>
-  <si>
-    <t>16436</t>
-  </si>
-  <si>
-    <t>3756</t>
-  </si>
-  <si>
-    <t>11395</t>
-  </si>
-  <si>
-    <t>17250</t>
-  </si>
-  <si>
-    <t>18889</t>
-  </si>
-  <si>
-    <t>18423</t>
-  </si>
-  <si>
-    <t>3252</t>
-  </si>
-  <si>
-    <t>19223</t>
-  </si>
-  <si>
-    <t>6358</t>
-  </si>
-  <si>
-    <t>19651</t>
-  </si>
-  <si>
-    <t>6907</t>
-  </si>
-  <si>
-    <t>18673</t>
-  </si>
-  <si>
-    <t>18455</t>
-  </si>
-  <si>
-    <t>18608</t>
-  </si>
-  <si>
-    <t>5426</t>
-  </si>
-  <si>
-    <t>11270</t>
-  </si>
-  <si>
-    <t>19372</t>
-  </si>
-  <si>
-    <t>973</t>
-  </si>
-  <si>
-    <t>19076</t>
-  </si>
-  <si>
-    <t>12621</t>
-  </si>
-  <si>
-    <t>15907</t>
-  </si>
-  <si>
-    <t>17646</t>
-  </si>
-  <si>
-    <t>9616</t>
-  </si>
-  <si>
-    <t>18602</t>
-  </si>
-  <si>
-    <t>3922</t>
-  </si>
-  <si>
-    <t>17957</t>
-  </si>
-  <si>
-    <t>11029</t>
-  </si>
-  <si>
-    <t>18792</t>
-  </si>
-  <si>
-    <t>18977</t>
-  </si>
-  <si>
-    <t>10695</t>
-  </si>
-  <si>
-    <t>18620</t>
-  </si>
-  <si>
-    <t>7161</t>
-  </si>
-  <si>
-    <t>18477</t>
-  </si>
-  <si>
-    <t>19221</t>
-  </si>
-  <si>
-    <t>19514</t>
-  </si>
-  <si>
-    <t>5046</t>
-  </si>
-  <si>
-    <t>19285</t>
-  </si>
-  <si>
-    <t>19321</t>
-  </si>
-  <si>
-    <t>19566</t>
-  </si>
-  <si>
-    <t>18796</t>
-  </si>
-  <si>
-    <t>12507</t>
-  </si>
-  <si>
-    <t>3889</t>
-  </si>
-  <si>
-    <t>15060</t>
-  </si>
-  <si>
-    <t>5200</t>
-  </si>
-  <si>
-    <t>18537</t>
-  </si>
-  <si>
-    <t>18988</t>
-  </si>
-  <si>
-    <t>18801</t>
-  </si>
-  <si>
-    <t>18968</t>
-  </si>
-  <si>
-    <t>19047</t>
-  </si>
-  <si>
-    <t>7431</t>
-  </si>
-  <si>
-    <t>6751</t>
-  </si>
-  <si>
-    <t>17596</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>15311</t>
-  </si>
-  <si>
-    <t>18835</t>
-  </si>
-  <si>
-    <t>19404</t>
-  </si>
-  <si>
-    <t>18779</t>
-  </si>
-  <si>
-    <t>18878</t>
-  </si>
-  <si>
-    <t>18577</t>
-  </si>
-  <si>
-    <t>18928</t>
-  </si>
-  <si>
-    <t>1383</t>
-  </si>
-  <si>
-    <t>19023</t>
-  </si>
-  <si>
-    <t>15751</t>
-  </si>
-  <si>
-    <t>924</t>
-  </si>
-  <si>
-    <t>12744</t>
-  </si>
-  <si>
-    <t>11873</t>
-  </si>
-  <si>
-    <t>19281</t>
-  </si>
-  <si>
-    <t>18791</t>
-  </si>
-  <si>
-    <t>945</t>
-  </si>
-  <si>
-    <t>922</t>
-  </si>
-  <si>
-    <t>18857</t>
-  </si>
-  <si>
-    <t>17884</t>
-  </si>
-  <si>
-    <t>6659</t>
-  </si>
-  <si>
-    <t>881</t>
-  </si>
-  <si>
-    <t>18883</t>
-  </si>
-  <si>
-    <t>8451</t>
-  </si>
-  <si>
-    <t>19847</t>
-  </si>
-  <si>
-    <t>10084</t>
-  </si>
-  <si>
-    <t>10698</t>
-  </si>
-  <si>
-    <t>19127</t>
-  </si>
-  <si>
-    <t>15934</t>
-  </si>
-  <si>
-    <t>19495</t>
-  </si>
-  <si>
-    <t>13680</t>
-  </si>
-  <si>
-    <t>804</t>
-  </si>
-  <si>
-    <t>14314</t>
-  </si>
-  <si>
-    <t>18584</t>
-  </si>
-  <si>
-    <t>18020</t>
-  </si>
-  <si>
-    <t>8693</t>
-  </si>
-  <si>
-    <t>7335</t>
-  </si>
-  <si>
-    <t>17217</t>
-  </si>
-  <si>
-    <t>960</t>
-  </si>
-  <si>
-    <t>7482</t>
-  </si>
-  <si>
-    <t>14303</t>
-  </si>
-  <si>
-    <t>19197</t>
-  </si>
-  <si>
-    <t>11578</t>
-  </si>
-  <si>
-    <t>16441</t>
-  </si>
-  <si>
-    <t>12882</t>
-  </si>
-  <si>
-    <t>6456</t>
-  </si>
-  <si>
-    <t>14205</t>
-  </si>
-  <si>
-    <t>7963</t>
-  </si>
-  <si>
-    <t>9086</t>
-  </si>
-  <si>
-    <t>13020</t>
-  </si>
-  <si>
-    <t>10069</t>
-  </si>
-  <si>
-    <t>4/25/2016 11:45:00 AM</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>752</t>
-  </si>
-  <si>
-    <t>2457</t>
-  </si>
-  <si>
-    <t>11294</t>
-  </si>
-  <si>
-    <t>12953</t>
-  </si>
-  <si>
-    <t>14452</t>
-  </si>
-  <si>
-    <t>8930</t>
-  </si>
-  <si>
-    <t>12207</t>
-  </si>
-  <si>
-    <t>12470</t>
-  </si>
-  <si>
-    <t>6677</t>
-  </si>
-  <si>
-    <t>9964</t>
-  </si>
-  <si>
-    <t>16984</t>
-  </si>
-  <si>
-    <t>5372</t>
-  </si>
-  <si>
-    <t>18781</t>
-  </si>
-  <si>
-    <t>4894</t>
-  </si>
-  <si>
-    <t>19749</t>
-  </si>
-  <si>
-    <t>6748</t>
-  </si>
-  <si>
-    <t>19357</t>
-  </si>
-  <si>
-    <t>3805</t>
-  </si>
-  <si>
-    <t>805</t>
-  </si>
-  <si>
-    <t>2355</t>
-  </si>
-  <si>
-    <t>16656</t>
-  </si>
-  <si>
-    <t>6754</t>
-  </si>
-  <si>
-    <t>3526</t>
-  </si>
-  <si>
-    <t>2510</t>
-  </si>
-  <si>
-    <t>16227</t>
-  </si>
-  <si>
-    <t>19951</t>
-  </si>
-  <si>
-    <t>2329</t>
-  </si>
-  <si>
-    <t>19572</t>
-  </si>
-  <si>
-    <t>14277</t>
-  </si>
-  <si>
-    <t>5716</t>
-  </si>
-  <si>
-    <t>19163</t>
-  </si>
-  <si>
-    <t>5225</t>
-  </si>
-  <si>
-    <t>16490</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>14427</t>
-  </si>
-  <si>
-    <t>11576</t>
-  </si>
-  <si>
-    <t>8143</t>
-  </si>
-  <si>
-    <t>20077</t>
-  </si>
-  <si>
-    <t>2073</t>
-  </si>
-  <si>
-    <t>19211</t>
-  </si>
-  <si>
-    <t>16553</t>
-  </si>
-  <si>
-    <t>916</t>
-  </si>
-  <si>
-    <t>18844</t>
-  </si>
-  <si>
-    <t>18745</t>
-  </si>
-  <si>
-    <t>18733</t>
-  </si>
-  <si>
-    <t>19351</t>
-  </si>
-  <si>
-    <t>13032</t>
-  </si>
-  <si>
-    <t>709</t>
-  </si>
-  <si>
-    <t>19400</t>
-  </si>
-  <si>
-    <t>15138</t>
-  </si>
-  <si>
-    <t>6021</t>
-  </si>
-  <si>
-    <t>18071</t>
-  </si>
-  <si>
-    <t>18691</t>
-  </si>
-  <si>
-    <t>3006</t>
-  </si>
-  <si>
-    <t>2895</t>
-  </si>
-  <si>
-    <t>18317</t>
-  </si>
-  <si>
-    <t>18371</t>
-  </si>
-  <si>
-    <t>13726</t>
-  </si>
-  <si>
-    <t>18152</t>
-  </si>
-  <si>
-    <t>11429</t>
-  </si>
-  <si>
-    <t>1914</t>
-  </si>
-  <si>
-    <t>7222</t>
-  </si>
-  <si>
-    <t>19897</t>
-  </si>
-  <si>
-    <t>16762</t>
-  </si>
-  <si>
-    <t>9211</t>
-  </si>
-  <si>
-    <t>18919</t>
-  </si>
-  <si>
-    <t>20264</t>
-  </si>
-  <si>
-    <t>19002</t>
-  </si>
-  <si>
-    <t>16572</t>
-  </si>
-  <si>
-    <t>10402</t>
-  </si>
-  <si>
-    <t>19034</t>
-  </si>
-  <si>
-    <t>18888</t>
-  </si>
-  <si>
-    <t>18818</t>
-  </si>
-  <si>
-    <t>18886</t>
-  </si>
-  <si>
-    <t>1924</t>
-  </si>
-  <si>
-    <t>3520</t>
-  </si>
-  <si>
-    <t>19201</t>
-  </si>
-  <si>
-    <t>18803</t>
-  </si>
-  <si>
-    <t>910</t>
-  </si>
-  <si>
-    <t>18851</t>
-  </si>
-  <si>
-    <t>7307</t>
-  </si>
-  <si>
-    <t>12526</t>
-  </si>
-  <si>
-    <t>16463</t>
-  </si>
-  <si>
-    <t>19178</t>
-  </si>
-  <si>
-    <t>20251</t>
-  </si>
-  <si>
-    <t>15867</t>
-  </si>
-  <si>
-    <t>15319</t>
-  </si>
-  <si>
-    <t>18068</t>
-  </si>
-  <si>
-    <t>18841</t>
-  </si>
-  <si>
-    <t>19145</t>
-  </si>
-  <si>
-    <t>18616</t>
-  </si>
-  <si>
-    <t>20472</t>
-  </si>
-  <si>
-    <t>19371</t>
-  </si>
-  <si>
-    <t>18811</t>
-  </si>
-  <si>
-    <t>12555</t>
-  </si>
-  <si>
-    <t>10964</t>
-  </si>
-  <si>
-    <t>19378</t>
-  </si>
-  <si>
-    <t>20345</t>
-  </si>
-  <si>
-    <t>9170</t>
-  </si>
-  <si>
-    <t>896</t>
-  </si>
-  <si>
-    <t>19149</t>
-  </si>
-  <si>
-    <t>18221</t>
-  </si>
-  <si>
-    <t>18442</t>
-  </si>
-  <si>
-    <t>18901</t>
-  </si>
-  <si>
-    <t>17482</t>
-  </si>
-  <si>
-    <t>19194</t>
-  </si>
-  <si>
-    <t>5851</t>
-  </si>
-  <si>
-    <t>2437</t>
-  </si>
-  <si>
-    <t>19869</t>
-  </si>
-  <si>
-    <t>19968</t>
-  </si>
-  <si>
-    <t>14020</t>
-  </si>
-  <si>
-    <t>18942</t>
-  </si>
-  <si>
-    <t>5011</t>
-  </si>
-  <si>
-    <t>2128</t>
-  </si>
-  <si>
-    <t>7999</t>
-  </si>
-  <si>
-    <t>3124</t>
-  </si>
-  <si>
-    <t>10845</t>
-  </si>
-  <si>
-    <t>20266</t>
-  </si>
-  <si>
-    <t>13149</t>
-  </si>
-  <si>
-    <t>19623</t>
-  </si>
-  <si>
-    <t>19174</t>
-  </si>
-  <si>
-    <t>8964</t>
-  </si>
-  <si>
-    <t>18117</t>
-  </si>
-  <si>
-    <t>16796</t>
-  </si>
-  <si>
-    <t>11951</t>
-  </si>
-  <si>
-    <t>17974</t>
-  </si>
-  <si>
-    <t>19236</t>
-  </si>
-  <si>
-    <t>18767</t>
-  </si>
-  <si>
-    <t>3409</t>
-  </si>
-  <si>
-    <t>19821</t>
-  </si>
-  <si>
-    <t>6396</t>
-  </si>
-  <si>
-    <t>18962</t>
-  </si>
-  <si>
-    <t>18863</t>
-  </si>
-  <si>
-    <t>18963</t>
-  </si>
-  <si>
-    <t>5612</t>
-  </si>
-  <si>
-    <t>11635</t>
-  </si>
-  <si>
-    <t>19481</t>
-  </si>
-  <si>
-    <t>932</t>
-  </si>
-  <si>
-    <t>19414</t>
-  </si>
-  <si>
-    <t>13049</t>
-  </si>
-  <si>
-    <t>16584</t>
-  </si>
-  <si>
-    <t>3808</t>
-  </si>
-  <si>
-    <t>18128</t>
-  </si>
-  <si>
-    <t>10299</t>
-  </si>
-  <si>
-    <t>3426</t>
-  </si>
-  <si>
-    <t>18859</t>
-  </si>
-  <si>
-    <t>4083</t>
-  </si>
-  <si>
-    <t>18287</t>
-  </si>
-  <si>
-    <t>11551</t>
-  </si>
-  <si>
-    <t>19018</t>
-  </si>
-  <si>
-    <t>19228</t>
-  </si>
-  <si>
-    <t>11272</t>
-  </si>
-  <si>
-    <t>7390</t>
-  </si>
-  <si>
-    <t>18830</t>
-  </si>
-  <si>
-    <t>19435</t>
-  </si>
-  <si>
-    <t>19016</t>
-  </si>
-  <si>
-    <t>19996</t>
-  </si>
-  <si>
-    <t>5181</t>
-  </si>
-  <si>
-    <t>19771</t>
-  </si>
-  <si>
-    <t>19786</t>
-  </si>
-  <si>
-    <t>20084</t>
-  </si>
-  <si>
-    <t>19142</t>
-  </si>
-  <si>
-    <t>13022</t>
-  </si>
-  <si>
-    <t>3913</t>
-  </si>
-  <si>
-    <t>16015</t>
-  </si>
-  <si>
-    <t>5254</t>
-  </si>
-  <si>
-    <t>19072</t>
-  </si>
-  <si>
-    <t>3155</t>
-  </si>
-  <si>
-    <t>7292</t>
-  </si>
-  <si>
-    <t>19344</t>
-  </si>
-  <si>
-    <t>19401</t>
-  </si>
-  <si>
-    <t>2478</t>
-  </si>
-  <si>
-    <t>19447</t>
-  </si>
-  <si>
-    <t>6940</t>
-  </si>
-  <si>
-    <t>18220</t>
-  </si>
-  <si>
-    <t>927</t>
-  </si>
-  <si>
-    <t>2717</t>
-  </si>
-  <si>
-    <t>15960</t>
-  </si>
-  <si>
-    <t>19391</t>
-  </si>
-  <si>
-    <t>19599</t>
-  </si>
-  <si>
-    <t>19128</t>
-  </si>
-  <si>
-    <t>19206</t>
-  </si>
-  <si>
-    <t>19069</t>
-  </si>
-  <si>
-    <t>19496</t>
-  </si>
-  <si>
-    <t>889</t>
-  </si>
-  <si>
-    <t>12525</t>
-  </si>
-  <si>
-    <t>19598</t>
-  </si>
-  <si>
-    <t>19685</t>
-  </si>
-  <si>
-    <t>899</t>
-  </si>
-  <si>
-    <t>874</t>
-  </si>
-  <si>
-    <t>19171</t>
-  </si>
-  <si>
-    <t>18439</t>
-  </si>
-  <si>
-    <t>7049</t>
-  </si>
-  <si>
-    <t>14193</t>
-  </si>
-  <si>
-    <t>855</t>
-  </si>
-  <si>
-    <t>19424</t>
-  </si>
-  <si>
-    <t>8846</t>
-  </si>
-  <si>
-    <t>20392</t>
-  </si>
-  <si>
-    <t>10589</t>
-  </si>
-  <si>
-    <t>11159</t>
-  </si>
-  <si>
-    <t>19584</t>
-  </si>
-  <si>
-    <t>16561</t>
-  </si>
-  <si>
-    <t>20036</t>
-  </si>
-  <si>
-    <t>766</t>
-  </si>
-  <si>
-    <t>15053</t>
-  </si>
-  <si>
-    <t>19358</t>
-  </si>
-  <si>
-    <t>18897</t>
-  </si>
-  <si>
-    <t>9145</t>
-  </si>
-  <si>
-    <t>7486</t>
-  </si>
-  <si>
-    <t>18005</t>
-  </si>
-  <si>
-    <t>925</t>
-  </si>
-  <si>
-    <t>7763</t>
-  </si>
-  <si>
-    <t>6480</t>
-  </si>
-  <si>
-    <t>19732</t>
-  </si>
-  <si>
-    <t>12085</t>
-  </si>
-  <si>
-    <t>13368</t>
-  </si>
-  <si>
-    <t>6526</t>
-  </si>
-  <si>
-    <t>14611</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>3933</t>
-  </si>
-  <si>
-    <t>8900</t>
-  </si>
-  <si>
-    <t>1097</t>
-  </si>
-  <si>
-    <t>4/25/2016 3:45:00 PM</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>747</t>
-  </si>
-  <si>
-    <t>11790</t>
-  </si>
-  <si>
-    <t>13239</t>
-  </si>
-  <si>
-    <t>14975</t>
-  </si>
-  <si>
-    <t>9071</t>
-  </si>
-  <si>
-    <t>12380</t>
-  </si>
-  <si>
-    <t>12685</t>
-  </si>
-  <si>
-    <t>6709</t>
-  </si>
-  <si>
-    <t>10189</t>
-  </si>
-  <si>
-    <t>15781</t>
-  </si>
-  <si>
-    <t>17478</t>
-  </si>
-  <si>
-    <t>14972</t>
-  </si>
-  <si>
-    <t>19568</t>
-  </si>
-  <si>
-    <t>5016</t>
-  </si>
-  <si>
-    <t>13209</t>
-  </si>
-  <si>
-    <t>20302</t>
-  </si>
-  <si>
-    <t>19838</t>
-  </si>
-  <si>
-    <t>3809</t>
-  </si>
-  <si>
-    <t>782</t>
-  </si>
-  <si>
-    <t>14376</t>
-  </si>
-  <si>
-    <t>17184</t>
-  </si>
-  <si>
-    <t>7070</t>
-  </si>
-  <si>
-    <t>3524</t>
-  </si>
-  <si>
-    <t>17021</t>
-  </si>
-  <si>
-    <t>16660</t>
-  </si>
-  <si>
-    <t>20260</t>
-  </si>
-  <si>
-    <t>2282</t>
-  </si>
-  <si>
-    <t>20109</t>
-  </si>
-  <si>
-    <t>19235</t>
-  </si>
-  <si>
-    <t>14914</t>
-  </si>
-  <si>
-    <t>5947</t>
-  </si>
-  <si>
-    <t>19541</t>
-  </si>
-  <si>
-    <t>5409</t>
-  </si>
-  <si>
-    <t>16831</t>
-  </si>
-  <si>
-    <t>2428</t>
-  </si>
-  <si>
-    <t>19590</t>
-  </si>
-  <si>
-    <t>14986</t>
-  </si>
-  <si>
-    <t>12169</t>
-  </si>
-  <si>
-    <t>8339</t>
-  </si>
-  <si>
-    <t>20359</t>
-  </si>
-  <si>
-    <t>19850</t>
-  </si>
-  <si>
-    <t>17106</t>
-  </si>
-  <si>
-    <t>2779</t>
-  </si>
-  <si>
-    <t>885</t>
-  </si>
-  <si>
-    <t>16080</t>
-  </si>
-  <si>
-    <t>19257</t>
-  </si>
-  <si>
-    <t>18980</t>
-  </si>
-  <si>
-    <t>19408</t>
-  </si>
-  <si>
-    <t>2347</t>
-  </si>
-  <si>
-    <t>13630</t>
-  </si>
-  <si>
-    <t>886</t>
-  </si>
-  <si>
-    <t>3396</t>
-  </si>
-  <si>
-    <t>20040</t>
-  </si>
-  <si>
-    <t>6111</t>
-  </si>
-  <si>
-    <t>18514</t>
-  </si>
-  <si>
-    <t>19082</t>
-  </si>
-  <si>
-    <t>2905</t>
-  </si>
-  <si>
-    <t>7530</t>
-  </si>
-  <si>
-    <t>18545</t>
-  </si>
-  <si>
-    <t>16925</t>
-  </si>
-  <si>
-    <t>19122</t>
-  </si>
-  <si>
-    <t>14458</t>
-  </si>
-  <si>
-    <t>18592</t>
-  </si>
-  <si>
-    <t>11929</t>
-  </si>
-  <si>
-    <t>20327</t>
-  </si>
-  <si>
-    <t>17531</t>
-  </si>
-  <si>
-    <t>9480</t>
-  </si>
-  <si>
-    <t>18876</t>
-  </si>
-  <si>
-    <t>19252</t>
-  </si>
-  <si>
-    <t>20875</t>
-  </si>
-  <si>
-    <t>19443</t>
-  </si>
-  <si>
-    <t>19360</t>
-  </si>
-  <si>
-    <t>19210</t>
-  </si>
-  <si>
-    <t>19112</t>
-  </si>
-  <si>
-    <t>19322</t>
-  </si>
-  <si>
-    <t>19019</t>
-  </si>
-  <si>
-    <t>13770</t>
-  </si>
-  <si>
-    <t>890</t>
-  </si>
-  <si>
-    <t>17721</t>
-  </si>
-  <si>
-    <t>19508</t>
-  </si>
-  <si>
-    <t>19209</t>
-  </si>
-  <si>
-    <t>7566</t>
-  </si>
-  <si>
-    <t>13052</t>
-  </si>
-  <si>
-    <t>19104</t>
-  </si>
-  <si>
-    <t>17067</t>
-  </si>
-  <si>
-    <t>19533</t>
-  </si>
-  <si>
-    <t>20706</t>
-  </si>
-  <si>
-    <t>16996</t>
-  </si>
-  <si>
-    <t>16478</t>
-  </si>
-  <si>
-    <t>16313</t>
-  </si>
-  <si>
-    <t>19273</t>
-  </si>
-  <si>
-    <t>19227</t>
-  </si>
-  <si>
-    <t>18799</t>
-  </si>
-  <si>
-    <t>20714</t>
-  </si>
-  <si>
-    <t>19726</t>
-  </si>
-  <si>
-    <t>19301</t>
-  </si>
-  <si>
-    <t>13172</t>
-  </si>
-  <si>
-    <t>11610</t>
-  </si>
-  <si>
-    <t>19753</t>
-  </si>
-  <si>
-    <t>3851</t>
-  </si>
-  <si>
-    <t>21005</t>
-  </si>
-  <si>
-    <t>6912</t>
-  </si>
-  <si>
-    <t>9639</t>
-  </si>
-  <si>
-    <t>845</t>
-  </si>
-  <si>
-    <t>18467</t>
-  </si>
-  <si>
-    <t>19025</t>
-  </si>
-  <si>
-    <t>18041</t>
-  </si>
-  <si>
-    <t>3621</t>
-  </si>
-  <si>
-    <t>2422</t>
-  </si>
-  <si>
-    <t>20269</t>
-  </si>
-  <si>
-    <t>20701</t>
-  </si>
-  <si>
-    <t>19125</t>
-  </si>
-  <si>
-    <t>5165</t>
-  </si>
-  <si>
-    <t>1889</t>
-  </si>
-  <si>
-    <t>18832</t>
-  </si>
-  <si>
-    <t>11168</t>
-  </si>
-  <si>
-    <t>20434</t>
-  </si>
-  <si>
-    <t>13811</t>
-  </si>
-  <si>
-    <t>19770</t>
-  </si>
-  <si>
-    <t>19768</t>
-  </si>
-  <si>
-    <t>2363</t>
-  </si>
-  <si>
-    <t>9265</t>
-  </si>
-  <si>
-    <t>18605</t>
-  </si>
-  <si>
-    <t>17100</t>
-  </si>
-  <si>
-    <t>3945</t>
-  </si>
-  <si>
-    <t>18523</t>
-  </si>
-  <si>
-    <t>19716</t>
-  </si>
-  <si>
-    <t>18970</t>
-  </si>
-  <si>
-    <t>3218</t>
-  </si>
-  <si>
-    <t>20384</t>
-  </si>
-  <si>
-    <t>6347</t>
-  </si>
-  <si>
-    <t>20518</t>
-  </si>
-  <si>
-    <t>7620</t>
-  </si>
-  <si>
-    <t>19204</t>
-  </si>
-  <si>
-    <t>19389</t>
-  </si>
-  <si>
-    <t>19704</t>
-  </si>
-  <si>
-    <t>19654</t>
-  </si>
-  <si>
-    <t>13709</t>
-  </si>
-  <si>
-    <t>17368</t>
-  </si>
-  <si>
-    <t>19003</t>
-  </si>
-  <si>
-    <t>3539</t>
-  </si>
-  <si>
-    <t>19107</t>
-  </si>
-  <si>
-    <t>18409</t>
-  </si>
-  <si>
-    <t>12028</t>
-  </si>
-  <si>
-    <t>19490</t>
-  </si>
-  <si>
-    <t>11876</t>
-  </si>
-  <si>
-    <t>19346</t>
-  </si>
-  <si>
-    <t>7650</t>
-  </si>
-  <si>
-    <t>19214</t>
-  </si>
-  <si>
-    <t>19683</t>
-  </si>
-  <si>
-    <t>20437</t>
-  </si>
-  <si>
-    <t>5350</t>
-  </si>
-  <si>
-    <t>19908</t>
-  </si>
-  <si>
-    <t>20050</t>
-  </si>
-  <si>
-    <t>20421</t>
-  </si>
-  <si>
-    <t>13721</t>
-  </si>
-  <si>
-    <t>3934</t>
-  </si>
-  <si>
-    <t>5319</t>
-  </si>
-  <si>
-    <t>19606</t>
-  </si>
-  <si>
-    <t>3153</t>
-  </si>
-  <si>
-    <t>7637</t>
-  </si>
-  <si>
-    <t>19581</t>
-  </si>
-  <si>
-    <t>19828</t>
-  </si>
-  <si>
-    <t>19628</t>
-  </si>
-  <si>
-    <t>7888</t>
-  </si>
-  <si>
-    <t>7140</t>
-  </si>
-  <si>
-    <t>18800</t>
-  </si>
-  <si>
-    <t>16489</t>
-  </si>
-  <si>
-    <t>19878</t>
-  </si>
-  <si>
-    <t>19872</t>
-  </si>
-  <si>
-    <t>19271</t>
-  </si>
-  <si>
-    <t>17498</t>
-  </si>
-  <si>
-    <t>19306</t>
-  </si>
-  <si>
-    <t>19562</t>
-  </si>
-  <si>
-    <t>19339</t>
-  </si>
-  <si>
-    <t>1328</t>
-  </si>
-  <si>
-    <t>17525</t>
-  </si>
-  <si>
-    <t>16657</t>
-  </si>
-  <si>
-    <t>888</t>
-  </si>
-  <si>
-    <t>13899</t>
-  </si>
-  <si>
-    <t>13231</t>
-  </si>
-  <si>
-    <t>19887</t>
-  </si>
-  <si>
-    <t>20188</t>
-  </si>
-  <si>
-    <t>846</t>
-  </si>
-  <si>
-    <t>19396</t>
-  </si>
-  <si>
-    <t>7357</t>
-  </si>
-  <si>
-    <t>14898</t>
-  </si>
-  <si>
-    <t>838</t>
-  </si>
-  <si>
-    <t>3465</t>
-  </si>
-  <si>
-    <t>19916</t>
-  </si>
-  <si>
-    <t>9213</t>
-  </si>
-  <si>
-    <t>20840</t>
-  </si>
-  <si>
-    <t>11709</t>
-  </si>
-  <si>
-    <t>19979</t>
-  </si>
-  <si>
-    <t>17127</t>
-  </si>
-  <si>
-    <t>20587</t>
-  </si>
-  <si>
-    <t>15005</t>
-  </si>
-  <si>
-    <t>745</t>
-  </si>
-  <si>
-    <t>15857</t>
-  </si>
-  <si>
-    <t>19980</t>
-  </si>
-  <si>
-    <t>9559</t>
-  </si>
-  <si>
-    <t>7621</t>
-  </si>
-  <si>
-    <t>18701</t>
-  </si>
-  <si>
-    <t>864</t>
-  </si>
-  <si>
-    <t>7994</t>
-  </si>
-  <si>
-    <t>15691</t>
-  </si>
-  <si>
-    <t>20340</t>
-  </si>
-  <si>
-    <t>12712</t>
-  </si>
-  <si>
-    <t>13798</t>
-  </si>
-  <si>
-    <t>6661</t>
-  </si>
-  <si>
-    <t>14873</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>7590</t>
-  </si>
-  <si>
-    <t>8734</t>
-  </si>
-  <si>
-    <t>13325</t>
-  </si>
-  <si>
-    <t>1032</t>
-  </si>
-  <si>
-    <t>9357</t>
-  </si>
-  <si>
-    <t>9721</t>
   </si>
 </sst>
 </file>
@@ -17946,7 +13929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:KX35"/>
+  <dimension ref="A1:KX29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:310">
@@ -36632,5598 +32615,6 @@
         <v>4527</v>
       </c>
     </row>
-    <row r="30" spans="1:310">
-      <c r="A30" t="s">
-        <v>4528</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4529</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4530</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1525</v>
-      </c>
-      <c r="E30" t="s">
-        <v>4531</v>
-      </c>
-      <c r="F30" t="s">
-        <v>4532</v>
-      </c>
-      <c r="G30" t="s">
-        <v>4533</v>
-      </c>
-      <c r="H30" t="s">
-        <v>4534</v>
-      </c>
-      <c r="I30" t="s">
-        <v>4535</v>
-      </c>
-      <c r="J30" t="s">
-        <v>3184</v>
-      </c>
-      <c r="K30" t="s">
-        <v>2498</v>
-      </c>
-      <c r="L30" t="s">
-        <v>4536</v>
-      </c>
-      <c r="M30" t="s">
-        <v>3132</v>
-      </c>
-      <c r="N30" t="s">
-        <v>4537</v>
-      </c>
-      <c r="O30" t="s">
-        <v>4538</v>
-      </c>
-      <c r="P30" t="s">
-        <v>4539</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>4540</v>
-      </c>
-      <c r="R30" t="s">
-        <v>3719</v>
-      </c>
-      <c r="S30" t="s">
-        <v>4541</v>
-      </c>
-      <c r="T30" t="s">
-        <v>659</v>
-      </c>
-      <c r="U30" t="s">
-        <v>4542</v>
-      </c>
-      <c r="V30" t="s">
-        <v>4543</v>
-      </c>
-      <c r="W30" t="s">
-        <v>4544</v>
-      </c>
-      <c r="X30" t="s">
-        <v>377</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>4545</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>4546</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>4547</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>4548</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>898</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>4549</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>3925</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>4550</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>4551</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>449</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>4552</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>1966</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>4553</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>4554</v>
-      </c>
-      <c r="AM30" t="s">
-        <v>2399</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>4555</v>
-      </c>
-      <c r="AO30" t="s">
-        <v>4556</v>
-      </c>
-      <c r="AP30" t="s">
-        <v>4557</v>
-      </c>
-      <c r="AQ30" t="s">
-        <v>4558</v>
-      </c>
-      <c r="AR30" t="s">
-        <v>1111</v>
-      </c>
-      <c r="AS30" t="s">
-        <v>2836</v>
-      </c>
-      <c r="AT30" t="s">
-        <v>4559</v>
-      </c>
-      <c r="AU30" t="s">
-        <v>4560</v>
-      </c>
-      <c r="AV30" t="s">
-        <v>4561</v>
-      </c>
-      <c r="AW30" t="s">
-        <v>3307</v>
-      </c>
-      <c r="AX30" t="s">
-        <v>565</v>
-      </c>
-      <c r="AY30" t="s">
-        <v>4562</v>
-      </c>
-      <c r="AZ30" t="s">
-        <v>4563</v>
-      </c>
-      <c r="BA30" t="s">
-        <v>3764</v>
-      </c>
-      <c r="BB30" t="s">
-        <v>4564</v>
-      </c>
-      <c r="BC30" t="s">
-        <v>4565</v>
-      </c>
-      <c r="BD30" t="s">
-        <v>645</v>
-      </c>
-      <c r="BE30" t="s">
-        <v>4566</v>
-      </c>
-      <c r="BF30" t="s">
-        <v>3478</v>
-      </c>
-      <c r="BG30" t="s">
-        <v>4567</v>
-      </c>
-      <c r="BH30" t="s">
-        <v>4568</v>
-      </c>
-      <c r="BI30" t="s">
-        <v>4569</v>
-      </c>
-      <c r="BJ30" t="s">
-        <v>4570</v>
-      </c>
-      <c r="BK30" t="s">
-        <v>551</v>
-      </c>
-      <c r="BL30" t="s">
-        <v>4571</v>
-      </c>
-      <c r="BM30" t="s">
-        <v>4572</v>
-      </c>
-      <c r="BN30" t="s">
-        <v>4573</v>
-      </c>
-      <c r="BO30" t="s">
-        <v>798</v>
-      </c>
-      <c r="BP30" t="s">
-        <v>4574</v>
-      </c>
-      <c r="BQ30" t="s">
-        <v>4575</v>
-      </c>
-      <c r="BR30" t="s">
-        <v>1725</v>
-      </c>
-      <c r="BS30" t="s">
-        <v>4576</v>
-      </c>
-      <c r="BT30" t="s">
-        <v>4577</v>
-      </c>
-      <c r="BU30" t="s">
-        <v>4578</v>
-      </c>
-      <c r="BV30" t="s">
-        <v>4579</v>
-      </c>
-      <c r="BW30" t="s">
-        <v>4580</v>
-      </c>
-      <c r="BX30" t="s">
-        <v>3561</v>
-      </c>
-      <c r="BY30" t="s">
-        <v>4581</v>
-      </c>
-      <c r="BZ30" t="s">
-        <v>1901</v>
-      </c>
-      <c r="CA30" t="s">
-        <v>4582</v>
-      </c>
-      <c r="CB30" t="s">
-        <v>4583</v>
-      </c>
-      <c r="CC30" t="s">
-        <v>4584</v>
-      </c>
-      <c r="CD30" t="s">
-        <v>4585</v>
-      </c>
-      <c r="CE30" t="s">
-        <v>4586</v>
-      </c>
-      <c r="CF30" t="s">
-        <v>4587</v>
-      </c>
-      <c r="CG30" t="s">
-        <v>2535</v>
-      </c>
-      <c r="CH30" t="s">
-        <v>4360</v>
-      </c>
-      <c r="CI30" t="s">
-        <v>441</v>
-      </c>
-      <c r="CJ30" t="s">
-        <v>2424</v>
-      </c>
-      <c r="CK30" t="s">
-        <v>4588</v>
-      </c>
-      <c r="CL30" t="s">
-        <v>4589</v>
-      </c>
-      <c r="CM30" t="s">
-        <v>4590</v>
-      </c>
-      <c r="CN30" t="s">
-        <v>4186</v>
-      </c>
-      <c r="CO30" t="s">
-        <v>2431</v>
-      </c>
-      <c r="CP30" t="s">
-        <v>4591</v>
-      </c>
-      <c r="CQ30" t="s">
-        <v>4592</v>
-      </c>
-      <c r="CR30" t="s">
-        <v>1052</v>
-      </c>
-      <c r="CS30" t="s">
-        <v>4593</v>
-      </c>
-      <c r="CT30" t="s">
-        <v>4594</v>
-      </c>
-      <c r="CU30" t="s">
-        <v>4595</v>
-      </c>
-      <c r="CV30" t="s">
-        <v>4596</v>
-      </c>
-      <c r="CW30" t="s">
-        <v>4597</v>
-      </c>
-      <c r="CX30" t="s">
-        <v>4464</v>
-      </c>
-      <c r="CY30" t="s">
-        <v>4598</v>
-      </c>
-      <c r="CZ30" t="s">
-        <v>4599</v>
-      </c>
-      <c r="DA30" t="s">
-        <v>4600</v>
-      </c>
-      <c r="DB30" t="s">
-        <v>4601</v>
-      </c>
-      <c r="DC30" t="s">
-        <v>835</v>
-      </c>
-      <c r="DD30" t="s">
-        <v>4602</v>
-      </c>
-      <c r="DE30" t="s">
-        <v>4603</v>
-      </c>
-      <c r="DF30" t="s">
-        <v>4604</v>
-      </c>
-      <c r="DG30" t="s">
-        <v>4605</v>
-      </c>
-      <c r="DH30" t="s">
-        <v>4606</v>
-      </c>
-      <c r="DI30" t="s">
-        <v>4607</v>
-      </c>
-      <c r="DJ30" t="s">
-        <v>4608</v>
-      </c>
-      <c r="DK30" t="s">
-        <v>4609</v>
-      </c>
-      <c r="DL30" t="s">
-        <v>4610</v>
-      </c>
-      <c r="DM30" t="s">
-        <v>4611</v>
-      </c>
-      <c r="DN30" t="s">
-        <v>4612</v>
-      </c>
-      <c r="DO30" t="s">
-        <v>4613</v>
-      </c>
-      <c r="DP30" t="s">
-        <v>4614</v>
-      </c>
-      <c r="DQ30" t="s">
-        <v>4615</v>
-      </c>
-      <c r="DR30" t="s">
-        <v>3322</v>
-      </c>
-      <c r="DS30" t="s">
-        <v>3293</v>
-      </c>
-      <c r="DT30" t="s">
-        <v>4616</v>
-      </c>
-      <c r="DU30" t="s">
-        <v>4617</v>
-      </c>
-      <c r="DV30" t="s">
-        <v>4618</v>
-      </c>
-      <c r="DW30" t="s">
-        <v>372</v>
-      </c>
-      <c r="DX30" t="s">
-        <v>4619</v>
-      </c>
-      <c r="DY30" t="s">
-        <v>4620</v>
-      </c>
-      <c r="DZ30" t="s">
-        <v>3437</v>
-      </c>
-      <c r="EA30" t="s">
-        <v>4621</v>
-      </c>
-      <c r="EB30" t="s">
-        <v>4622</v>
-      </c>
-      <c r="EC30" t="s">
-        <v>4623</v>
-      </c>
-      <c r="ED30" t="s">
-        <v>4624</v>
-      </c>
-      <c r="EE30" t="s">
-        <v>4592</v>
-      </c>
-      <c r="EF30" t="s">
-        <v>4625</v>
-      </c>
-      <c r="EG30" t="s">
-        <v>4626</v>
-      </c>
-      <c r="EH30" t="s">
-        <v>4627</v>
-      </c>
-      <c r="EI30" t="s">
-        <v>4628</v>
-      </c>
-      <c r="EJ30" t="s">
-        <v>4094</v>
-      </c>
-      <c r="EK30" t="s">
-        <v>4629</v>
-      </c>
-      <c r="EL30" t="s">
-        <v>4630</v>
-      </c>
-      <c r="EM30" t="s">
-        <v>4631</v>
-      </c>
-      <c r="EN30" t="s">
-        <v>4632</v>
-      </c>
-      <c r="EO30" t="s">
-        <v>4633</v>
-      </c>
-      <c r="EP30" t="s">
-        <v>4634</v>
-      </c>
-      <c r="EQ30" t="s">
-        <v>4635</v>
-      </c>
-      <c r="ER30" t="s">
-        <v>4636</v>
-      </c>
-      <c r="ES30" t="s">
-        <v>4637</v>
-      </c>
-      <c r="ET30" t="s">
-        <v>4638</v>
-      </c>
-      <c r="EU30" t="s">
-        <v>1631</v>
-      </c>
-      <c r="EV30" t="s">
-        <v>4173</v>
-      </c>
-      <c r="EW30" t="s">
-        <v>2980</v>
-      </c>
-      <c r="EX30" t="s">
-        <v>4639</v>
-      </c>
-      <c r="EY30" t="s">
-        <v>4640</v>
-      </c>
-      <c r="EZ30" t="s">
-        <v>4641</v>
-      </c>
-      <c r="FA30" t="s">
-        <v>4169</v>
-      </c>
-      <c r="FB30" t="s">
-        <v>1833</v>
-      </c>
-      <c r="FC30" t="s">
-        <v>4642</v>
-      </c>
-      <c r="FD30" t="s">
-        <v>4643</v>
-      </c>
-      <c r="FE30" t="s">
-        <v>4644</v>
-      </c>
-      <c r="FF30" t="s">
-        <v>4645</v>
-      </c>
-      <c r="FG30" t="s">
-        <v>1271</v>
-      </c>
-      <c r="FH30" t="s">
-        <v>4646</v>
-      </c>
-      <c r="FI30" t="s">
-        <v>4647</v>
-      </c>
-      <c r="FJ30" t="s">
-        <v>2849</v>
-      </c>
-      <c r="FK30" t="s">
-        <v>4648</v>
-      </c>
-      <c r="FL30" t="s">
-        <v>4649</v>
-      </c>
-      <c r="FM30" t="s">
-        <v>1462</v>
-      </c>
-      <c r="FN30" t="s">
-        <v>1178</v>
-      </c>
-      <c r="FO30" t="s">
-        <v>2898</v>
-      </c>
-      <c r="FP30" t="s">
-        <v>2245</v>
-      </c>
-      <c r="FQ30" t="s">
-        <v>4650</v>
-      </c>
-      <c r="FR30" t="s">
-        <v>801</v>
-      </c>
-      <c r="FS30" t="s">
-        <v>4651</v>
-      </c>
-      <c r="FT30" t="s">
-        <v>4652</v>
-      </c>
-      <c r="FU30" t="s">
-        <v>4653</v>
-      </c>
-      <c r="FV30" t="s">
-        <v>4654</v>
-      </c>
-      <c r="FW30" t="s">
-        <v>4655</v>
-      </c>
-      <c r="FX30" t="s">
-        <v>4656</v>
-      </c>
-      <c r="FY30" t="s">
-        <v>4657</v>
-      </c>
-      <c r="FZ30" t="s">
-        <v>1301</v>
-      </c>
-      <c r="GA30" t="s">
-        <v>4658</v>
-      </c>
-      <c r="GB30" t="s">
-        <v>2070</v>
-      </c>
-      <c r="GC30" t="s">
-        <v>4659</v>
-      </c>
-      <c r="GD30" t="s">
-        <v>4660</v>
-      </c>
-      <c r="GE30" t="s">
-        <v>4661</v>
-      </c>
-      <c r="GF30" t="s">
-        <v>4662</v>
-      </c>
-      <c r="GG30" t="s">
-        <v>4663</v>
-      </c>
-      <c r="GH30" t="s">
-        <v>2232</v>
-      </c>
-      <c r="GI30" t="s">
-        <v>2836</v>
-      </c>
-      <c r="GJ30" t="s">
-        <v>4664</v>
-      </c>
-      <c r="GK30" t="s">
-        <v>4665</v>
-      </c>
-      <c r="GL30" t="s">
-        <v>4666</v>
-      </c>
-      <c r="GM30" t="s">
-        <v>4667</v>
-      </c>
-      <c r="GN30" t="s">
-        <v>653</v>
-      </c>
-      <c r="GO30" t="s">
-        <v>4668</v>
-      </c>
-      <c r="GP30" t="s">
-        <v>4669</v>
-      </c>
-      <c r="GQ30" t="s">
-        <v>4670</v>
-      </c>
-      <c r="GR30" t="s">
-        <v>4671</v>
-      </c>
-      <c r="GS30" t="s">
-        <v>4672</v>
-      </c>
-      <c r="GT30" t="s">
-        <v>4673</v>
-      </c>
-      <c r="GU30" t="s">
-        <v>4674</v>
-      </c>
-      <c r="GV30" t="s">
-        <v>4675</v>
-      </c>
-      <c r="GW30" t="s">
-        <v>4676</v>
-      </c>
-      <c r="GX30" t="s">
-        <v>4677</v>
-      </c>
-      <c r="GY30" t="s">
-        <v>4678</v>
-      </c>
-      <c r="GZ30" t="s">
-        <v>4679</v>
-      </c>
-      <c r="HA30" t="s">
-        <v>4680</v>
-      </c>
-      <c r="HB30" t="s">
-        <v>4681</v>
-      </c>
-      <c r="HC30" t="s">
-        <v>1669</v>
-      </c>
-      <c r="HD30" t="s">
-        <v>1382</v>
-      </c>
-      <c r="HE30" t="s">
-        <v>4682</v>
-      </c>
-      <c r="HF30" t="s">
-        <v>4683</v>
-      </c>
-      <c r="HG30" t="s">
-        <v>4684</v>
-      </c>
-      <c r="HH30" t="s">
-        <v>4685</v>
-      </c>
-      <c r="HI30" t="s">
-        <v>4686</v>
-      </c>
-      <c r="HJ30" t="s">
-        <v>3300</v>
-      </c>
-      <c r="HK30" t="s">
-        <v>4687</v>
-      </c>
-      <c r="HL30" t="s">
-        <v>4688</v>
-      </c>
-      <c r="HM30" t="s">
-        <v>4689</v>
-      </c>
-      <c r="HN30" t="s">
-        <v>4690</v>
-      </c>
-      <c r="HO30" t="s">
-        <v>4691</v>
-      </c>
-      <c r="HP30" t="s">
-        <v>4692</v>
-      </c>
-      <c r="HQ30" t="s">
-        <v>4693</v>
-      </c>
-      <c r="HR30" t="s">
-        <v>4694</v>
-      </c>
-      <c r="HS30" t="s">
-        <v>4695</v>
-      </c>
-      <c r="HT30" t="s">
-        <v>4696</v>
-      </c>
-      <c r="HU30" t="s">
-        <v>967</v>
-      </c>
-      <c r="HV30" t="s">
-        <v>4697</v>
-      </c>
-      <c r="HW30" t="s">
-        <v>4698</v>
-      </c>
-      <c r="HX30" t="s">
-        <v>4699</v>
-      </c>
-      <c r="HY30" t="s">
-        <v>4700</v>
-      </c>
-      <c r="HZ30" t="s">
-        <v>553</v>
-      </c>
-      <c r="IA30" t="s">
-        <v>1026</v>
-      </c>
-      <c r="IB30" t="s">
-        <v>4701</v>
-      </c>
-      <c r="IC30" t="s">
-        <v>4702</v>
-      </c>
-      <c r="ID30" t="s">
-        <v>4703</v>
-      </c>
-      <c r="IE30" t="s">
-        <v>4704</v>
-      </c>
-      <c r="IF30" t="s">
-        <v>4705</v>
-      </c>
-      <c r="IG30" t="s">
-        <v>4632</v>
-      </c>
-      <c r="IH30" t="s">
-        <v>4706</v>
-      </c>
-      <c r="II30" t="s">
-        <v>3438</v>
-      </c>
-      <c r="IJ30" t="s">
-        <v>4707</v>
-      </c>
-      <c r="IK30" t="s">
-        <v>4708</v>
-      </c>
-      <c r="IL30" t="s">
-        <v>4709</v>
-      </c>
-      <c r="IM30" t="s">
-        <v>4710</v>
-      </c>
-      <c r="IN30" t="s">
-        <v>4711</v>
-      </c>
-      <c r="IO30" t="s">
-        <v>4712</v>
-      </c>
-      <c r="IP30" t="s">
-        <v>4713</v>
-      </c>
-      <c r="IQ30" t="s">
-        <v>528</v>
-      </c>
-      <c r="IR30" t="s">
-        <v>4714</v>
-      </c>
-      <c r="IS30" t="s">
-        <v>616</v>
-      </c>
-      <c r="IT30" t="s">
-        <v>440</v>
-      </c>
-      <c r="IU30" t="s">
-        <v>4715</v>
-      </c>
-      <c r="IV30" t="s">
-        <v>725</v>
-      </c>
-      <c r="IW30" t="s">
-        <v>4716</v>
-      </c>
-      <c r="IX30" t="s">
-        <v>4717</v>
-      </c>
-      <c r="IY30" t="s">
-        <v>714</v>
-      </c>
-      <c r="IZ30" t="s">
-        <v>4718</v>
-      </c>
-      <c r="JA30" t="s">
-        <v>4719</v>
-      </c>
-      <c r="JB30" t="s">
-        <v>4720</v>
-      </c>
-      <c r="JC30" t="s">
-        <v>4721</v>
-      </c>
-      <c r="JD30" t="s">
-        <v>4722</v>
-      </c>
-      <c r="JE30" t="s">
-        <v>4717</v>
-      </c>
-      <c r="JF30" t="s">
-        <v>4723</v>
-      </c>
-      <c r="JG30" t="s">
-        <v>450</v>
-      </c>
-      <c r="JH30" t="s">
-        <v>4724</v>
-      </c>
-      <c r="JI30" t="s">
-        <v>1917</v>
-      </c>
-      <c r="JJ30" t="s">
-        <v>4725</v>
-      </c>
-      <c r="JK30" t="s">
-        <v>4726</v>
-      </c>
-      <c r="JL30" t="s">
-        <v>2237</v>
-      </c>
-      <c r="JM30" t="s">
-        <v>4727</v>
-      </c>
-      <c r="JN30" t="s">
-        <v>4728</v>
-      </c>
-      <c r="JO30" t="s">
-        <v>4729</v>
-      </c>
-      <c r="JP30" t="s">
-        <v>4730</v>
-      </c>
-      <c r="JQ30" t="s">
-        <v>4731</v>
-      </c>
-      <c r="JR30" t="s">
-        <v>2448</v>
-      </c>
-      <c r="JS30" t="s">
-        <v>4732</v>
-      </c>
-      <c r="JT30" t="s">
-        <v>4733</v>
-      </c>
-      <c r="JU30" t="s">
-        <v>4734</v>
-      </c>
-      <c r="JV30" t="s">
-        <v>2776</v>
-      </c>
-      <c r="JW30" t="s">
-        <v>4735</v>
-      </c>
-      <c r="JX30" t="s">
-        <v>4736</v>
-      </c>
-      <c r="JY30" t="s">
-        <v>4737</v>
-      </c>
-      <c r="JZ30" t="s">
-        <v>4317</v>
-      </c>
-      <c r="KA30" t="s">
-        <v>4738</v>
-      </c>
-      <c r="KB30" t="s">
-        <v>4739</v>
-      </c>
-      <c r="KC30" t="s">
-        <v>4740</v>
-      </c>
-      <c r="KD30" t="s">
-        <v>4741</v>
-      </c>
-      <c r="KE30" t="s">
-        <v>4742</v>
-      </c>
-      <c r="KF30" t="s">
-        <v>4743</v>
-      </c>
-      <c r="KG30" t="s">
-        <v>4744</v>
-      </c>
-      <c r="KH30" t="s">
-        <v>4745</v>
-      </c>
-      <c r="KI30" t="s">
-        <v>4746</v>
-      </c>
-      <c r="KJ30" t="s">
-        <v>3654</v>
-      </c>
-      <c r="KK30" t="s">
-        <v>4747</v>
-      </c>
-      <c r="KL30" t="s">
-        <v>3714</v>
-      </c>
-      <c r="KM30" t="s">
-        <v>4748</v>
-      </c>
-      <c r="KN30" t="s">
-        <v>4749</v>
-      </c>
-      <c r="KO30" t="s">
-        <v>3148</v>
-      </c>
-      <c r="KP30" t="s">
-        <v>2295</v>
-      </c>
-      <c r="KQ30" t="s">
-        <v>4750</v>
-      </c>
-      <c r="KR30" t="s">
-        <v>4751</v>
-      </c>
-      <c r="KS30" t="s">
-        <v>4752</v>
-      </c>
-      <c r="KT30" t="s">
-        <v>4753</v>
-      </c>
-      <c r="KU30" t="s">
-        <v>523</v>
-      </c>
-      <c r="KV30" t="s">
-        <v>4754</v>
-      </c>
-      <c r="KW30" t="s">
-        <v>1620</v>
-      </c>
-      <c r="KX30" t="s">
-        <v>4755</v>
-      </c>
-    </row>
-    <row r="31" spans="1:310">
-      <c r="A31" t="s">
-        <v>4756</v>
-      </c>
-      <c r="B31" t="s">
-        <v>4757</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4758</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1852</v>
-      </c>
-      <c r="E31" t="s">
-        <v>4759</v>
-      </c>
-      <c r="F31" t="s">
-        <v>4760</v>
-      </c>
-      <c r="G31" t="s">
-        <v>4761</v>
-      </c>
-      <c r="H31" t="s">
-        <v>4762</v>
-      </c>
-      <c r="I31" t="s">
-        <v>4763</v>
-      </c>
-      <c r="J31" t="s">
-        <v>4764</v>
-      </c>
-      <c r="K31" t="s">
-        <v>4765</v>
-      </c>
-      <c r="L31" t="s">
-        <v>4766</v>
-      </c>
-      <c r="M31" t="s">
-        <v>4767</v>
-      </c>
-      <c r="N31" t="s">
-        <v>4768</v>
-      </c>
-      <c r="O31" t="s">
-        <v>3454</v>
-      </c>
-      <c r="P31" t="s">
-        <v>4543</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>2516</v>
-      </c>
-      <c r="R31" t="s">
-        <v>3966</v>
-      </c>
-      <c r="S31" t="s">
-        <v>4769</v>
-      </c>
-      <c r="T31" t="s">
-        <v>665</v>
-      </c>
-      <c r="U31" t="s">
-        <v>4770</v>
-      </c>
-      <c r="V31" t="s">
-        <v>3084</v>
-      </c>
-      <c r="W31" t="s">
-        <v>4771</v>
-      </c>
-      <c r="X31" t="s">
-        <v>600</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>4772</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>4773</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>1570</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>4774</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>4775</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>3281</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>3484</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>4776</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>4218</v>
-      </c>
-      <c r="AH31" t="s">
-        <v>544</v>
-      </c>
-      <c r="AI31" t="s">
-        <v>4777</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>1001</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>4778</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>4779</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>701</v>
-      </c>
-      <c r="AN31" t="s">
-        <v>1853</v>
-      </c>
-      <c r="AO31" t="s">
-        <v>4780</v>
-      </c>
-      <c r="AP31" t="s">
-        <v>4781</v>
-      </c>
-      <c r="AQ31" t="s">
-        <v>4782</v>
-      </c>
-      <c r="AR31" t="s">
-        <v>1122</v>
-      </c>
-      <c r="AS31" t="s">
-        <v>3471</v>
-      </c>
-      <c r="AT31" t="s">
-        <v>4783</v>
-      </c>
-      <c r="AU31" t="s">
-        <v>1685</v>
-      </c>
-      <c r="AV31" t="s">
-        <v>4784</v>
-      </c>
-      <c r="AW31" t="s">
-        <v>885</v>
-      </c>
-      <c r="AX31" t="s">
-        <v>3241</v>
-      </c>
-      <c r="AY31" t="s">
-        <v>4785</v>
-      </c>
-      <c r="AZ31" t="s">
-        <v>4786</v>
-      </c>
-      <c r="BA31" t="s">
-        <v>4170</v>
-      </c>
-      <c r="BB31" t="s">
-        <v>3398</v>
-      </c>
-      <c r="BC31" t="s">
-        <v>4787</v>
-      </c>
-      <c r="BD31" t="s">
-        <v>968</v>
-      </c>
-      <c r="BE31" t="s">
-        <v>4788</v>
-      </c>
-      <c r="BF31" t="s">
-        <v>4789</v>
-      </c>
-      <c r="BG31" t="s">
-        <v>1100</v>
-      </c>
-      <c r="BH31" t="s">
-        <v>4790</v>
-      </c>
-      <c r="BI31" t="s">
-        <v>4791</v>
-      </c>
-      <c r="BJ31" t="s">
-        <v>4792</v>
-      </c>
-      <c r="BK31" t="s">
-        <v>653</v>
-      </c>
-      <c r="BL31" t="s">
-        <v>4793</v>
-      </c>
-      <c r="BM31" t="s">
-        <v>4794</v>
-      </c>
-      <c r="BN31" t="s">
-        <v>4795</v>
-      </c>
-      <c r="BO31" t="s">
-        <v>841</v>
-      </c>
-      <c r="BP31" t="s">
-        <v>4796</v>
-      </c>
-      <c r="BQ31" t="s">
-        <v>4797</v>
-      </c>
-      <c r="BR31" t="s">
-        <v>2195</v>
-      </c>
-      <c r="BS31" t="s">
-        <v>4708</v>
-      </c>
-      <c r="BT31" t="s">
-        <v>4798</v>
-      </c>
-      <c r="BU31" t="s">
-        <v>2989</v>
-      </c>
-      <c r="BV31" t="s">
-        <v>4497</v>
-      </c>
-      <c r="BW31" t="s">
-        <v>4799</v>
-      </c>
-      <c r="BX31" t="s">
-        <v>1704</v>
-      </c>
-      <c r="BY31" t="s">
-        <v>4800</v>
-      </c>
-      <c r="BZ31" t="s">
-        <v>4414</v>
-      </c>
-      <c r="CA31" t="s">
-        <v>1456</v>
-      </c>
-      <c r="CB31" t="s">
-        <v>4732</v>
-      </c>
-      <c r="CC31" t="s">
-        <v>3574</v>
-      </c>
-      <c r="CD31" t="s">
-        <v>4801</v>
-      </c>
-      <c r="CE31" t="s">
-        <v>4802</v>
-      </c>
-      <c r="CF31" t="s">
-        <v>4803</v>
-      </c>
-      <c r="CG31" t="s">
-        <v>4804</v>
-      </c>
-      <c r="CH31" t="s">
-        <v>2439</v>
-      </c>
-      <c r="CI31" t="s">
-        <v>440</v>
-      </c>
-      <c r="CJ31" t="s">
-        <v>1200</v>
-      </c>
-      <c r="CK31" t="s">
-        <v>2293</v>
-      </c>
-      <c r="CL31" t="s">
-        <v>4805</v>
-      </c>
-      <c r="CM31" t="s">
-        <v>4806</v>
-      </c>
-      <c r="CN31" t="s">
-        <v>4807</v>
-      </c>
-      <c r="CO31" t="s">
-        <v>1057</v>
-      </c>
-      <c r="CP31" t="s">
-        <v>4194</v>
-      </c>
-      <c r="CQ31" t="s">
-        <v>4808</v>
-      </c>
-      <c r="CR31" t="s">
-        <v>4809</v>
-      </c>
-      <c r="CS31" t="s">
-        <v>4810</v>
-      </c>
-      <c r="CT31" t="s">
-        <v>4811</v>
-      </c>
-      <c r="CU31" t="s">
-        <v>4812</v>
-      </c>
-      <c r="CV31" t="s">
-        <v>4813</v>
-      </c>
-      <c r="CW31" t="s">
-        <v>4814</v>
-      </c>
-      <c r="CX31" t="s">
-        <v>4815</v>
-      </c>
-      <c r="CY31" t="s">
-        <v>4816</v>
-      </c>
-      <c r="CZ31" t="s">
-        <v>4636</v>
-      </c>
-      <c r="DA31" t="s">
-        <v>4817</v>
-      </c>
-      <c r="DB31" t="s">
-        <v>3435</v>
-      </c>
-      <c r="DC31" t="s">
-        <v>4818</v>
-      </c>
-      <c r="DD31" t="s">
-        <v>4819</v>
-      </c>
-      <c r="DE31" t="s">
-        <v>4820</v>
-      </c>
-      <c r="DF31" t="s">
-        <v>4821</v>
-      </c>
-      <c r="DG31" t="s">
-        <v>4822</v>
-      </c>
-      <c r="DH31" t="s">
-        <v>1390</v>
-      </c>
-      <c r="DI31" t="s">
-        <v>4823</v>
-      </c>
-      <c r="DJ31" t="s">
-        <v>557</v>
-      </c>
-      <c r="DK31" t="s">
-        <v>4824</v>
-      </c>
-      <c r="DL31" t="s">
-        <v>4825</v>
-      </c>
-      <c r="DM31" t="s">
-        <v>1248</v>
-      </c>
-      <c r="DN31" t="s">
-        <v>4826</v>
-      </c>
-      <c r="DO31" t="s">
-        <v>4827</v>
-      </c>
-      <c r="DP31" t="s">
-        <v>4828</v>
-      </c>
-      <c r="DQ31" t="s">
-        <v>4829</v>
-      </c>
-      <c r="DR31" t="s">
-        <v>4830</v>
-      </c>
-      <c r="DS31" t="s">
-        <v>4831</v>
-      </c>
-      <c r="DT31" t="s">
-        <v>4832</v>
-      </c>
-      <c r="DU31" t="s">
-        <v>4833</v>
-      </c>
-      <c r="DV31" t="s">
-        <v>4834</v>
-      </c>
-      <c r="DW31" t="s">
-        <v>4835</v>
-      </c>
-      <c r="DX31" t="s">
-        <v>4836</v>
-      </c>
-      <c r="DY31" t="s">
-        <v>4837</v>
-      </c>
-      <c r="DZ31" t="s">
-        <v>4838</v>
-      </c>
-      <c r="EA31" t="s">
-        <v>4839</v>
-      </c>
-      <c r="EB31" t="s">
-        <v>4840</v>
-      </c>
-      <c r="EC31" t="s">
-        <v>4667</v>
-      </c>
-      <c r="ED31" t="s">
-        <v>4841</v>
-      </c>
-      <c r="EE31" t="s">
-        <v>4842</v>
-      </c>
-      <c r="EF31" t="s">
-        <v>4843</v>
-      </c>
-      <c r="EG31" t="s">
-        <v>4844</v>
-      </c>
-      <c r="EH31" t="s">
-        <v>4845</v>
-      </c>
-      <c r="EI31" t="s">
-        <v>4846</v>
-      </c>
-      <c r="EJ31" t="s">
-        <v>1312</v>
-      </c>
-      <c r="EK31" t="s">
-        <v>4847</v>
-      </c>
-      <c r="EL31" t="s">
-        <v>4848</v>
-      </c>
-      <c r="EM31" t="s">
-        <v>4849</v>
-      </c>
-      <c r="EN31" t="s">
-        <v>3639</v>
-      </c>
-      <c r="EO31" t="s">
-        <v>4850</v>
-      </c>
-      <c r="EP31" t="s">
-        <v>4851</v>
-      </c>
-      <c r="EQ31" t="s">
-        <v>4852</v>
-      </c>
-      <c r="ER31" t="s">
-        <v>4853</v>
-      </c>
-      <c r="ES31" t="s">
-        <v>4854</v>
-      </c>
-      <c r="ET31" t="s">
-        <v>4855</v>
-      </c>
-      <c r="EU31" t="s">
-        <v>1728</v>
-      </c>
-      <c r="EV31" t="s">
-        <v>3758</v>
-      </c>
-      <c r="EW31" t="s">
-        <v>3672</v>
-      </c>
-      <c r="EX31" t="s">
-        <v>4856</v>
-      </c>
-      <c r="EY31" t="s">
-        <v>4857</v>
-      </c>
-      <c r="EZ31" t="s">
-        <v>4858</v>
-      </c>
-      <c r="FA31" t="s">
-        <v>4859</v>
-      </c>
-      <c r="FB31" t="s">
-        <v>4860</v>
-      </c>
-      <c r="FC31" t="s">
-        <v>1753</v>
-      </c>
-      <c r="FD31" t="s">
-        <v>735</v>
-      </c>
-      <c r="FE31" t="s">
-        <v>4861</v>
-      </c>
-      <c r="FF31" t="s">
-        <v>3948</v>
-      </c>
-      <c r="FG31" t="s">
-        <v>1740</v>
-      </c>
-      <c r="FH31" t="s">
-        <v>4862</v>
-      </c>
-      <c r="FI31" t="s">
-        <v>4863</v>
-      </c>
-      <c r="FJ31" t="s">
-        <v>3344</v>
-      </c>
-      <c r="FK31" t="s">
-        <v>4864</v>
-      </c>
-      <c r="FL31" t="s">
-        <v>4865</v>
-      </c>
-      <c r="FM31" t="s">
-        <v>1139</v>
-      </c>
-      <c r="FN31" t="s">
-        <v>1261</v>
-      </c>
-      <c r="FO31" t="s">
-        <v>868</v>
-      </c>
-      <c r="FP31" t="s">
-        <v>4866</v>
-      </c>
-      <c r="FQ31" t="s">
-        <v>4867</v>
-      </c>
-      <c r="FR31" t="s">
-        <v>2239</v>
-      </c>
-      <c r="FS31" t="s">
-        <v>4093</v>
-      </c>
-      <c r="FT31" t="s">
-        <v>1269</v>
-      </c>
-      <c r="FU31" t="s">
-        <v>4868</v>
-      </c>
-      <c r="FV31" t="s">
-        <v>4869</v>
-      </c>
-      <c r="FW31" t="s">
-        <v>1421</v>
-      </c>
-      <c r="FX31" t="s">
-        <v>4870</v>
-      </c>
-      <c r="FY31" t="s">
-        <v>4871</v>
-      </c>
-      <c r="FZ31" t="s">
-        <v>4872</v>
-      </c>
-      <c r="GA31" t="s">
-        <v>4873</v>
-      </c>
-      <c r="GB31" t="s">
-        <v>4874</v>
-      </c>
-      <c r="GC31" t="s">
-        <v>4875</v>
-      </c>
-      <c r="GD31" t="s">
-        <v>4876</v>
-      </c>
-      <c r="GE31" t="s">
-        <v>4877</v>
-      </c>
-      <c r="GF31" t="s">
-        <v>4878</v>
-      </c>
-      <c r="GG31" t="s">
-        <v>4879</v>
-      </c>
-      <c r="GH31" t="s">
-        <v>4880</v>
-      </c>
-      <c r="GI31" t="s">
-        <v>4881</v>
-      </c>
-      <c r="GJ31" t="s">
-        <v>4882</v>
-      </c>
-      <c r="GK31" t="s">
-        <v>4883</v>
-      </c>
-      <c r="GL31" t="s">
-        <v>4884</v>
-      </c>
-      <c r="GM31" t="s">
-        <v>4885</v>
-      </c>
-      <c r="GN31" t="s">
-        <v>416</v>
-      </c>
-      <c r="GO31" t="s">
-        <v>4886</v>
-      </c>
-      <c r="GP31" t="s">
-        <v>4887</v>
-      </c>
-      <c r="GQ31" t="s">
-        <v>4888</v>
-      </c>
-      <c r="GR31" t="s">
-        <v>4889</v>
-      </c>
-      <c r="GS31" t="s">
-        <v>4890</v>
-      </c>
-      <c r="GT31" t="s">
-        <v>4891</v>
-      </c>
-      <c r="GU31" t="s">
-        <v>4892</v>
-      </c>
-      <c r="GV31" t="s">
-        <v>4893</v>
-      </c>
-      <c r="GW31" t="s">
-        <v>4894</v>
-      </c>
-      <c r="GX31" t="s">
-        <v>4895</v>
-      </c>
-      <c r="GY31" t="s">
-        <v>4896</v>
-      </c>
-      <c r="GZ31" t="s">
-        <v>4897</v>
-      </c>
-      <c r="HA31" t="s">
-        <v>4898</v>
-      </c>
-      <c r="HB31" t="s">
-        <v>4899</v>
-      </c>
-      <c r="HC31" t="s">
-        <v>629</v>
-      </c>
-      <c r="HD31" t="s">
-        <v>933</v>
-      </c>
-      <c r="HE31" t="s">
-        <v>4900</v>
-      </c>
-      <c r="HF31" t="s">
-        <v>4901</v>
-      </c>
-      <c r="HG31" t="s">
-        <v>4902</v>
-      </c>
-      <c r="HH31" t="s">
-        <v>4903</v>
-      </c>
-      <c r="HI31" t="s">
-        <v>4904</v>
-      </c>
-      <c r="HJ31" t="s">
-        <v>4905</v>
-      </c>
-      <c r="HK31" t="s">
-        <v>4906</v>
-      </c>
-      <c r="HL31" t="s">
-        <v>4907</v>
-      </c>
-      <c r="HM31" t="s">
-        <v>4908</v>
-      </c>
-      <c r="HN31" t="s">
-        <v>4909</v>
-      </c>
-      <c r="HO31" t="s">
-        <v>4910</v>
-      </c>
-      <c r="HP31" t="s">
-        <v>4911</v>
-      </c>
-      <c r="HQ31" t="s">
-        <v>4912</v>
-      </c>
-      <c r="HR31" t="s">
-        <v>4913</v>
-      </c>
-      <c r="HS31" t="s">
-        <v>4914</v>
-      </c>
-      <c r="HT31" t="s">
-        <v>4915</v>
-      </c>
-      <c r="HU31" t="s">
-        <v>4916</v>
-      </c>
-      <c r="HV31" t="s">
-        <v>2022</v>
-      </c>
-      <c r="HW31" t="s">
-        <v>3907</v>
-      </c>
-      <c r="HX31" t="s">
-        <v>4917</v>
-      </c>
-      <c r="HY31" t="s">
-        <v>4918</v>
-      </c>
-      <c r="HZ31" t="s">
-        <v>922</v>
-      </c>
-      <c r="IA31" t="s">
-        <v>2319</v>
-      </c>
-      <c r="IB31" t="s">
-        <v>4919</v>
-      </c>
-      <c r="IC31" t="s">
-        <v>4920</v>
-      </c>
-      <c r="ID31" t="s">
-        <v>4921</v>
-      </c>
-      <c r="IE31" t="s">
-        <v>4922</v>
-      </c>
-      <c r="IF31" t="s">
-        <v>4923</v>
-      </c>
-      <c r="IG31" t="s">
-        <v>4924</v>
-      </c>
-      <c r="IH31" t="s">
-        <v>4925</v>
-      </c>
-      <c r="II31" t="s">
-        <v>4926</v>
-      </c>
-      <c r="IJ31" t="s">
-        <v>4927</v>
-      </c>
-      <c r="IK31" t="s">
-        <v>4928</v>
-      </c>
-      <c r="IL31" t="s">
-        <v>4929</v>
-      </c>
-      <c r="IM31" t="s">
-        <v>4930</v>
-      </c>
-      <c r="IN31" t="s">
-        <v>4931</v>
-      </c>
-      <c r="IO31" t="s">
-        <v>4932</v>
-      </c>
-      <c r="IP31" t="s">
-        <v>4933</v>
-      </c>
-      <c r="IQ31" t="s">
-        <v>483</v>
-      </c>
-      <c r="IR31" t="s">
-        <v>4934</v>
-      </c>
-      <c r="IS31" t="s">
-        <v>700</v>
-      </c>
-      <c r="IT31" t="s">
-        <v>2544</v>
-      </c>
-      <c r="IU31" t="s">
-        <v>4935</v>
-      </c>
-      <c r="IV31" t="s">
-        <v>427</v>
-      </c>
-      <c r="IW31" t="s">
-        <v>4936</v>
-      </c>
-      <c r="IX31" t="s">
-        <v>4726</v>
-      </c>
-      <c r="IY31" t="s">
-        <v>477</v>
-      </c>
-      <c r="IZ31" t="s">
-        <v>4937</v>
-      </c>
-      <c r="JA31" t="s">
-        <v>4938</v>
-      </c>
-      <c r="JB31" t="s">
-        <v>4939</v>
-      </c>
-      <c r="JC31" t="s">
-        <v>4940</v>
-      </c>
-      <c r="JD31" t="s">
-        <v>4941</v>
-      </c>
-      <c r="JE31" t="s">
-        <v>4942</v>
-      </c>
-      <c r="JF31" t="s">
-        <v>4943</v>
-      </c>
-      <c r="JG31" t="s">
-        <v>1036</v>
-      </c>
-      <c r="JH31" t="s">
-        <v>4944</v>
-      </c>
-      <c r="JI31" t="s">
-        <v>4945</v>
-      </c>
-      <c r="JJ31" t="s">
-        <v>4946</v>
-      </c>
-      <c r="JK31" t="s">
-        <v>4947</v>
-      </c>
-      <c r="JL31" t="s">
-        <v>4948</v>
-      </c>
-      <c r="JM31" t="s">
-        <v>4949</v>
-      </c>
-      <c r="JN31" t="s">
-        <v>4950</v>
-      </c>
-      <c r="JO31" t="s">
-        <v>4589</v>
-      </c>
-      <c r="JP31" t="s">
-        <v>4951</v>
-      </c>
-      <c r="JQ31" t="s">
-        <v>4952</v>
-      </c>
-      <c r="JR31" t="s">
-        <v>2751</v>
-      </c>
-      <c r="JS31" t="s">
-        <v>4953</v>
-      </c>
-      <c r="JT31" t="s">
-        <v>4954</v>
-      </c>
-      <c r="JU31" t="s">
-        <v>4955</v>
-      </c>
-      <c r="JV31" t="s">
-        <v>4956</v>
-      </c>
-      <c r="JW31" t="s">
-        <v>4957</v>
-      </c>
-      <c r="JX31" t="s">
-        <v>4958</v>
-      </c>
-      <c r="JY31" t="s">
-        <v>4959</v>
-      </c>
-      <c r="JZ31" t="s">
-        <v>4960</v>
-      </c>
-      <c r="KA31" t="s">
-        <v>4961</v>
-      </c>
-      <c r="KB31" t="s">
-        <v>4962</v>
-      </c>
-      <c r="KC31" t="s">
-        <v>4963</v>
-      </c>
-      <c r="KD31" t="s">
-        <v>4964</v>
-      </c>
-      <c r="KE31" t="s">
-        <v>4965</v>
-      </c>
-      <c r="KF31" t="s">
-        <v>4966</v>
-      </c>
-      <c r="KG31" t="s">
-        <v>4697</v>
-      </c>
-      <c r="KH31" t="s">
-        <v>4967</v>
-      </c>
-      <c r="KI31" t="s">
-        <v>4968</v>
-      </c>
-      <c r="KJ31" t="s">
-        <v>4969</v>
-      </c>
-      <c r="KK31" t="s">
-        <v>4970</v>
-      </c>
-      <c r="KL31" t="s">
-        <v>4971</v>
-      </c>
-      <c r="KM31" t="s">
-        <v>1982</v>
-      </c>
-      <c r="KN31" t="s">
-        <v>4972</v>
-      </c>
-      <c r="KO31" t="s">
-        <v>3148</v>
-      </c>
-      <c r="KP31" t="s">
-        <v>1585</v>
-      </c>
-      <c r="KQ31" t="s">
-        <v>4973</v>
-      </c>
-      <c r="KR31" t="s">
-        <v>2657</v>
-      </c>
-      <c r="KS31" t="s">
-        <v>762</v>
-      </c>
-      <c r="KT31" t="s">
-        <v>4974</v>
-      </c>
-      <c r="KU31" t="s">
-        <v>4975</v>
-      </c>
-      <c r="KV31" t="s">
-        <v>4976</v>
-      </c>
-      <c r="KW31" t="s">
-        <v>2257</v>
-      </c>
-      <c r="KX31" t="s">
-        <v>4977</v>
-      </c>
-    </row>
-    <row r="32" spans="1:310">
-      <c r="A32" t="s">
-        <v>4978</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4979</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4980</v>
-      </c>
-      <c r="D32" t="s">
-        <v>4981</v>
-      </c>
-      <c r="E32" t="s">
-        <v>3199</v>
-      </c>
-      <c r="F32" t="s">
-        <v>4982</v>
-      </c>
-      <c r="G32" t="s">
-        <v>4983</v>
-      </c>
-      <c r="H32" t="s">
-        <v>4984</v>
-      </c>
-      <c r="I32" t="s">
-        <v>3466</v>
-      </c>
-      <c r="J32" t="s">
-        <v>3047</v>
-      </c>
-      <c r="K32" t="s">
-        <v>1869</v>
-      </c>
-      <c r="L32" t="s">
-        <v>4985</v>
-      </c>
-      <c r="M32" t="s">
-        <v>4986</v>
-      </c>
-      <c r="N32" t="s">
-        <v>4987</v>
-      </c>
-      <c r="O32" t="s">
-        <v>4988</v>
-      </c>
-      <c r="P32" t="s">
-        <v>4989</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>1777</v>
-      </c>
-      <c r="R32" t="s">
-        <v>4990</v>
-      </c>
-      <c r="S32" t="s">
-        <v>4991</v>
-      </c>
-      <c r="T32" t="s">
-        <v>627</v>
-      </c>
-      <c r="U32" t="s">
-        <v>4992</v>
-      </c>
-      <c r="V32" t="s">
-        <v>4236</v>
-      </c>
-      <c r="W32" t="s">
-        <v>4993</v>
-      </c>
-      <c r="X32" t="s">
-        <v>481</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>4994</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>4821</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>4995</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>4996</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>4997</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>4483</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>4998</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>4999</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>5000</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>433</v>
-      </c>
-      <c r="AI32" t="s">
-        <v>5001</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>938</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>5002</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>5003</v>
-      </c>
-      <c r="AM32" t="s">
-        <v>586</v>
-      </c>
-      <c r="AN32" t="s">
-        <v>1888</v>
-      </c>
-      <c r="AO32" t="s">
-        <v>5004</v>
-      </c>
-      <c r="AP32" t="s">
-        <v>5005</v>
-      </c>
-      <c r="AQ32" t="s">
-        <v>3498</v>
-      </c>
-      <c r="AR32" t="s">
-        <v>1129</v>
-      </c>
-      <c r="AS32" t="s">
-        <v>5006</v>
-      </c>
-      <c r="AT32" t="s">
-        <v>5007</v>
-      </c>
-      <c r="AU32" t="s">
-        <v>5008</v>
-      </c>
-      <c r="AV32" t="s">
-        <v>5009</v>
-      </c>
-      <c r="AW32" t="s">
-        <v>2125</v>
-      </c>
-      <c r="AX32" t="s">
-        <v>617</v>
-      </c>
-      <c r="AY32" t="s">
-        <v>5010</v>
-      </c>
-      <c r="AZ32" t="s">
-        <v>5011</v>
-      </c>
-      <c r="BA32" t="s">
-        <v>5012</v>
-      </c>
-      <c r="BB32" t="s">
-        <v>5013</v>
-      </c>
-      <c r="BC32" t="s">
-        <v>5014</v>
-      </c>
-      <c r="BD32" t="s">
-        <v>5015</v>
-      </c>
-      <c r="BE32" t="s">
-        <v>4821</v>
-      </c>
-      <c r="BF32" t="s">
-        <v>5016</v>
-      </c>
-      <c r="BG32" t="s">
-        <v>1029</v>
-      </c>
-      <c r="BH32" t="s">
-        <v>4726</v>
-      </c>
-      <c r="BI32" t="s">
-        <v>5017</v>
-      </c>
-      <c r="BJ32" t="s">
-        <v>5018</v>
-      </c>
-      <c r="BK32" t="s">
-        <v>367</v>
-      </c>
-      <c r="BL32" t="s">
-        <v>4885</v>
-      </c>
-      <c r="BM32" t="s">
-        <v>5019</v>
-      </c>
-      <c r="BN32" t="s">
-        <v>5020</v>
-      </c>
-      <c r="BO32" t="s">
-        <v>828</v>
-      </c>
-      <c r="BP32" t="s">
-        <v>5021</v>
-      </c>
-      <c r="BQ32" t="s">
-        <v>5022</v>
-      </c>
-      <c r="BR32" t="s">
-        <v>5023</v>
-      </c>
-      <c r="BS32" t="s">
-        <v>5024</v>
-      </c>
-      <c r="BT32" t="s">
-        <v>5025</v>
-      </c>
-      <c r="BU32" t="s">
-        <v>5026</v>
-      </c>
-      <c r="BV32" t="s">
-        <v>5027</v>
-      </c>
-      <c r="BW32" t="s">
-        <v>5028</v>
-      </c>
-      <c r="BX32" t="s">
-        <v>1652</v>
-      </c>
-      <c r="BY32" t="s">
-        <v>3563</v>
-      </c>
-      <c r="BZ32" t="s">
-        <v>5029</v>
-      </c>
-      <c r="CA32" t="s">
-        <v>1381</v>
-      </c>
-      <c r="CB32" t="s">
-        <v>5030</v>
-      </c>
-      <c r="CC32" t="s">
-        <v>5031</v>
-      </c>
-      <c r="CD32" t="s">
-        <v>5032</v>
-      </c>
-      <c r="CE32" t="s">
-        <v>5033</v>
-      </c>
-      <c r="CF32" t="s">
-        <v>5034</v>
-      </c>
-      <c r="CG32" t="s">
-        <v>5035</v>
-      </c>
-      <c r="CH32" t="s">
-        <v>1244</v>
-      </c>
-      <c r="CI32" t="s">
-        <v>5036</v>
-      </c>
-      <c r="CJ32" t="s">
-        <v>555</v>
-      </c>
-      <c r="CK32" t="s">
-        <v>3140</v>
-      </c>
-      <c r="CL32" t="s">
-        <v>5037</v>
-      </c>
-      <c r="CM32" t="s">
-        <v>5038</v>
-      </c>
-      <c r="CN32" t="s">
-        <v>5039</v>
-      </c>
-      <c r="CO32" t="s">
-        <v>5040</v>
-      </c>
-      <c r="CP32" t="s">
-        <v>5041</v>
-      </c>
-      <c r="CQ32" t="s">
-        <v>5024</v>
-      </c>
-      <c r="CR32" t="s">
-        <v>1523</v>
-      </c>
-      <c r="CS32" t="s">
-        <v>5042</v>
-      </c>
-      <c r="CT32" t="s">
-        <v>5043</v>
-      </c>
-      <c r="CU32" t="s">
-        <v>4562</v>
-      </c>
-      <c r="CV32" t="s">
-        <v>5044</v>
-      </c>
-      <c r="CW32" t="s">
-        <v>5045</v>
-      </c>
-      <c r="CX32" t="s">
-        <v>5046</v>
-      </c>
-      <c r="CY32" t="s">
-        <v>4931</v>
-      </c>
-      <c r="CZ32" t="s">
-        <v>5047</v>
-      </c>
-      <c r="DA32" t="s">
-        <v>5048</v>
-      </c>
-      <c r="DB32" t="s">
-        <v>897</v>
-      </c>
-      <c r="DC32" t="s">
-        <v>5049</v>
-      </c>
-      <c r="DD32" t="s">
-        <v>1554</v>
-      </c>
-      <c r="DE32" t="s">
-        <v>5050</v>
-      </c>
-      <c r="DF32" t="s">
-        <v>5051</v>
-      </c>
-      <c r="DG32" t="s">
-        <v>5052</v>
-      </c>
-      <c r="DH32" t="s">
-        <v>616</v>
-      </c>
-      <c r="DI32" t="s">
-        <v>5053</v>
-      </c>
-      <c r="DJ32" t="s">
-        <v>5054</v>
-      </c>
-      <c r="DK32" t="s">
-        <v>5055</v>
-      </c>
-      <c r="DL32" t="s">
-        <v>5056</v>
-      </c>
-      <c r="DM32" t="s">
-        <v>1884</v>
-      </c>
-      <c r="DN32" t="s">
-        <v>5057</v>
-      </c>
-      <c r="DO32" t="s">
-        <v>5058</v>
-      </c>
-      <c r="DP32" t="s">
-        <v>5059</v>
-      </c>
-      <c r="DQ32" t="s">
-        <v>5060</v>
-      </c>
-      <c r="DR32" t="s">
-        <v>3119</v>
-      </c>
-      <c r="DS32" t="s">
-        <v>5061</v>
-      </c>
-      <c r="DT32" t="s">
-        <v>5062</v>
-      </c>
-      <c r="DU32" t="s">
-        <v>5063</v>
-      </c>
-      <c r="DV32" t="s">
-        <v>3521</v>
-      </c>
-      <c r="DW32" t="s">
-        <v>609</v>
-      </c>
-      <c r="DX32" t="s">
-        <v>5064</v>
-      </c>
-      <c r="DY32" t="s">
-        <v>5065</v>
-      </c>
-      <c r="DZ32" t="s">
-        <v>5066</v>
-      </c>
-      <c r="EA32" t="s">
-        <v>5067</v>
-      </c>
-      <c r="EB32" t="s">
-        <v>5068</v>
-      </c>
-      <c r="EC32" t="s">
-        <v>5069</v>
-      </c>
-      <c r="ED32" t="s">
-        <v>5070</v>
-      </c>
-      <c r="EE32" t="s">
-        <v>5071</v>
-      </c>
-      <c r="EF32" t="s">
-        <v>5072</v>
-      </c>
-      <c r="EG32" t="s">
-        <v>5073</v>
-      </c>
-      <c r="EH32" t="s">
-        <v>3297</v>
-      </c>
-      <c r="EI32" t="s">
-        <v>5074</v>
-      </c>
-      <c r="EJ32" t="s">
-        <v>5075</v>
-      </c>
-      <c r="EK32" t="s">
-        <v>5076</v>
-      </c>
-      <c r="EL32" t="s">
-        <v>2270</v>
-      </c>
-      <c r="EM32" t="s">
-        <v>5077</v>
-      </c>
-      <c r="EN32" t="s">
-        <v>5078</v>
-      </c>
-      <c r="EO32" t="s">
-        <v>5079</v>
-      </c>
-      <c r="EP32" t="s">
-        <v>5080</v>
-      </c>
-      <c r="EQ32" t="s">
-        <v>5081</v>
-      </c>
-      <c r="ER32" t="s">
-        <v>5082</v>
-      </c>
-      <c r="ES32" t="s">
-        <v>5083</v>
-      </c>
-      <c r="ET32" t="s">
-        <v>5084</v>
-      </c>
-      <c r="EU32" t="s">
-        <v>4261</v>
-      </c>
-      <c r="EV32" t="s">
-        <v>4151</v>
-      </c>
-      <c r="EW32" t="s">
-        <v>5085</v>
-      </c>
-      <c r="EX32" t="s">
-        <v>5086</v>
-      </c>
-      <c r="EY32" t="s">
-        <v>5087</v>
-      </c>
-      <c r="EZ32" t="s">
-        <v>5088</v>
-      </c>
-      <c r="FA32" t="s">
-        <v>5089</v>
-      </c>
-      <c r="FB32" t="s">
-        <v>5090</v>
-      </c>
-      <c r="FC32" t="s">
-        <v>1589</v>
-      </c>
-      <c r="FD32" t="s">
-        <v>5091</v>
-      </c>
-      <c r="FE32" t="s">
-        <v>3189</v>
-      </c>
-      <c r="FF32" t="s">
-        <v>5092</v>
-      </c>
-      <c r="FG32" t="s">
-        <v>1106</v>
-      </c>
-      <c r="FH32" t="s">
-        <v>5093</v>
-      </c>
-      <c r="FI32" t="s">
-        <v>5094</v>
-      </c>
-      <c r="FJ32" t="s">
-        <v>5095</v>
-      </c>
-      <c r="FK32" t="s">
-        <v>5096</v>
-      </c>
-      <c r="FL32" t="s">
-        <v>5097</v>
-      </c>
-      <c r="FM32" t="s">
-        <v>1753</v>
-      </c>
-      <c r="FN32" t="s">
-        <v>5098</v>
-      </c>
-      <c r="FO32" t="s">
-        <v>788</v>
-      </c>
-      <c r="FP32" t="s">
-        <v>5099</v>
-      </c>
-      <c r="FQ32" t="s">
-        <v>5100</v>
-      </c>
-      <c r="FR32" t="s">
-        <v>1183</v>
-      </c>
-      <c r="FS32" t="s">
-        <v>3966</v>
-      </c>
-      <c r="FT32" t="s">
-        <v>1612</v>
-      </c>
-      <c r="FU32" t="s">
-        <v>5101</v>
-      </c>
-      <c r="FV32" t="s">
-        <v>5102</v>
-      </c>
-      <c r="FW32" t="s">
-        <v>1021</v>
-      </c>
-      <c r="FX32" t="s">
-        <v>5103</v>
-      </c>
-      <c r="FY32" t="s">
-        <v>4897</v>
-      </c>
-      <c r="FZ32" t="s">
-        <v>1345</v>
-      </c>
-      <c r="GA32" t="s">
-        <v>5104</v>
-      </c>
-      <c r="GB32" t="s">
-        <v>5105</v>
-      </c>
-      <c r="GC32" t="s">
-        <v>5106</v>
-      </c>
-      <c r="GD32" t="s">
-        <v>5107</v>
-      </c>
-      <c r="GE32" t="s">
-        <v>5108</v>
-      </c>
-      <c r="GF32" t="s">
-        <v>5109</v>
-      </c>
-      <c r="GG32" t="s">
-        <v>5110</v>
-      </c>
-      <c r="GH32" t="s">
-        <v>1229</v>
-      </c>
-      <c r="GI32" t="s">
-        <v>5111</v>
-      </c>
-      <c r="GJ32" t="s">
-        <v>2771</v>
-      </c>
-      <c r="GK32" t="s">
-        <v>5112</v>
-      </c>
-      <c r="GL32" t="s">
-        <v>5113</v>
-      </c>
-      <c r="GM32" t="s">
-        <v>5114</v>
-      </c>
-      <c r="GN32" t="s">
-        <v>547</v>
-      </c>
-      <c r="GO32" t="s">
-        <v>5115</v>
-      </c>
-      <c r="GP32" t="s">
-        <v>5116</v>
-      </c>
-      <c r="GQ32" t="s">
-        <v>1477</v>
-      </c>
-      <c r="GR32" t="s">
-        <v>5117</v>
-      </c>
-      <c r="GS32" t="s">
-        <v>5118</v>
-      </c>
-      <c r="GT32" t="s">
-        <v>5119</v>
-      </c>
-      <c r="GU32" t="s">
-        <v>5120</v>
-      </c>
-      <c r="GV32" t="s">
-        <v>3228</v>
-      </c>
-      <c r="GW32" t="s">
-        <v>5121</v>
-      </c>
-      <c r="GX32" t="s">
-        <v>2659</v>
-      </c>
-      <c r="GY32" t="s">
-        <v>5122</v>
-      </c>
-      <c r="GZ32" t="s">
-        <v>5123</v>
-      </c>
-      <c r="HA32" t="s">
-        <v>5124</v>
-      </c>
-      <c r="HB32" t="s">
-        <v>5125</v>
-      </c>
-      <c r="HC32" t="s">
-        <v>5126</v>
-      </c>
-      <c r="HD32" t="s">
-        <v>1004</v>
-      </c>
-      <c r="HE32" t="s">
-        <v>5127</v>
-      </c>
-      <c r="HF32" t="s">
-        <v>5128</v>
-      </c>
-      <c r="HG32" t="s">
-        <v>5129</v>
-      </c>
-      <c r="HH32" t="s">
-        <v>5130</v>
-      </c>
-      <c r="HI32" t="s">
-        <v>5131</v>
-      </c>
-      <c r="HJ32" t="s">
-        <v>5132</v>
-      </c>
-      <c r="HK32" t="s">
-        <v>5133</v>
-      </c>
-      <c r="HL32" t="s">
-        <v>5134</v>
-      </c>
-      <c r="HM32" t="s">
-        <v>4841</v>
-      </c>
-      <c r="HN32" t="s">
-        <v>5135</v>
-      </c>
-      <c r="HO32" t="s">
-        <v>5136</v>
-      </c>
-      <c r="HP32" t="s">
-        <v>1283</v>
-      </c>
-      <c r="HQ32" t="s">
-        <v>5137</v>
-      </c>
-      <c r="HR32" t="s">
-        <v>5138</v>
-      </c>
-      <c r="HS32" t="s">
-        <v>5139</v>
-      </c>
-      <c r="HT32" t="s">
-        <v>1528</v>
-      </c>
-      <c r="HU32" t="s">
-        <v>1003</v>
-      </c>
-      <c r="HV32" t="s">
-        <v>5140</v>
-      </c>
-      <c r="HW32" t="s">
-        <v>630</v>
-      </c>
-      <c r="HX32" t="s">
-        <v>5141</v>
-      </c>
-      <c r="HY32" t="s">
-        <v>5142</v>
-      </c>
-      <c r="HZ32" t="s">
-        <v>572</v>
-      </c>
-      <c r="IA32" t="s">
-        <v>5143</v>
-      </c>
-      <c r="IB32" t="s">
-        <v>5144</v>
-      </c>
-      <c r="IC32" t="s">
-        <v>5145</v>
-      </c>
-      <c r="ID32" t="s">
-        <v>5146</v>
-      </c>
-      <c r="IE32" t="s">
-        <v>5147</v>
-      </c>
-      <c r="IF32" t="s">
-        <v>5148</v>
-      </c>
-      <c r="IG32" t="s">
-        <v>5149</v>
-      </c>
-      <c r="IH32" t="s">
-        <v>5150</v>
-      </c>
-      <c r="II32" t="s">
-        <v>3890</v>
-      </c>
-      <c r="IJ32" t="s">
-        <v>5151</v>
-      </c>
-      <c r="IK32" t="s">
-        <v>5152</v>
-      </c>
-      <c r="IL32" t="s">
-        <v>5153</v>
-      </c>
-      <c r="IM32" t="s">
-        <v>4340</v>
-      </c>
-      <c r="IN32" t="s">
-        <v>5154</v>
-      </c>
-      <c r="IO32" t="s">
-        <v>5155</v>
-      </c>
-      <c r="IP32" t="s">
-        <v>5156</v>
-      </c>
-      <c r="IQ32" t="s">
-        <v>446</v>
-      </c>
-      <c r="IR32" t="s">
-        <v>5157</v>
-      </c>
-      <c r="IS32" t="s">
-        <v>3241</v>
-      </c>
-      <c r="IT32" t="s">
-        <v>410</v>
-      </c>
-      <c r="IU32" t="s">
-        <v>5158</v>
-      </c>
-      <c r="IV32" t="s">
-        <v>427</v>
-      </c>
-      <c r="IW32" t="s">
-        <v>3827</v>
-      </c>
-      <c r="IX32" t="s">
-        <v>5159</v>
-      </c>
-      <c r="IY32" t="s">
-        <v>997</v>
-      </c>
-      <c r="IZ32" t="s">
-        <v>5115</v>
-      </c>
-      <c r="JA32" t="s">
-        <v>5160</v>
-      </c>
-      <c r="JB32" t="s">
-        <v>5161</v>
-      </c>
-      <c r="JC32" t="s">
-        <v>5162</v>
-      </c>
-      <c r="JD32" t="s">
-        <v>5163</v>
-      </c>
-      <c r="JE32" t="s">
-        <v>5164</v>
-      </c>
-      <c r="JF32" t="s">
-        <v>5060</v>
-      </c>
-      <c r="JG32" t="s">
-        <v>5165</v>
-      </c>
-      <c r="JH32" t="s">
-        <v>5166</v>
-      </c>
-      <c r="JI32" t="s">
-        <v>5167</v>
-      </c>
-      <c r="JJ32" t="s">
-        <v>5168</v>
-      </c>
-      <c r="JK32" t="s">
-        <v>5169</v>
-      </c>
-      <c r="JL32" t="s">
-        <v>5170</v>
-      </c>
-      <c r="JM32" t="s">
-        <v>5171</v>
-      </c>
-      <c r="JN32" t="s">
-        <v>3889</v>
-      </c>
-      <c r="JO32" t="s">
-        <v>5172</v>
-      </c>
-      <c r="JP32" t="s">
-        <v>5173</v>
-      </c>
-      <c r="JQ32" t="s">
-        <v>5174</v>
-      </c>
-      <c r="JR32" t="s">
-        <v>5175</v>
-      </c>
-      <c r="JS32" t="s">
-        <v>5176</v>
-      </c>
-      <c r="JT32" t="s">
-        <v>3782</v>
-      </c>
-      <c r="JU32" t="s">
-        <v>5177</v>
-      </c>
-      <c r="JV32" t="s">
-        <v>5178</v>
-      </c>
-      <c r="JW32" t="s">
-        <v>5179</v>
-      </c>
-      <c r="JX32" t="s">
-        <v>5180</v>
-      </c>
-      <c r="JY32" t="s">
-        <v>5181</v>
-      </c>
-      <c r="JZ32" t="s">
-        <v>5182</v>
-      </c>
-      <c r="KA32" t="s">
-        <v>5183</v>
-      </c>
-      <c r="KB32" t="s">
-        <v>5184</v>
-      </c>
-      <c r="KC32" t="s">
-        <v>5185</v>
-      </c>
-      <c r="KD32" t="s">
-        <v>5186</v>
-      </c>
-      <c r="KE32" t="s">
-        <v>5187</v>
-      </c>
-      <c r="KF32" t="s">
-        <v>5188</v>
-      </c>
-      <c r="KG32" t="s">
-        <v>5189</v>
-      </c>
-      <c r="KH32" t="s">
-        <v>5190</v>
-      </c>
-      <c r="KI32" t="s">
-        <v>5191</v>
-      </c>
-      <c r="KJ32" t="s">
-        <v>5192</v>
-      </c>
-      <c r="KK32" t="s">
-        <v>5193</v>
-      </c>
-      <c r="KL32" t="s">
-        <v>5194</v>
-      </c>
-      <c r="KM32" t="s">
-        <v>5195</v>
-      </c>
-      <c r="KN32" t="s">
-        <v>5196</v>
-      </c>
-      <c r="KO32" t="s">
-        <v>370</v>
-      </c>
-      <c r="KP32" t="s">
-        <v>1576</v>
-      </c>
-      <c r="KQ32" t="s">
-        <v>5197</v>
-      </c>
-      <c r="KR32" t="s">
-        <v>5198</v>
-      </c>
-      <c r="KS32" t="s">
-        <v>2056</v>
-      </c>
-      <c r="KT32" t="s">
-        <v>5199</v>
-      </c>
-      <c r="KU32" t="s">
-        <v>3388</v>
-      </c>
-      <c r="KV32" t="s">
-        <v>5200</v>
-      </c>
-      <c r="KW32" t="s">
-        <v>1222</v>
-      </c>
-      <c r="KX32" t="s">
-        <v>5201</v>
-      </c>
-    </row>
-    <row r="33" spans="1:310">
-      <c r="A33" t="s">
-        <v>5202</v>
-      </c>
-      <c r="B33" t="s">
-        <v>5203</v>
-      </c>
-      <c r="C33" t="s">
-        <v>5204</v>
-      </c>
-      <c r="D33" t="s">
-        <v>5205</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5206</v>
-      </c>
-      <c r="F33" t="s">
-        <v>5207</v>
-      </c>
-      <c r="G33" t="s">
-        <v>5208</v>
-      </c>
-      <c r="H33" t="s">
-        <v>5209</v>
-      </c>
-      <c r="I33" t="s">
-        <v>3272</v>
-      </c>
-      <c r="J33" t="s">
-        <v>5210</v>
-      </c>
-      <c r="K33" t="s">
-        <v>5211</v>
-      </c>
-      <c r="L33" t="s">
-        <v>5212</v>
-      </c>
-      <c r="M33" t="s">
-        <v>5213</v>
-      </c>
-      <c r="N33" t="s">
-        <v>5214</v>
-      </c>
-      <c r="O33" t="s">
-        <v>5215</v>
-      </c>
-      <c r="P33" t="s">
-        <v>5216</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>5217</v>
-      </c>
-      <c r="R33" t="s">
-        <v>5218</v>
-      </c>
-      <c r="S33" t="s">
-        <v>5219</v>
-      </c>
-      <c r="T33" t="s">
-        <v>582</v>
-      </c>
-      <c r="U33" t="s">
-        <v>5220</v>
-      </c>
-      <c r="V33" t="s">
-        <v>1522</v>
-      </c>
-      <c r="W33" t="s">
-        <v>5221</v>
-      </c>
-      <c r="X33" t="s">
-        <v>561</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>5222</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>5223</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>1478</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>5224</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>4775</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>3430</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>5225</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>1893</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>5226</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>543</v>
-      </c>
-      <c r="AI33" t="s">
-        <v>5227</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>987</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>5228</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>5229</v>
-      </c>
-      <c r="AM33" t="s">
-        <v>3425</v>
-      </c>
-      <c r="AN33" t="s">
-        <v>1288</v>
-      </c>
-      <c r="AO33" t="s">
-        <v>5230</v>
-      </c>
-      <c r="AP33" t="s">
-        <v>4949</v>
-      </c>
-      <c r="AQ33" t="s">
-        <v>3326</v>
-      </c>
-      <c r="AR33" t="s">
-        <v>5231</v>
-      </c>
-      <c r="AS33" t="s">
-        <v>5232</v>
-      </c>
-      <c r="AT33" t="s">
-        <v>5233</v>
-      </c>
-      <c r="AU33" t="s">
-        <v>5234</v>
-      </c>
-      <c r="AV33" t="s">
-        <v>5235</v>
-      </c>
-      <c r="AW33" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AX33" t="s">
-        <v>1228</v>
-      </c>
-      <c r="AY33" t="s">
-        <v>5236</v>
-      </c>
-      <c r="AZ33" t="s">
-        <v>3450</v>
-      </c>
-      <c r="BA33" t="s">
-        <v>4668</v>
-      </c>
-      <c r="BB33" t="s">
-        <v>5237</v>
-      </c>
-      <c r="BC33" t="s">
-        <v>5238</v>
-      </c>
-      <c r="BD33" t="s">
-        <v>5239</v>
-      </c>
-      <c r="BE33" t="s">
-        <v>5240</v>
-      </c>
-      <c r="BF33" t="s">
-        <v>5241</v>
-      </c>
-      <c r="BG33" t="s">
-        <v>1042</v>
-      </c>
-      <c r="BH33" t="s">
-        <v>5242</v>
-      </c>
-      <c r="BI33" t="s">
-        <v>5243</v>
-      </c>
-      <c r="BJ33" t="s">
-        <v>5244</v>
-      </c>
-      <c r="BK33" t="s">
-        <v>718</v>
-      </c>
-      <c r="BL33" t="s">
-        <v>5245</v>
-      </c>
-      <c r="BM33" t="s">
-        <v>5246</v>
-      </c>
-      <c r="BN33" t="s">
-        <v>5247</v>
-      </c>
-      <c r="BO33" t="s">
-        <v>1101</v>
-      </c>
-      <c r="BP33" t="s">
-        <v>5248</v>
-      </c>
-      <c r="BQ33" t="s">
-        <v>5249</v>
-      </c>
-      <c r="BR33" t="s">
-        <v>5250</v>
-      </c>
-      <c r="BS33" t="s">
-        <v>5251</v>
-      </c>
-      <c r="BT33" t="s">
-        <v>3464</v>
-      </c>
-      <c r="BU33" t="s">
-        <v>5252</v>
-      </c>
-      <c r="BV33" t="s">
-        <v>5253</v>
-      </c>
-      <c r="BW33" t="s">
-        <v>5254</v>
-      </c>
-      <c r="BX33" t="s">
-        <v>5255</v>
-      </c>
-      <c r="BY33" t="s">
-        <v>5256</v>
-      </c>
-      <c r="BZ33" t="s">
-        <v>5257</v>
-      </c>
-      <c r="CA33" t="s">
-        <v>1387</v>
-      </c>
-      <c r="CB33" t="s">
-        <v>5258</v>
-      </c>
-      <c r="CC33" t="s">
-        <v>5259</v>
-      </c>
-      <c r="CD33" t="s">
-        <v>5260</v>
-      </c>
-      <c r="CE33" t="s">
-        <v>5261</v>
-      </c>
-      <c r="CF33" t="s">
-        <v>4892</v>
-      </c>
-      <c r="CG33" t="s">
-        <v>5262</v>
-      </c>
-      <c r="CH33" t="s">
-        <v>4360</v>
-      </c>
-      <c r="CI33" t="s">
-        <v>3191</v>
-      </c>
-      <c r="CJ33" t="s">
-        <v>711</v>
-      </c>
-      <c r="CK33" t="s">
-        <v>5263</v>
-      </c>
-      <c r="CL33" t="s">
-        <v>5264</v>
-      </c>
-      <c r="CM33" t="s">
-        <v>5265</v>
-      </c>
-      <c r="CN33" t="s">
-        <v>5266</v>
-      </c>
-      <c r="CO33" t="s">
-        <v>870</v>
-      </c>
-      <c r="CP33" t="s">
-        <v>2761</v>
-      </c>
-      <c r="CQ33" t="s">
-        <v>5267</v>
-      </c>
-      <c r="CR33" t="s">
-        <v>1114</v>
-      </c>
-      <c r="CS33" t="s">
-        <v>5268</v>
-      </c>
-      <c r="CT33" t="s">
-        <v>5269</v>
-      </c>
-      <c r="CU33" t="s">
-        <v>5270</v>
-      </c>
-      <c r="CV33" t="s">
-        <v>4284</v>
-      </c>
-      <c r="CW33" t="s">
-        <v>5271</v>
-      </c>
-      <c r="CX33" t="s">
-        <v>5272</v>
-      </c>
-      <c r="CY33" t="s">
-        <v>5273</v>
-      </c>
-      <c r="CZ33" t="s">
-        <v>5274</v>
-      </c>
-      <c r="DA33" t="s">
-        <v>5275</v>
-      </c>
-      <c r="DB33" t="s">
-        <v>1555</v>
-      </c>
-      <c r="DC33" t="s">
-        <v>1052</v>
-      </c>
-      <c r="DD33" t="s">
-        <v>5276</v>
-      </c>
-      <c r="DE33" t="s">
-        <v>5277</v>
-      </c>
-      <c r="DF33" t="s">
-        <v>5278</v>
-      </c>
-      <c r="DG33" t="s">
-        <v>5279</v>
-      </c>
-      <c r="DH33" t="s">
-        <v>1411</v>
-      </c>
-      <c r="DI33" t="s">
-        <v>5078</v>
-      </c>
-      <c r="DJ33" t="s">
-        <v>1683</v>
-      </c>
-      <c r="DK33" t="s">
-        <v>5280</v>
-      </c>
-      <c r="DL33" t="s">
-        <v>5162</v>
-      </c>
-      <c r="DM33" t="s">
-        <v>3167</v>
-      </c>
-      <c r="DN33" t="s">
-        <v>5281</v>
-      </c>
-      <c r="DO33" t="s">
-        <v>5282</v>
-      </c>
-      <c r="DP33" t="s">
-        <v>5283</v>
-      </c>
-      <c r="DQ33" t="s">
-        <v>5284</v>
-      </c>
-      <c r="DR33" t="s">
-        <v>1463</v>
-      </c>
-      <c r="DS33" t="s">
-        <v>5285</v>
-      </c>
-      <c r="DT33" t="s">
-        <v>5247</v>
-      </c>
-      <c r="DU33" t="s">
-        <v>5286</v>
-      </c>
-      <c r="DV33" t="s">
-        <v>4188</v>
-      </c>
-      <c r="DW33" t="s">
-        <v>428</v>
-      </c>
-      <c r="DX33" t="s">
-        <v>4358</v>
-      </c>
-      <c r="DY33" t="s">
-        <v>4104</v>
-      </c>
-      <c r="DZ33" t="s">
-        <v>5287</v>
-      </c>
-      <c r="EA33" t="s">
-        <v>5288</v>
-      </c>
-      <c r="EB33" t="s">
-        <v>5289</v>
-      </c>
-      <c r="EC33" t="s">
-        <v>5246</v>
-      </c>
-      <c r="ED33" t="s">
-        <v>5290</v>
-      </c>
-      <c r="EE33" t="s">
-        <v>5291</v>
-      </c>
-      <c r="EF33" t="s">
-        <v>5292</v>
-      </c>
-      <c r="EG33" t="s">
-        <v>4725</v>
-      </c>
-      <c r="EH33" t="s">
-        <v>5293</v>
-      </c>
-      <c r="EI33" t="s">
-        <v>5294</v>
-      </c>
-      <c r="EJ33" t="s">
-        <v>5295</v>
-      </c>
-      <c r="EK33" t="s">
-        <v>5296</v>
-      </c>
-      <c r="EL33" t="s">
-        <v>5297</v>
-      </c>
-      <c r="EM33" t="s">
-        <v>5298</v>
-      </c>
-      <c r="EN33" t="s">
-        <v>5299</v>
-      </c>
-      <c r="EO33" t="s">
-        <v>5300</v>
-      </c>
-      <c r="EP33" t="s">
-        <v>5301</v>
-      </c>
-      <c r="EQ33" t="s">
-        <v>5302</v>
-      </c>
-      <c r="ER33" t="s">
-        <v>5303</v>
-      </c>
-      <c r="ES33" t="s">
-        <v>5304</v>
-      </c>
-      <c r="ET33" t="s">
-        <v>5305</v>
-      </c>
-      <c r="EU33" t="s">
-        <v>2746</v>
-      </c>
-      <c r="EV33" t="s">
-        <v>5306</v>
-      </c>
-      <c r="EW33" t="s">
-        <v>1792</v>
-      </c>
-      <c r="EX33" t="s">
-        <v>5307</v>
-      </c>
-      <c r="EY33" t="s">
-        <v>5308</v>
-      </c>
-      <c r="EZ33" t="s">
-        <v>5309</v>
-      </c>
-      <c r="FA33" t="s">
-        <v>5245</v>
-      </c>
-      <c r="FB33" t="s">
-        <v>5310</v>
-      </c>
-      <c r="FC33" t="s">
-        <v>1071</v>
-      </c>
-      <c r="FD33" t="s">
-        <v>5311</v>
-      </c>
-      <c r="FE33" t="s">
-        <v>3009</v>
-      </c>
-      <c r="FF33" t="s">
-        <v>5312</v>
-      </c>
-      <c r="FG33" t="s">
-        <v>4329</v>
-      </c>
-      <c r="FH33" t="s">
-        <v>5313</v>
-      </c>
-      <c r="FI33" t="s">
-        <v>5314</v>
-      </c>
-      <c r="FJ33" t="s">
-        <v>5315</v>
-      </c>
-      <c r="FK33" t="s">
-        <v>5316</v>
-      </c>
-      <c r="FL33" t="s">
-        <v>5317</v>
-      </c>
-      <c r="FM33" t="s">
-        <v>1198</v>
-      </c>
-      <c r="FN33" t="s">
-        <v>1927</v>
-      </c>
-      <c r="FO33" t="s">
-        <v>840</v>
-      </c>
-      <c r="FP33" t="s">
-        <v>5318</v>
-      </c>
-      <c r="FQ33" t="s">
-        <v>5319</v>
-      </c>
-      <c r="FR33" t="s">
-        <v>1920</v>
-      </c>
-      <c r="FS33" t="s">
-        <v>5320</v>
-      </c>
-      <c r="FT33" t="s">
-        <v>5321</v>
-      </c>
-      <c r="FU33" t="s">
-        <v>5322</v>
-      </c>
-      <c r="FV33" t="s">
-        <v>5323</v>
-      </c>
-      <c r="FW33" t="s">
-        <v>3202</v>
-      </c>
-      <c r="FX33" t="s">
-        <v>5324</v>
-      </c>
-      <c r="FY33" t="s">
-        <v>5325</v>
-      </c>
-      <c r="FZ33" t="s">
-        <v>5326</v>
-      </c>
-      <c r="GA33" t="s">
-        <v>5327</v>
-      </c>
-      <c r="GB33" t="s">
-        <v>5328</v>
-      </c>
-      <c r="GC33" t="s">
-        <v>5329</v>
-      </c>
-      <c r="GD33" t="s">
-        <v>5330</v>
-      </c>
-      <c r="GE33" t="s">
-        <v>5331</v>
-      </c>
-      <c r="GF33" t="s">
-        <v>5332</v>
-      </c>
-      <c r="GG33" t="s">
-        <v>5333</v>
-      </c>
-      <c r="GH33" t="s">
-        <v>2185</v>
-      </c>
-      <c r="GI33" t="s">
-        <v>5334</v>
-      </c>
-      <c r="GJ33" t="s">
-        <v>5335</v>
-      </c>
-      <c r="GK33" t="s">
-        <v>5336</v>
-      </c>
-      <c r="GL33" t="s">
-        <v>5337</v>
-      </c>
-      <c r="GM33" t="s">
-        <v>5338</v>
-      </c>
-      <c r="GN33" t="s">
-        <v>555</v>
-      </c>
-      <c r="GO33" t="s">
-        <v>5339</v>
-      </c>
-      <c r="GP33" t="s">
-        <v>5340</v>
-      </c>
-      <c r="GQ33" t="s">
-        <v>1542</v>
-      </c>
-      <c r="GR33" t="s">
-        <v>5341</v>
-      </c>
-      <c r="GS33" t="s">
-        <v>5342</v>
-      </c>
-      <c r="GT33" t="s">
-        <v>3866</v>
-      </c>
-      <c r="GU33" t="s">
-        <v>5343</v>
-      </c>
-      <c r="GV33" t="s">
-        <v>5344</v>
-      </c>
-      <c r="GW33" t="s">
-        <v>5345</v>
-      </c>
-      <c r="GX33" t="s">
-        <v>5346</v>
-      </c>
-      <c r="GY33" t="s">
-        <v>5347</v>
-      </c>
-      <c r="GZ33" t="s">
-        <v>5348</v>
-      </c>
-      <c r="HA33" t="s">
-        <v>5349</v>
-      </c>
-      <c r="HB33" t="s">
-        <v>5350</v>
-      </c>
-      <c r="HC33" t="s">
-        <v>495</v>
-      </c>
-      <c r="HD33" t="s">
-        <v>4456</v>
-      </c>
-      <c r="HE33" t="s">
-        <v>5351</v>
-      </c>
-      <c r="HF33" t="s">
-        <v>5352</v>
-      </c>
-      <c r="HG33" t="s">
-        <v>5353</v>
-      </c>
-      <c r="HH33" t="s">
-        <v>5060</v>
-      </c>
-      <c r="HI33" t="s">
-        <v>5354</v>
-      </c>
-      <c r="HJ33" t="s">
-        <v>5355</v>
-      </c>
-      <c r="HK33" t="s">
-        <v>5356</v>
-      </c>
-      <c r="HL33" t="s">
-        <v>5357</v>
-      </c>
-      <c r="HM33" t="s">
-        <v>5358</v>
-      </c>
-      <c r="HN33" t="s">
-        <v>5359</v>
-      </c>
-      <c r="HO33" t="s">
-        <v>5360</v>
-      </c>
-      <c r="HP33" t="s">
-        <v>5361</v>
-      </c>
-      <c r="HQ33" t="s">
-        <v>5362</v>
-      </c>
-      <c r="HR33" t="s">
-        <v>5363</v>
-      </c>
-      <c r="HS33" t="s">
-        <v>5364</v>
-      </c>
-      <c r="HT33" t="s">
-        <v>1182</v>
-      </c>
-      <c r="HU33" t="s">
-        <v>1253</v>
-      </c>
-      <c r="HV33" t="s">
-        <v>4200</v>
-      </c>
-      <c r="HW33" t="s">
-        <v>612</v>
-      </c>
-      <c r="HX33" t="s">
-        <v>5365</v>
-      </c>
-      <c r="HY33" t="s">
-        <v>5366</v>
-      </c>
-      <c r="HZ33" t="s">
-        <v>590</v>
-      </c>
-      <c r="IA33" t="s">
-        <v>1300</v>
-      </c>
-      <c r="IB33" t="s">
-        <v>5367</v>
-      </c>
-      <c r="IC33" t="s">
-        <v>5368</v>
-      </c>
-      <c r="ID33" t="s">
-        <v>5369</v>
-      </c>
-      <c r="IE33" t="s">
-        <v>5370</v>
-      </c>
-      <c r="IF33" t="s">
-        <v>5371</v>
-      </c>
-      <c r="IG33" t="s">
-        <v>5372</v>
-      </c>
-      <c r="IH33" t="s">
-        <v>1167</v>
-      </c>
-      <c r="II33" t="s">
-        <v>5373</v>
-      </c>
-      <c r="IJ33" t="s">
-        <v>5374</v>
-      </c>
-      <c r="IK33" t="s">
-        <v>5375</v>
-      </c>
-      <c r="IL33" t="s">
-        <v>5376</v>
-      </c>
-      <c r="IM33" t="s">
-        <v>4223</v>
-      </c>
-      <c r="IN33" t="s">
-        <v>5377</v>
-      </c>
-      <c r="IO33" t="s">
-        <v>5378</v>
-      </c>
-      <c r="IP33" t="s">
-        <v>5379</v>
-      </c>
-      <c r="IQ33" t="s">
-        <v>5380</v>
-      </c>
-      <c r="IR33" t="s">
-        <v>5381</v>
-      </c>
-      <c r="IS33" t="s">
-        <v>427</v>
-      </c>
-      <c r="IT33" t="s">
-        <v>529</v>
-      </c>
-      <c r="IU33" t="s">
-        <v>4009</v>
-      </c>
-      <c r="IV33" t="s">
-        <v>509</v>
-      </c>
-      <c r="IW33" t="s">
-        <v>5382</v>
-      </c>
-      <c r="IX33" t="s">
-        <v>5383</v>
-      </c>
-      <c r="IY33" t="s">
-        <v>416</v>
-      </c>
-      <c r="IZ33" t="s">
-        <v>5384</v>
-      </c>
-      <c r="JA33" t="s">
-        <v>5385</v>
-      </c>
-      <c r="JB33" t="s">
-        <v>5386</v>
-      </c>
-      <c r="JC33" t="s">
-        <v>5387</v>
-      </c>
-      <c r="JD33" t="s">
-        <v>5388</v>
-      </c>
-      <c r="JE33" t="s">
-        <v>5389</v>
-      </c>
-      <c r="JF33" t="s">
-        <v>5390</v>
-      </c>
-      <c r="JG33" t="s">
-        <v>5165</v>
-      </c>
-      <c r="JH33" t="s">
-        <v>5391</v>
-      </c>
-      <c r="JI33" t="s">
-        <v>5392</v>
-      </c>
-      <c r="JJ33" t="s">
-        <v>3925</v>
-      </c>
-      <c r="JK33" t="s">
-        <v>5393</v>
-      </c>
-      <c r="JL33" t="s">
-        <v>1304</v>
-      </c>
-      <c r="JM33" t="s">
-        <v>5394</v>
-      </c>
-      <c r="JN33" t="s">
-        <v>3310</v>
-      </c>
-      <c r="JO33" t="s">
-        <v>5395</v>
-      </c>
-      <c r="JP33" t="s">
-        <v>5396</v>
-      </c>
-      <c r="JQ33" t="s">
-        <v>5397</v>
-      </c>
-      <c r="JR33" t="s">
-        <v>5398</v>
-      </c>
-      <c r="JS33" t="s">
-        <v>5399</v>
-      </c>
-      <c r="JT33" t="s">
-        <v>5400</v>
-      </c>
-      <c r="JU33" t="s">
-        <v>5401</v>
-      </c>
-      <c r="JV33" t="s">
-        <v>5402</v>
-      </c>
-      <c r="JW33" t="s">
-        <v>5403</v>
-      </c>
-      <c r="JX33" t="s">
-        <v>5404</v>
-      </c>
-      <c r="JY33" t="s">
-        <v>5405</v>
-      </c>
-      <c r="JZ33" t="s">
-        <v>5406</v>
-      </c>
-      <c r="KA33" t="s">
-        <v>5407</v>
-      </c>
-      <c r="KB33" t="s">
-        <v>5408</v>
-      </c>
-      <c r="KC33" t="s">
-        <v>5409</v>
-      </c>
-      <c r="KD33" t="s">
-        <v>5410</v>
-      </c>
-      <c r="KE33" t="s">
-        <v>5411</v>
-      </c>
-      <c r="KF33" t="s">
-        <v>5412</v>
-      </c>
-      <c r="KG33" t="s">
-        <v>1945</v>
-      </c>
-      <c r="KH33" t="s">
-        <v>5413</v>
-      </c>
-      <c r="KI33" t="s">
-        <v>5414</v>
-      </c>
-      <c r="KJ33" t="s">
-        <v>5415</v>
-      </c>
-      <c r="KK33" t="s">
-        <v>2112</v>
-      </c>
-      <c r="KL33" t="s">
-        <v>5416</v>
-      </c>
-      <c r="KM33" t="s">
-        <v>5417</v>
-      </c>
-      <c r="KN33" t="s">
-        <v>5418</v>
-      </c>
-      <c r="KO33" t="s">
-        <v>4038</v>
-      </c>
-      <c r="KP33" t="s">
-        <v>1625</v>
-      </c>
-      <c r="KQ33" t="s">
-        <v>5419</v>
-      </c>
-      <c r="KR33" t="s">
-        <v>5420</v>
-      </c>
-      <c r="KS33" t="s">
-        <v>1613</v>
-      </c>
-      <c r="KT33" t="s">
-        <v>5421</v>
-      </c>
-      <c r="KU33" t="s">
-        <v>4884</v>
-      </c>
-      <c r="KV33" t="s">
-        <v>4077</v>
-      </c>
-      <c r="KW33" t="s">
-        <v>1740</v>
-      </c>
-      <c r="KX33" t="s">
-        <v>5422</v>
-      </c>
-    </row>
-    <row r="34" spans="1:310">
-      <c r="A34" t="s">
-        <v>5423</v>
-      </c>
-      <c r="B34" t="s">
-        <v>5424</v>
-      </c>
-      <c r="C34" t="s">
-        <v>5425</v>
-      </c>
-      <c r="D34" t="s">
-        <v>5426</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5427</v>
-      </c>
-      <c r="F34" t="s">
-        <v>5428</v>
-      </c>
-      <c r="G34" t="s">
-        <v>5429</v>
-      </c>
-      <c r="H34" t="s">
-        <v>5430</v>
-      </c>
-      <c r="I34" t="s">
-        <v>5431</v>
-      </c>
-      <c r="J34" t="s">
-        <v>5432</v>
-      </c>
-      <c r="K34" t="s">
-        <v>5433</v>
-      </c>
-      <c r="L34" t="s">
-        <v>5434</v>
-      </c>
-      <c r="M34" t="s">
-        <v>4276</v>
-      </c>
-      <c r="N34" t="s">
-        <v>5435</v>
-      </c>
-      <c r="O34" t="s">
-        <v>3777</v>
-      </c>
-      <c r="P34" t="s">
-        <v>1314</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>5436</v>
-      </c>
-      <c r="R34" t="s">
-        <v>5437</v>
-      </c>
-      <c r="S34" t="s">
-        <v>5438</v>
-      </c>
-      <c r="T34" t="s">
-        <v>3449</v>
-      </c>
-      <c r="U34" t="s">
-        <v>3390</v>
-      </c>
-      <c r="V34" t="s">
-        <v>4692</v>
-      </c>
-      <c r="W34" t="s">
-        <v>5439</v>
-      </c>
-      <c r="X34" t="s">
-        <v>480</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>5440</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>5441</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>5442</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>5443</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>5444</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>5017</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>5445</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>5446</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>5447</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>443</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>4580</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>5448</v>
-      </c>
-      <c r="AK34" t="s">
-        <v>5449</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>5450</v>
-      </c>
-      <c r="AM34" t="s">
-        <v>803</v>
-      </c>
-      <c r="AN34" t="s">
-        <v>5451</v>
-      </c>
-      <c r="AO34" t="s">
-        <v>5452</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>5245</v>
-      </c>
-      <c r="AQ34" t="s">
-        <v>5453</v>
-      </c>
-      <c r="AR34" t="s">
-        <v>1123</v>
-      </c>
-      <c r="AS34" t="s">
-        <v>5454</v>
-      </c>
-      <c r="AT34" t="s">
-        <v>5455</v>
-      </c>
-      <c r="AU34" t="s">
-        <v>5456</v>
-      </c>
-      <c r="AV34" t="s">
-        <v>5457</v>
-      </c>
-      <c r="AW34" t="s">
-        <v>1888</v>
-      </c>
-      <c r="AX34" t="s">
-        <v>2544</v>
-      </c>
-      <c r="AY34" t="s">
-        <v>5458</v>
-      </c>
-      <c r="AZ34" t="s">
-        <v>5459</v>
-      </c>
-      <c r="BA34" t="s">
-        <v>5460</v>
-      </c>
-      <c r="BB34" t="s">
-        <v>5461</v>
-      </c>
-      <c r="BC34" t="s">
-        <v>5462</v>
-      </c>
-      <c r="BD34" t="s">
-        <v>5463</v>
-      </c>
-      <c r="BE34" t="s">
-        <v>5464</v>
-      </c>
-      <c r="BF34" t="s">
-        <v>5465</v>
-      </c>
-      <c r="BG34" t="s">
-        <v>1523</v>
-      </c>
-      <c r="BH34" t="s">
-        <v>5466</v>
-      </c>
-      <c r="BI34" t="s">
-        <v>4963</v>
-      </c>
-      <c r="BJ34" t="s">
-        <v>5467</v>
-      </c>
-      <c r="BK34" t="s">
-        <v>4698</v>
-      </c>
-      <c r="BL34" t="s">
-        <v>5468</v>
-      </c>
-      <c r="BM34" t="s">
-        <v>5469</v>
-      </c>
-      <c r="BN34" t="s">
-        <v>5470</v>
-      </c>
-      <c r="BO34" t="s">
-        <v>3307</v>
-      </c>
-      <c r="BP34" t="s">
-        <v>5471</v>
-      </c>
-      <c r="BQ34" t="s">
-        <v>5472</v>
-      </c>
-      <c r="BR34" t="s">
-        <v>2490</v>
-      </c>
-      <c r="BS34" t="s">
-        <v>5473</v>
-      </c>
-      <c r="BT34" t="s">
-        <v>5474</v>
-      </c>
-      <c r="BU34" t="s">
-        <v>5475</v>
-      </c>
-      <c r="BV34" t="s">
-        <v>5476</v>
-      </c>
-      <c r="BW34" t="s">
-        <v>5477</v>
-      </c>
-      <c r="BX34" t="s">
-        <v>1376</v>
-      </c>
-      <c r="BY34" t="s">
-        <v>2233</v>
-      </c>
-      <c r="BZ34" t="s">
-        <v>5478</v>
-      </c>
-      <c r="CA34" t="s">
-        <v>5479</v>
-      </c>
-      <c r="CB34" t="s">
-        <v>5480</v>
-      </c>
-      <c r="CC34" t="s">
-        <v>3953</v>
-      </c>
-      <c r="CD34" t="s">
-        <v>5481</v>
-      </c>
-      <c r="CE34" t="s">
-        <v>5482</v>
-      </c>
-      <c r="CF34" t="s">
-        <v>5483</v>
-      </c>
-      <c r="CG34" t="s">
-        <v>5484</v>
-      </c>
-      <c r="CH34" t="s">
-        <v>5485</v>
-      </c>
-      <c r="CI34" t="s">
-        <v>478</v>
-      </c>
-      <c r="CJ34" t="s">
-        <v>501</v>
-      </c>
-      <c r="CK34" t="s">
-        <v>5486</v>
-      </c>
-      <c r="CL34" t="s">
-        <v>3227</v>
-      </c>
-      <c r="CM34" t="s">
-        <v>5487</v>
-      </c>
-      <c r="CN34" t="s">
-        <v>5488</v>
-      </c>
-      <c r="CO34" t="s">
-        <v>820</v>
-      </c>
-      <c r="CP34" t="s">
-        <v>5489</v>
-      </c>
-      <c r="CQ34" t="s">
-        <v>5333</v>
-      </c>
-      <c r="CR34" t="s">
-        <v>4156</v>
-      </c>
-      <c r="CS34" t="s">
-        <v>5490</v>
-      </c>
-      <c r="CT34" t="s">
-        <v>5491</v>
-      </c>
-      <c r="CU34" t="s">
-        <v>5492</v>
-      </c>
-      <c r="CV34" t="s">
-        <v>5493</v>
-      </c>
-      <c r="CW34" t="s">
-        <v>5494</v>
-      </c>
-      <c r="CX34" t="s">
-        <v>5495</v>
-      </c>
-      <c r="CY34" t="s">
-        <v>5496</v>
-      </c>
-      <c r="CZ34" t="s">
-        <v>5497</v>
-      </c>
-      <c r="DA34" t="s">
-        <v>5498</v>
-      </c>
-      <c r="DB34" t="s">
-        <v>5499</v>
-      </c>
-      <c r="DC34" t="s">
-        <v>1138</v>
-      </c>
-      <c r="DD34" t="s">
-        <v>5500</v>
-      </c>
-      <c r="DE34" t="s">
-        <v>5501</v>
-      </c>
-      <c r="DF34" t="s">
-        <v>5502</v>
-      </c>
-      <c r="DG34" t="s">
-        <v>4966</v>
-      </c>
-      <c r="DH34" t="s">
-        <v>797</v>
-      </c>
-      <c r="DI34" t="s">
-        <v>5503</v>
-      </c>
-      <c r="DJ34" t="s">
-        <v>907</v>
-      </c>
-      <c r="DK34" t="s">
-        <v>4453</v>
-      </c>
-      <c r="DL34" t="s">
-        <v>5086</v>
-      </c>
-      <c r="DM34" t="s">
-        <v>2834</v>
-      </c>
-      <c r="DN34" t="s">
-        <v>5504</v>
-      </c>
-      <c r="DO34" t="s">
-        <v>5505</v>
-      </c>
-      <c r="DP34" t="s">
-        <v>5506</v>
-      </c>
-      <c r="DQ34" t="s">
-        <v>5003</v>
-      </c>
-      <c r="DR34" t="s">
-        <v>1894</v>
-      </c>
-      <c r="DS34" t="s">
-        <v>5507</v>
-      </c>
-      <c r="DT34" t="s">
-        <v>5508</v>
-      </c>
-      <c r="DU34" t="s">
-        <v>5509</v>
-      </c>
-      <c r="DV34" t="s">
-        <v>4441</v>
-      </c>
-      <c r="DW34" t="s">
-        <v>450</v>
-      </c>
-      <c r="DX34" t="s">
-        <v>5510</v>
-      </c>
-      <c r="DY34" t="s">
-        <v>5511</v>
-      </c>
-      <c r="DZ34" t="s">
-        <v>5512</v>
-      </c>
-      <c r="EA34" t="s">
-        <v>5513</v>
-      </c>
-      <c r="EB34" t="s">
-        <v>5514</v>
-      </c>
-      <c r="EC34" t="s">
-        <v>5515</v>
-      </c>
-      <c r="ED34" t="s">
-        <v>5516</v>
-      </c>
-      <c r="EE34" t="s">
-        <v>5517</v>
-      </c>
-      <c r="EF34" t="s">
-        <v>5518</v>
-      </c>
-      <c r="EG34" t="s">
-        <v>5519</v>
-      </c>
-      <c r="EH34" t="s">
-        <v>5520</v>
-      </c>
-      <c r="EI34" t="s">
-        <v>5521</v>
-      </c>
-      <c r="EJ34" t="s">
-        <v>1436</v>
-      </c>
-      <c r="EK34" t="s">
-        <v>5522</v>
-      </c>
-      <c r="EL34" t="s">
-        <v>2231</v>
-      </c>
-      <c r="EM34" t="s">
-        <v>5523</v>
-      </c>
-      <c r="EN34" t="s">
-        <v>5524</v>
-      </c>
-      <c r="EO34" t="s">
-        <v>5525</v>
-      </c>
-      <c r="EP34" t="s">
-        <v>5526</v>
-      </c>
-      <c r="EQ34" t="s">
-        <v>5527</v>
-      </c>
-      <c r="ER34" t="s">
-        <v>5528</v>
-      </c>
-      <c r="ES34" t="s">
-        <v>5529</v>
-      </c>
-      <c r="ET34" t="s">
-        <v>5530</v>
-      </c>
-      <c r="EU34" t="s">
-        <v>5531</v>
-      </c>
-      <c r="EV34" t="s">
-        <v>2899</v>
-      </c>
-      <c r="EW34" t="s">
-        <v>5532</v>
-      </c>
-      <c r="EX34" t="s">
-        <v>5533</v>
-      </c>
-      <c r="EY34" t="s">
-        <v>5534</v>
-      </c>
-      <c r="EZ34" t="s">
-        <v>5535</v>
-      </c>
-      <c r="FA34" t="s">
-        <v>5536</v>
-      </c>
-      <c r="FB34" t="s">
-        <v>5537</v>
-      </c>
-      <c r="FC34" t="s">
-        <v>4191</v>
-      </c>
-      <c r="FD34" t="s">
-        <v>5538</v>
-      </c>
-      <c r="FE34" t="s">
-        <v>5539</v>
-      </c>
-      <c r="FF34" t="s">
-        <v>4907</v>
-      </c>
-      <c r="FG34" t="s">
-        <v>5540</v>
-      </c>
-      <c r="FH34" t="s">
-        <v>5541</v>
-      </c>
-      <c r="FI34" t="s">
-        <v>5542</v>
-      </c>
-      <c r="FJ34" t="s">
-        <v>5543</v>
-      </c>
-      <c r="FK34" t="s">
-        <v>5544</v>
-      </c>
-      <c r="FL34" t="s">
-        <v>5545</v>
-      </c>
-      <c r="FM34" t="s">
-        <v>1285</v>
-      </c>
-      <c r="FN34" t="s">
-        <v>2365</v>
-      </c>
-      <c r="FO34" t="s">
-        <v>2125</v>
-      </c>
-      <c r="FP34" t="s">
-        <v>5546</v>
-      </c>
-      <c r="FQ34" t="s">
-        <v>5547</v>
-      </c>
-      <c r="FR34" t="s">
-        <v>1368</v>
-      </c>
-      <c r="FS34" t="s">
-        <v>5548</v>
-      </c>
-      <c r="FT34" t="s">
-        <v>1607</v>
-      </c>
-      <c r="FU34" t="s">
-        <v>5549</v>
-      </c>
-      <c r="FV34" t="s">
-        <v>5550</v>
-      </c>
-      <c r="FW34" t="s">
-        <v>3800</v>
-      </c>
-      <c r="FX34" t="s">
-        <v>5551</v>
-      </c>
-      <c r="FY34" t="s">
-        <v>5552</v>
-      </c>
-      <c r="FZ34" t="s">
-        <v>5553</v>
-      </c>
-      <c r="GA34" t="s">
-        <v>5554</v>
-      </c>
-      <c r="GB34" t="s">
-        <v>5555</v>
-      </c>
-      <c r="GC34" t="s">
-        <v>5314</v>
-      </c>
-      <c r="GD34" t="s">
-        <v>3916</v>
-      </c>
-      <c r="GE34" t="s">
-        <v>5556</v>
-      </c>
-      <c r="GF34" t="s">
-        <v>5557</v>
-      </c>
-      <c r="GG34" t="s">
-        <v>5558</v>
-      </c>
-      <c r="GH34" t="s">
-        <v>2887</v>
-      </c>
-      <c r="GI34" t="s">
-        <v>5559</v>
-      </c>
-      <c r="GJ34" t="s">
-        <v>5560</v>
-      </c>
-      <c r="GK34" t="s">
-        <v>5561</v>
-      </c>
-      <c r="GL34" t="s">
-        <v>5562</v>
-      </c>
-      <c r="GM34" t="s">
-        <v>5563</v>
-      </c>
-      <c r="GN34" t="s">
-        <v>2544</v>
-      </c>
-      <c r="GO34" t="s">
-        <v>5564</v>
-      </c>
-      <c r="GP34" t="s">
-        <v>5565</v>
-      </c>
-      <c r="GQ34" t="s">
-        <v>5566</v>
-      </c>
-      <c r="GR34" t="s">
-        <v>5567</v>
-      </c>
-      <c r="GS34" t="s">
-        <v>5568</v>
-      </c>
-      <c r="GT34" t="s">
-        <v>5569</v>
-      </c>
-      <c r="GU34" t="s">
-        <v>5570</v>
-      </c>
-      <c r="GV34" t="s">
-        <v>5571</v>
-      </c>
-      <c r="GW34" t="s">
-        <v>5572</v>
-      </c>
-      <c r="GX34" t="s">
-        <v>5573</v>
-      </c>
-      <c r="GY34" t="s">
-        <v>5574</v>
-      </c>
-      <c r="GZ34" t="s">
-        <v>5575</v>
-      </c>
-      <c r="HA34" t="s">
-        <v>5576</v>
-      </c>
-      <c r="HB34" t="s">
-        <v>5308</v>
-      </c>
-      <c r="HC34" t="s">
-        <v>458</v>
-      </c>
-      <c r="HD34" t="s">
-        <v>1317</v>
-      </c>
-      <c r="HE34" t="s">
-        <v>5577</v>
-      </c>
-      <c r="HF34" t="s">
-        <v>5578</v>
-      </c>
-      <c r="HG34" t="s">
-        <v>5579</v>
-      </c>
-      <c r="HH34" t="s">
-        <v>5580</v>
-      </c>
-      <c r="HI34" t="s">
-        <v>5581</v>
-      </c>
-      <c r="HJ34" t="s">
-        <v>5582</v>
-      </c>
-      <c r="HK34" t="s">
-        <v>5583</v>
-      </c>
-      <c r="HL34" t="s">
-        <v>5584</v>
-      </c>
-      <c r="HM34" t="s">
-        <v>5585</v>
-      </c>
-      <c r="HN34" t="s">
-        <v>5586</v>
-      </c>
-      <c r="HO34" t="s">
-        <v>5587</v>
-      </c>
-      <c r="HP34" t="s">
-        <v>5588</v>
-      </c>
-      <c r="HQ34" t="s">
-        <v>5589</v>
-      </c>
-      <c r="HR34" t="s">
-        <v>5590</v>
-      </c>
-      <c r="HS34" t="s">
-        <v>5591</v>
-      </c>
-      <c r="HT34" t="s">
-        <v>5592</v>
-      </c>
-      <c r="HU34" t="s">
-        <v>1479</v>
-      </c>
-      <c r="HV34" t="s">
-        <v>5593</v>
-      </c>
-      <c r="HW34" t="s">
-        <v>697</v>
-      </c>
-      <c r="HX34" t="s">
-        <v>5594</v>
-      </c>
-      <c r="HY34" t="s">
-        <v>5595</v>
-      </c>
-      <c r="HZ34" t="s">
-        <v>629</v>
-      </c>
-      <c r="IA34" t="s">
-        <v>5596</v>
-      </c>
-      <c r="IB34" t="s">
-        <v>5597</v>
-      </c>
-      <c r="IC34" t="s">
-        <v>5458</v>
-      </c>
-      <c r="ID34" t="s">
-        <v>2093</v>
-      </c>
-      <c r="IE34" t="s">
-        <v>5598</v>
-      </c>
-      <c r="IF34" t="s">
-        <v>5599</v>
-      </c>
-      <c r="IG34" t="s">
-        <v>5600</v>
-      </c>
-      <c r="IH34" t="s">
-        <v>5601</v>
-      </c>
-      <c r="II34" t="s">
-        <v>5602</v>
-      </c>
-      <c r="IJ34" t="s">
-        <v>5603</v>
-      </c>
-      <c r="IK34" t="s">
-        <v>5604</v>
-      </c>
-      <c r="IL34" t="s">
-        <v>5586</v>
-      </c>
-      <c r="IM34" t="s">
-        <v>5548</v>
-      </c>
-      <c r="IN34" t="s">
-        <v>5605</v>
-      </c>
-      <c r="IO34" t="s">
-        <v>5606</v>
-      </c>
-      <c r="IP34" t="s">
-        <v>5607</v>
-      </c>
-      <c r="IQ34" t="s">
-        <v>431</v>
-      </c>
-      <c r="IR34" t="s">
-        <v>5608</v>
-      </c>
-      <c r="IS34" t="s">
-        <v>367</v>
-      </c>
-      <c r="IT34" t="s">
-        <v>3552</v>
-      </c>
-      <c r="IU34" t="s">
-        <v>4792</v>
-      </c>
-      <c r="IV34" t="s">
-        <v>486</v>
-      </c>
-      <c r="IW34" t="s">
-        <v>4457</v>
-      </c>
-      <c r="IX34" t="s">
-        <v>5609</v>
-      </c>
-      <c r="IY34" t="s">
-        <v>722</v>
-      </c>
-      <c r="IZ34" t="s">
-        <v>3461</v>
-      </c>
-      <c r="JA34" t="s">
-        <v>5610</v>
-      </c>
-      <c r="JB34" t="s">
-        <v>5611</v>
-      </c>
-      <c r="JC34" t="s">
-        <v>5612</v>
-      </c>
-      <c r="JD34" t="s">
-        <v>5613</v>
-      </c>
-      <c r="JE34" t="s">
-        <v>5614</v>
-      </c>
-      <c r="JF34" t="s">
-        <v>5615</v>
-      </c>
-      <c r="JG34" t="s">
-        <v>944</v>
-      </c>
-      <c r="JH34" t="s">
-        <v>5616</v>
-      </c>
-      <c r="JI34" t="s">
-        <v>5617</v>
-      </c>
-      <c r="JJ34" t="s">
-        <v>5618</v>
-      </c>
-      <c r="JK34" t="s">
-        <v>5619</v>
-      </c>
-      <c r="JL34" t="s">
-        <v>1599</v>
-      </c>
-      <c r="JM34" t="s">
-        <v>5620</v>
-      </c>
-      <c r="JN34" t="s">
-        <v>4760</v>
-      </c>
-      <c r="JO34" t="s">
-        <v>5621</v>
-      </c>
-      <c r="JP34" t="s">
-        <v>5622</v>
-      </c>
-      <c r="JQ34" t="s">
-        <v>5623</v>
-      </c>
-      <c r="JR34" t="s">
-        <v>5624</v>
-      </c>
-      <c r="JS34" t="s">
-        <v>5625</v>
-      </c>
-      <c r="JT34" t="s">
-        <v>5626</v>
-      </c>
-      <c r="JU34" t="s">
-        <v>5627</v>
-      </c>
-      <c r="JV34" t="s">
-        <v>3890</v>
-      </c>
-      <c r="JW34" t="s">
-        <v>5628</v>
-      </c>
-      <c r="JX34" t="s">
-        <v>5629</v>
-      </c>
-      <c r="JY34" t="s">
-        <v>5630</v>
-      </c>
-      <c r="JZ34" t="s">
-        <v>5631</v>
-      </c>
-      <c r="KA34" t="s">
-        <v>5632</v>
-      </c>
-      <c r="KB34" t="s">
-        <v>5633</v>
-      </c>
-      <c r="KC34" t="s">
-        <v>5634</v>
-      </c>
-      <c r="KD34" t="s">
-        <v>5635</v>
-      </c>
-      <c r="KE34" t="s">
-        <v>5636</v>
-      </c>
-      <c r="KF34" t="s">
-        <v>3448</v>
-      </c>
-      <c r="KG34" t="s">
-        <v>5637</v>
-      </c>
-      <c r="KH34" t="s">
-        <v>5638</v>
-      </c>
-      <c r="KI34" t="s">
-        <v>5639</v>
-      </c>
-      <c r="KJ34" t="s">
-        <v>5005</v>
-      </c>
-      <c r="KK34" t="s">
-        <v>1290</v>
-      </c>
-      <c r="KL34" t="s">
-        <v>5640</v>
-      </c>
-      <c r="KM34" t="s">
-        <v>5641</v>
-      </c>
-      <c r="KN34" t="s">
-        <v>5642</v>
-      </c>
-      <c r="KO34" t="s">
-        <v>5643</v>
-      </c>
-      <c r="KP34" t="s">
-        <v>5644</v>
-      </c>
-      <c r="KQ34" t="s">
-        <v>2193</v>
-      </c>
-      <c r="KR34" t="s">
-        <v>5645</v>
-      </c>
-      <c r="KS34" t="s">
-        <v>3435</v>
-      </c>
-      <c r="KT34" t="s">
-        <v>3331</v>
-      </c>
-      <c r="KU34" t="s">
-        <v>5646</v>
-      </c>
-      <c r="KV34" t="s">
-        <v>2425</v>
-      </c>
-      <c r="KW34" t="s">
-        <v>1012</v>
-      </c>
-      <c r="KX34" t="s">
-        <v>3841</v>
-      </c>
-    </row>
-    <row r="35" spans="1:310">
-      <c r="A35" t="s">
-        <v>5647</v>
-      </c>
-      <c r="B35" t="s">
-        <v>5648</v>
-      </c>
-      <c r="C35" t="s">
-        <v>5649</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2994</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5650</v>
-      </c>
-      <c r="F35" t="s">
-        <v>5651</v>
-      </c>
-      <c r="G35" t="s">
-        <v>5652</v>
-      </c>
-      <c r="H35" t="s">
-        <v>5653</v>
-      </c>
-      <c r="I35" t="s">
-        <v>5654</v>
-      </c>
-      <c r="J35" t="s">
-        <v>5655</v>
-      </c>
-      <c r="K35" t="s">
-        <v>5656</v>
-      </c>
-      <c r="L35" t="s">
-        <v>5657</v>
-      </c>
-      <c r="M35" t="s">
-        <v>5658</v>
-      </c>
-      <c r="N35" t="s">
-        <v>5659</v>
-      </c>
-      <c r="O35" t="s">
-        <v>5660</v>
-      </c>
-      <c r="P35" t="s">
-        <v>4062</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>3016</v>
-      </c>
-      <c r="R35" t="s">
-        <v>5661</v>
-      </c>
-      <c r="S35" t="s">
-        <v>5662</v>
-      </c>
-      <c r="T35" t="s">
-        <v>633</v>
-      </c>
-      <c r="U35" t="s">
-        <v>5663</v>
-      </c>
-      <c r="V35" t="s">
-        <v>1601</v>
-      </c>
-      <c r="W35" t="s">
-        <v>5664</v>
-      </c>
-      <c r="X35" t="s">
-        <v>454</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>2169</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>5665</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>5666</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>5667</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>1437</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>5668</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>5669</v>
-      </c>
-      <c r="AF35" t="s">
-        <v>5670</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>5671</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>3325</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>5672</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>1969</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>5673</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>5674</v>
-      </c>
-      <c r="AM35" t="s">
-        <v>582</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>5675</v>
-      </c>
-      <c r="AO35" t="s">
-        <v>5676</v>
-      </c>
-      <c r="AP35" t="s">
-        <v>5677</v>
-      </c>
-      <c r="AQ35" t="s">
-        <v>5678</v>
-      </c>
-      <c r="AR35" t="s">
-        <v>2291</v>
-      </c>
-      <c r="AS35" t="s">
-        <v>5679</v>
-      </c>
-      <c r="AT35" t="s">
-        <v>5680</v>
-      </c>
-      <c r="AU35" t="s">
-        <v>5681</v>
-      </c>
-      <c r="AV35" t="s">
-        <v>5682</v>
-      </c>
-      <c r="AW35" t="s">
-        <v>5683</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>590</v>
-      </c>
-      <c r="AY35" t="s">
-        <v>5684</v>
-      </c>
-      <c r="AZ35" t="s">
-        <v>5685</v>
-      </c>
-      <c r="BA35" t="s">
-        <v>5686</v>
-      </c>
-      <c r="BB35" t="s">
-        <v>5687</v>
-      </c>
-      <c r="BC35" t="s">
-        <v>5688</v>
-      </c>
-      <c r="BD35" t="s">
-        <v>741</v>
-      </c>
-      <c r="BE35" t="s">
-        <v>5689</v>
-      </c>
-      <c r="BF35" t="s">
-        <v>5690</v>
-      </c>
-      <c r="BG35" t="s">
-        <v>5691</v>
-      </c>
-      <c r="BH35" t="s">
-        <v>5692</v>
-      </c>
-      <c r="BI35" t="s">
-        <v>5693</v>
-      </c>
-      <c r="BJ35" t="s">
-        <v>5694</v>
-      </c>
-      <c r="BK35" t="s">
-        <v>494</v>
-      </c>
-      <c r="BL35" t="s">
-        <v>5591</v>
-      </c>
-      <c r="BM35" t="s">
-        <v>5695</v>
-      </c>
-      <c r="BN35" t="s">
-        <v>5696</v>
-      </c>
-      <c r="BO35" t="s">
-        <v>5697</v>
-      </c>
-      <c r="BP35" t="s">
-        <v>5698</v>
-      </c>
-      <c r="BQ35" t="s">
-        <v>5699</v>
-      </c>
-      <c r="BR35" t="s">
-        <v>5700</v>
-      </c>
-      <c r="BS35" t="s">
-        <v>5701</v>
-      </c>
-      <c r="BT35" t="s">
-        <v>4987</v>
-      </c>
-      <c r="BU35" t="s">
-        <v>5702</v>
-      </c>
-      <c r="BV35" t="s">
-        <v>5703</v>
-      </c>
-      <c r="BW35" t="s">
-        <v>5704</v>
-      </c>
-      <c r="BX35" t="s">
-        <v>5705</v>
-      </c>
-      <c r="BY35" t="s">
-        <v>5706</v>
-      </c>
-      <c r="BZ35" t="s">
-        <v>1180</v>
-      </c>
-      <c r="CA35" t="s">
-        <v>3926</v>
-      </c>
-      <c r="CB35" t="s">
-        <v>5707</v>
-      </c>
-      <c r="CC35" t="s">
-        <v>5708</v>
-      </c>
-      <c r="CD35" t="s">
-        <v>5709</v>
-      </c>
-      <c r="CE35" t="s">
-        <v>5710</v>
-      </c>
-      <c r="CF35" t="s">
-        <v>5711</v>
-      </c>
-      <c r="CG35" t="s">
-        <v>5712</v>
-      </c>
-      <c r="CH35" t="s">
-        <v>1686</v>
-      </c>
-      <c r="CI35" t="s">
-        <v>416</v>
-      </c>
-      <c r="CJ35" t="s">
-        <v>464</v>
-      </c>
-      <c r="CK35" t="s">
-        <v>3641</v>
-      </c>
-      <c r="CL35" t="s">
-        <v>3040</v>
-      </c>
-      <c r="CM35" t="s">
-        <v>5713</v>
-      </c>
-      <c r="CN35" t="s">
-        <v>5714</v>
-      </c>
-      <c r="CO35" t="s">
-        <v>2328</v>
-      </c>
-      <c r="CP35" t="s">
-        <v>5715</v>
-      </c>
-      <c r="CQ35" t="s">
-        <v>5716</v>
-      </c>
-      <c r="CR35" t="s">
-        <v>3308</v>
-      </c>
-      <c r="CS35" t="s">
-        <v>5717</v>
-      </c>
-      <c r="CT35" t="s">
-        <v>5718</v>
-      </c>
-      <c r="CU35" t="s">
-        <v>5719</v>
-      </c>
-      <c r="CV35" t="s">
-        <v>4593</v>
-      </c>
-      <c r="CW35" t="s">
-        <v>4301</v>
-      </c>
-      <c r="CX35" t="s">
-        <v>5720</v>
-      </c>
-      <c r="CY35" t="s">
-        <v>5721</v>
-      </c>
-      <c r="CZ35" t="s">
-        <v>5722</v>
-      </c>
-      <c r="DA35" t="s">
-        <v>5704</v>
-      </c>
-      <c r="DB35" t="s">
-        <v>576</v>
-      </c>
-      <c r="DC35" t="s">
-        <v>1245</v>
-      </c>
-      <c r="DD35" t="s">
-        <v>1603</v>
-      </c>
-      <c r="DE35" t="s">
-        <v>5723</v>
-      </c>
-      <c r="DF35" t="s">
-        <v>5724</v>
-      </c>
-      <c r="DG35" t="s">
-        <v>5725</v>
-      </c>
-      <c r="DH35" t="s">
-        <v>555</v>
-      </c>
-      <c r="DI35" t="s">
-        <v>5726</v>
-      </c>
-      <c r="DJ35" t="s">
-        <v>1993</v>
-      </c>
-      <c r="DK35" t="s">
-        <v>5727</v>
-      </c>
-      <c r="DL35" t="s">
-        <v>5728</v>
-      </c>
-      <c r="DM35" t="s">
-        <v>1111</v>
-      </c>
-      <c r="DN35" t="s">
-        <v>5729</v>
-      </c>
-      <c r="DO35" t="s">
-        <v>5730</v>
-      </c>
-      <c r="DP35" t="s">
-        <v>5731</v>
-      </c>
-      <c r="DQ35" t="s">
-        <v>5732</v>
-      </c>
-      <c r="DR35" t="s">
-        <v>3663</v>
-      </c>
-      <c r="DS35" t="s">
-        <v>5733</v>
-      </c>
-      <c r="DT35" t="s">
-        <v>5734</v>
-      </c>
-      <c r="DU35" t="s">
-        <v>5735</v>
-      </c>
-      <c r="DV35" t="s">
-        <v>5736</v>
-      </c>
-      <c r="DW35" t="s">
-        <v>403</v>
-      </c>
-      <c r="DX35" t="s">
-        <v>5737</v>
-      </c>
-      <c r="DY35" t="s">
-        <v>5738</v>
-      </c>
-      <c r="DZ35" t="s">
-        <v>5230</v>
-      </c>
-      <c r="EA35" t="s">
-        <v>5739</v>
-      </c>
-      <c r="EB35" t="s">
-        <v>5740</v>
-      </c>
-      <c r="EC35" t="s">
-        <v>5741</v>
-      </c>
-      <c r="ED35" t="s">
-        <v>5742</v>
-      </c>
-      <c r="EE35" t="s">
-        <v>5743</v>
-      </c>
-      <c r="EF35" t="s">
-        <v>5744</v>
-      </c>
-      <c r="EG35" t="s">
-        <v>5745</v>
-      </c>
-      <c r="EH35" t="s">
-        <v>5746</v>
-      </c>
-      <c r="EI35" t="s">
-        <v>5747</v>
-      </c>
-      <c r="EJ35" t="s">
-        <v>5748</v>
-      </c>
-      <c r="EK35" t="s">
-        <v>5749</v>
-      </c>
-      <c r="EL35" t="s">
-        <v>5750</v>
-      </c>
-      <c r="EM35" t="s">
-        <v>5751</v>
-      </c>
-      <c r="EN35" t="s">
-        <v>5752</v>
-      </c>
-      <c r="EO35" t="s">
-        <v>5229</v>
-      </c>
-      <c r="EP35" t="s">
-        <v>5753</v>
-      </c>
-      <c r="EQ35" t="s">
-        <v>5754</v>
-      </c>
-      <c r="ER35" t="s">
-        <v>5732</v>
-      </c>
-      <c r="ES35" t="s">
-        <v>5755</v>
-      </c>
-      <c r="ET35" t="s">
-        <v>5720</v>
-      </c>
-      <c r="EU35" t="s">
-        <v>2012</v>
-      </c>
-      <c r="EV35" t="s">
-        <v>5756</v>
-      </c>
-      <c r="EW35" t="s">
-        <v>5757</v>
-      </c>
-      <c r="EX35" t="s">
-        <v>5758</v>
-      </c>
-      <c r="EY35" t="s">
-        <v>5759</v>
-      </c>
-      <c r="EZ35" t="s">
-        <v>3486</v>
-      </c>
-      <c r="FA35" t="s">
-        <v>5760</v>
-      </c>
-      <c r="FB35" t="s">
-        <v>5761</v>
-      </c>
-      <c r="FC35" t="s">
-        <v>5762</v>
-      </c>
-      <c r="FD35" t="s">
-        <v>842</v>
-      </c>
-      <c r="FE35" t="s">
-        <v>2366</v>
-      </c>
-      <c r="FF35" t="s">
-        <v>5763</v>
-      </c>
-      <c r="FG35" t="s">
-        <v>3561</v>
-      </c>
-      <c r="FH35" t="s">
-        <v>5764</v>
-      </c>
-      <c r="FI35" t="s">
-        <v>5765</v>
-      </c>
-      <c r="FJ35" t="s">
-        <v>5766</v>
-      </c>
-      <c r="FK35" t="s">
-        <v>5767</v>
-      </c>
-      <c r="FL35" t="s">
-        <v>5768</v>
-      </c>
-      <c r="FM35" t="s">
-        <v>3741</v>
-      </c>
-      <c r="FN35" t="s">
-        <v>2737</v>
-      </c>
-      <c r="FO35" t="s">
-        <v>5769</v>
-      </c>
-      <c r="FP35" t="s">
-        <v>5770</v>
-      </c>
-      <c r="FQ35" t="s">
-        <v>5771</v>
-      </c>
-      <c r="FR35" t="s">
-        <v>830</v>
-      </c>
-      <c r="FS35" t="s">
-        <v>5772</v>
-      </c>
-      <c r="FT35" t="s">
-        <v>5773</v>
-      </c>
-      <c r="FU35" t="s">
-        <v>3229</v>
-      </c>
-      <c r="FV35" t="s">
-        <v>5774</v>
-      </c>
-      <c r="FW35" t="s">
-        <v>976</v>
-      </c>
-      <c r="FX35" t="s">
-        <v>5775</v>
-      </c>
-      <c r="FY35" t="s">
-        <v>5776</v>
-      </c>
-      <c r="FZ35" t="s">
-        <v>5777</v>
-      </c>
-      <c r="GA35" t="s">
-        <v>5778</v>
-      </c>
-      <c r="GB35" t="s">
-        <v>5779</v>
-      </c>
-      <c r="GC35" t="s">
-        <v>5780</v>
-      </c>
-      <c r="GD35" t="s">
-        <v>5781</v>
-      </c>
-      <c r="GE35" t="s">
-        <v>5782</v>
-      </c>
-      <c r="GF35" t="s">
-        <v>5308</v>
-      </c>
-      <c r="GG35" t="s">
-        <v>5783</v>
-      </c>
-      <c r="GH35" t="s">
-        <v>4611</v>
-      </c>
-      <c r="GI35" t="s">
-        <v>1858</v>
-      </c>
-      <c r="GJ35" t="s">
-        <v>5315</v>
-      </c>
-      <c r="GK35" t="s">
-        <v>5784</v>
-      </c>
-      <c r="GL35" t="s">
-        <v>4507</v>
-      </c>
-      <c r="GM35" t="s">
-        <v>5785</v>
-      </c>
-      <c r="GN35" t="s">
-        <v>471</v>
-      </c>
-      <c r="GO35" t="s">
-        <v>5786</v>
-      </c>
-      <c r="GP35" t="s">
-        <v>5787</v>
-      </c>
-      <c r="GQ35" t="s">
-        <v>4692</v>
-      </c>
-      <c r="GR35" t="s">
-        <v>5788</v>
-      </c>
-      <c r="GS35" t="s">
-        <v>5262</v>
-      </c>
-      <c r="GT35" t="s">
-        <v>5789</v>
-      </c>
-      <c r="GU35" t="s">
-        <v>5790</v>
-      </c>
-      <c r="GV35" t="s">
-        <v>1585</v>
-      </c>
-      <c r="GW35" t="s">
-        <v>5791</v>
-      </c>
-      <c r="GX35" t="s">
-        <v>5792</v>
-      </c>
-      <c r="GY35" t="s">
-        <v>5501</v>
-      </c>
-      <c r="GZ35" t="s">
-        <v>5793</v>
-      </c>
-      <c r="HA35" t="s">
-        <v>5794</v>
-      </c>
-      <c r="HB35" t="s">
-        <v>5795</v>
-      </c>
-      <c r="HC35" t="s">
-        <v>2765</v>
-      </c>
-      <c r="HD35" t="s">
-        <v>929</v>
-      </c>
-      <c r="HE35" t="s">
-        <v>5796</v>
-      </c>
-      <c r="HF35" t="s">
-        <v>5797</v>
-      </c>
-      <c r="HG35" t="s">
-        <v>5798</v>
-      </c>
-      <c r="HH35" t="s">
-        <v>5696</v>
-      </c>
-      <c r="HI35" t="s">
-        <v>5799</v>
-      </c>
-      <c r="HJ35" t="s">
-        <v>5800</v>
-      </c>
-      <c r="HK35" t="s">
-        <v>5801</v>
-      </c>
-      <c r="HL35" t="s">
-        <v>5802</v>
-      </c>
-      <c r="HM35" t="s">
-        <v>5803</v>
-      </c>
-      <c r="HN35" t="s">
-        <v>5521</v>
-      </c>
-      <c r="HO35" t="s">
-        <v>5804</v>
-      </c>
-      <c r="HP35" t="s">
-        <v>5805</v>
-      </c>
-      <c r="HQ35" t="s">
-        <v>4152</v>
-      </c>
-      <c r="HR35" t="s">
-        <v>5806</v>
-      </c>
-      <c r="HS35" t="s">
-        <v>5807</v>
-      </c>
-      <c r="HT35" t="s">
-        <v>5808</v>
-      </c>
-      <c r="HU35" t="s">
-        <v>2365</v>
-      </c>
-      <c r="HV35" t="s">
-        <v>5809</v>
-      </c>
-      <c r="HW35" t="s">
-        <v>464</v>
-      </c>
-      <c r="HX35" t="s">
-        <v>5810</v>
-      </c>
-      <c r="HY35" t="s">
-        <v>5811</v>
-      </c>
-      <c r="HZ35" t="s">
-        <v>2550</v>
-      </c>
-      <c r="IA35" t="s">
-        <v>4247</v>
-      </c>
-      <c r="IB35" t="s">
-        <v>5680</v>
-      </c>
-      <c r="IC35" t="s">
-        <v>5812</v>
-      </c>
-      <c r="ID35" t="s">
-        <v>5813</v>
-      </c>
-      <c r="IE35" t="s">
-        <v>5814</v>
-      </c>
-      <c r="IF35" t="s">
-        <v>5815</v>
-      </c>
-      <c r="IG35" t="s">
-        <v>5614</v>
-      </c>
-      <c r="IH35" t="s">
-        <v>1548</v>
-      </c>
-      <c r="II35" t="s">
-        <v>5816</v>
-      </c>
-      <c r="IJ35" t="s">
-        <v>5817</v>
-      </c>
-      <c r="IK35" t="s">
-        <v>5818</v>
-      </c>
-      <c r="IL35" t="s">
-        <v>5819</v>
-      </c>
-      <c r="IM35" t="s">
-        <v>5820</v>
-      </c>
-      <c r="IN35" t="s">
-        <v>5821</v>
-      </c>
-      <c r="IO35" t="s">
-        <v>5822</v>
-      </c>
-      <c r="IP35" t="s">
-        <v>5823</v>
-      </c>
-      <c r="IQ35" t="s">
-        <v>2469</v>
-      </c>
-      <c r="IR35" t="s">
-        <v>5583</v>
-      </c>
-      <c r="IS35" t="s">
-        <v>423</v>
-      </c>
-      <c r="IT35" t="s">
-        <v>5824</v>
-      </c>
-      <c r="IU35" t="s">
-        <v>5825</v>
-      </c>
-      <c r="IV35" t="s">
-        <v>571</v>
-      </c>
-      <c r="IW35" t="s">
-        <v>5826</v>
-      </c>
-      <c r="IX35" t="s">
-        <v>5827</v>
-      </c>
-      <c r="IY35" t="s">
-        <v>554</v>
-      </c>
-      <c r="IZ35" t="s">
-        <v>5828</v>
-      </c>
-      <c r="JA35" t="s">
-        <v>5829</v>
-      </c>
-      <c r="JB35" t="s">
-        <v>5830</v>
-      </c>
-      <c r="JC35" t="s">
-        <v>5831</v>
-      </c>
-      <c r="JD35" t="s">
-        <v>5692</v>
-      </c>
-      <c r="JE35" t="s">
-        <v>5832</v>
-      </c>
-      <c r="JF35" t="s">
-        <v>5833</v>
-      </c>
-      <c r="JG35" t="s">
-        <v>345</v>
-      </c>
-      <c r="JH35" t="s">
-        <v>5413</v>
-      </c>
-      <c r="JI35" t="s">
-        <v>5834</v>
-      </c>
-      <c r="JJ35" t="s">
-        <v>5835</v>
-      </c>
-      <c r="JK35" t="s">
-        <v>5836</v>
-      </c>
-      <c r="JL35" t="s">
-        <v>5837</v>
-      </c>
-      <c r="JM35" t="s">
-        <v>5838</v>
-      </c>
-      <c r="JN35" t="s">
-        <v>4248</v>
-      </c>
-      <c r="JO35" t="s">
-        <v>5839</v>
-      </c>
-      <c r="JP35" t="s">
-        <v>5840</v>
-      </c>
-      <c r="JQ35" t="s">
-        <v>3365</v>
-      </c>
-      <c r="JR35" t="s">
-        <v>5841</v>
-      </c>
-      <c r="JS35" t="s">
-        <v>5842</v>
-      </c>
-      <c r="JT35" t="s">
-        <v>5843</v>
-      </c>
-      <c r="JU35" t="s">
-        <v>5844</v>
-      </c>
-      <c r="JV35" t="s">
-        <v>5845</v>
-      </c>
-      <c r="JW35" t="s">
-        <v>5846</v>
-      </c>
-      <c r="JX35" t="s">
-        <v>5847</v>
-      </c>
-      <c r="JY35" t="s">
-        <v>5848</v>
-      </c>
-      <c r="JZ35" t="s">
-        <v>5793</v>
-      </c>
-      <c r="KA35" t="s">
-        <v>5849</v>
-      </c>
-      <c r="KB35" t="s">
-        <v>5850</v>
-      </c>
-      <c r="KC35" t="s">
-        <v>5851</v>
-      </c>
-      <c r="KD35" t="s">
-        <v>5852</v>
-      </c>
-      <c r="KE35" t="s">
-        <v>5853</v>
-      </c>
-      <c r="KF35" t="s">
-        <v>5854</v>
-      </c>
-      <c r="KG35" t="s">
-        <v>5392</v>
-      </c>
-      <c r="KH35" t="s">
-        <v>5855</v>
-      </c>
-      <c r="KI35" t="s">
-        <v>5856</v>
-      </c>
-      <c r="KJ35" t="s">
-        <v>4377</v>
-      </c>
-      <c r="KK35" t="s">
-        <v>1401</v>
-      </c>
-      <c r="KL35" t="s">
-        <v>5857</v>
-      </c>
-      <c r="KM35" t="s">
-        <v>5858</v>
-      </c>
-      <c r="KN35" t="s">
-        <v>5859</v>
-      </c>
-      <c r="KO35" t="s">
-        <v>5860</v>
-      </c>
-      <c r="KP35" t="s">
-        <v>1451</v>
-      </c>
-      <c r="KQ35" t="s">
-        <v>5861</v>
-      </c>
-      <c r="KR35" t="s">
-        <v>5862</v>
-      </c>
-      <c r="KS35" t="s">
-        <v>883</v>
-      </c>
-      <c r="KT35" t="s">
-        <v>5863</v>
-      </c>
-      <c r="KU35" t="s">
-        <v>5864</v>
-      </c>
-      <c r="KV35" t="s">
-        <v>5865</v>
-      </c>
-      <c r="KW35" t="s">
-        <v>977</v>
-      </c>
-      <c r="KX35" t="s">
-        <v>5866</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
